--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>API — Work Order Settings</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>API — Work Order Settings</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>API — Work Order Settings</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>API — Work Order Settings</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>API — Work Order Settings</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>API — Permissions</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>API — Permissions</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -1447,47 +1447,47 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-05</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Completion — No-PO / Skip (Story 2)</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when a required vehicle field is missing</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>S2-R2 / S2 AC (missing required fields blocked)</t>
         </is>
@@ -1870,47 +1870,47 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-14</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Verify Complete Without Receiving completes the WO, keeps unreceived parts waiting, and keeps the line Receive button</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>S3-R6</t>
         </is>
@@ -2199,94 +2199,94 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-21</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Completion — Line approval gate</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Key Decision (all lines approved) / S3-R9 / S4-R8</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-22</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Completion — Line approval gate</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Key Decision (holds regardless of Auto-approve)</t>
         </is>
@@ -3515,47 +3515,47 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>SF-VMIS-01</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>S6-R1</t>
         </is>
@@ -7134,47 +7134,47 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="4" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-01</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G142" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I142" s="4" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>S2-R2 / S3-R3 / S4-R3</t>
         </is>
@@ -7604,47 +7604,47 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="4" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-11</t>
         </is>
       </c>
-      <c r="B152" s="4" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C152" s="4" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>Verify the approve-line error text appears when completing with an unapproved line</t>
         </is>
       </c>
-      <c r="D152" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G152" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I152" s="4" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
         <is>
           <t>Key Decision (line approval)</t>
         </is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 78 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 71 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I160"/>
+  <dimension ref="A1:K160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -504,6 +504,8 @@
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,6 +554,16 @@
           <t>Related story/question</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>VIU sub-bucket</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>VIU sub-bucket detail (QA-pending only)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -599,6 +611,12 @@
           <t>S1-R1..R8 / Story 1 AC</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -646,6 +664,12 @@
           <t>S1 AC / Key Decision (no operatingMode)</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -693,6 +717,12 @@
           <t>Q5 | S1-R2 (Create purchase orders)</t>
         </is>
       </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -740,6 +770,12 @@
           <t>S1-R3 (Vendor invoice Optional/Required)</t>
         </is>
       </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -787,6 +823,12 @@
           <t>S1-R1 (Auto-approve ON)</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -834,6 +876,12 @@
           <t>S1-R1 (Auto-approve OFF)</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -881,6 +929,12 @@
           <t>S1-R5..R8 (existing settings surfaced)</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -928,6 +982,12 @@
           <t>Q3, Q4 | S1 first-use defaults / §4</t>
         </is>
       </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -975,6 +1035,12 @@
           <t>S1-R9 (Save persists org-wide)</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1022,6 +1088,16 @@
           <t>S1-R9 (future completions only, never retroactive)</t>
         </is>
       </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1069,6 +1145,12 @@
           <t>S1 AC (non-admin can't see/modify)</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1116,6 +1198,12 @@
           <t>S1 AC (no requireVin / no operatingMode field)</t>
         </is>
       </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1163,6 +1251,12 @@
           <t>Q6 | S1 (Save dirty-state)</t>
         </is>
       </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1210,6 +1304,12 @@
           <t>S1-R4 (Require review before completion)</t>
         </is>
       </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1257,6 +1357,12 @@
           <t>S1 AC (helper text per toggle)</t>
         </is>
       </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1304,6 +1410,12 @@
           <t>S2-R1</t>
         </is>
       </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1351,6 +1463,12 @@
           <t>S2-R2 / S2-R3 / S2-R4</t>
         </is>
       </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1398,53 +1516,65 @@
           <t>S2-R4 / S2-R5 / S15-R3</t>
         </is>
       </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-04</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Completion — No-PO / Skip (Story 2)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Verify Go to Invoice from the Success screen opens the Finance step where the invoice number is shown</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>S2-R5 / S15-R3</t>
         </is>
       </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1492,6 +1622,12 @@
           <t>S2-R2 / S2 AC (missing required fields blocked)</t>
         </is>
       </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1539,6 +1675,12 @@
           <t>Q5 | S2-R6 / S2 AC (Create POs off ⇒ no PO)</t>
         </is>
       </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1586,6 +1728,12 @@
           <t>Q2 | S2-R6 / §5 invariant 1</t>
         </is>
       </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1633,6 +1781,16 @@
           <t>S2-R2 / S2 AC (auto-pick off ⇒ pick in modal)</t>
         </is>
       </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>flip Auto-pick Inventory OFF and drive the completion modal pick step.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1680,6 +1838,12 @@
           <t>S2-R6 / S2 AC (re-open returns to Approved)</t>
         </is>
       </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1727,6 +1891,16 @@
           <t>S2 AC (individual-line Complete + per-part receive kept)</t>
         </is>
       </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1774,6 +1948,12 @@
           <t>S3-R4</t>
         </is>
       </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1821,6 +2001,12 @@
           <t>S3-R1 / S3-R2 / S3-R9</t>
         </is>
       </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1868,6 +2054,16 @@
           <t>S3-R5</t>
         </is>
       </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>a WO PO in an ORDERED/deliverable state (vendor-assigned part on a PO with pending delivery); optional-flow 'Receive Parts' routed back to the WO, not Accept Delivery.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1915,6 +2111,12 @@
           <t>S3-R6</t>
         </is>
       </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1962,100 +2164,122 @@
           <t>S3-R7 / S3-R9 (Cancel idempotent)</t>
         </is>
       </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>drive optional-flow Cancel and re-open; check no duplicate POs.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-16</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>S3-R3</t>
         </is>
       </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-17</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>S3-R8</t>
         </is>
       </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2103,6 +2327,12 @@
           <t>S4-R4</t>
         </is>
       </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2150,6 +2380,16 @@
           <t>S4-R5 / S4-R7</t>
         </is>
       </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>a receivable PO + vendor invoice number to drive the required-invoice receive round-trip.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2197,6 +2437,16 @@
           <t>S4-R6</t>
         </is>
       </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>required-invoice flow (requireVendorInvoiceNumber=ON) + part-bearing WO; Cancel = no change.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2244,6 +2494,12 @@
           <t>Key Decision (all lines approved) / S3-R9 / S4-R8</t>
         </is>
       </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2291,6 +2547,12 @@
           <t>Key Decision (holds regardless of Auto-approve)</t>
         </is>
       </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2338,6 +2600,16 @@
           <t>S3-R9 (no duplicate POs on re-Complete)</t>
         </is>
       </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>re-run completion after a prior attempt; check no duplicate POs.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -2385,6 +2657,16 @@
           <t>S3-C1 / S4-C1 / Resolve Cores handoff</t>
         </is>
       </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>an inventory/catalog part flagged is_core (genuine core) + a received cored line; the manual sub-form only sets core_charge (is_core stays false) and resolve-cores needs receiving.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -2432,6 +2714,16 @@
           <t>S3-C1 (skipped if none)</t>
         </is>
       </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>a genuine core part to prove the Resolve-Cores step appears, plus a no-core WO to prove it is skipped (is_core not seedable via canned/sub-form).</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -2479,6 +2771,16 @@
           <t>S3-C2</t>
         </is>
       </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>a special-order core part + optional-invoice completion (needs is_core part).</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -2526,6 +2828,16 @@
           <t>S3-C3</t>
         </is>
       </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>an unresolved special-order core at the invoice gate ('Cores pending' flag) — needs is_core part + receiving.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2573,6 +2885,16 @@
           <t>S3-C4</t>
         </is>
       </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>resolve cores at the Create-Invoice gate -&gt; receive the cored line (needs is_core part + receiving).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2620,6 +2942,16 @@
           <t>S3-C4 (cancel path)</t>
         </is>
       </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>cancel the invoice-gate core resolution (needs is_core part + invoice gate).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -2667,6 +2999,16 @@
           <t>S4-C2</t>
         </is>
       </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>special-order cores in the required-invoice receive round-trip (needs is_core part + receiving).</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -2714,6 +3056,16 @@
           <t>S3 Guardrail (PartRequest-only core)</t>
         </is>
       </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>an unresolved special-order core that exists only as a PartRequest (needs is_core part).</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -2761,6 +3113,16 @@
           <t>S3 Guardrail (part-sale vs service WO)</t>
         </is>
       </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>a part-sale WO vs service WO with cores (needs is_core part + receiving).</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -2808,6 +3170,16 @@
           <t>Resolve Cores handoff (live +$ total)</t>
         </is>
       </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>the Resolve-Cores step live '+$ to invoice' total (needs is_core part + receiving).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2855,6 +3227,12 @@
           <t>TS-R1</t>
         </is>
       </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2902,6 +3280,12 @@
           <t>TS-R2</t>
         </is>
       </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2949,6 +3333,12 @@
           <t>TS-R3</t>
         </is>
       </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2996,147 +3386,171 @@
           <t>TS-R4</t>
         </is>
       </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>SF-TECH-05</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the multi-line tech-story gate flow (with the specific test-id).</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>TS-R4 (multi-line navigation)</t>
         </is>
       </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>SF-TECH-06</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the multi-line tech-story gate flow (with the specific test-id).</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>TS-R5</t>
         </is>
       </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>SF-TECH-07</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the multi-line tech-story gate flow (with the specific test-id).</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>TS-R6 (test id)</t>
         </is>
       </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -3184,147 +3598,171 @@
           <t>Q9, Q4 | TS Decision vs S15-R2</t>
         </is>
       </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>SF-VPART-01</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Verify a part can be requested with only description, quantity and sell price (part number, cost, vendor empty)</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed + drive the vendorless / no-PN part add flow.</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>S5-R1</t>
         </is>
       </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>SF-VPART-02</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Verify adding a part is blocked when description, quantity or sell price is missing</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the vendorless / no-PN add sub-form validation (not reached in the last session's budget).</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>S5-R1 / S5 AC (validation)</t>
         </is>
       </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>SF-VPART-03</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed + drive the vendorless / no-PN part add flow.</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>S5-R2</t>
         </is>
       </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -3372,53 +3810,69 @@
           <t>S5-R3</t>
         </is>
       </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>edit an existing vendorless part inline (part_number/sell/qty row fields exist).</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>SF-VPART-05</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Verify a no-part-number part creates no inventory item and no Part History</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed + drive the vendorless / no-PN part add flow.</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>S5-R4 / S5 AC (no inventory interaction)</t>
         </is>
       </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -3466,6 +3920,16 @@
           <t>S5 AC (transitions out of vendorless)</t>
         </is>
       </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>add a PN + vendor to a vendorless part and confirm it transitions out of vendorless.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -3513,6 +3977,16 @@
           <t>S5-R4 / S5 AC (receive gate)</t>
         </is>
       </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>a receivable/deliverable state to prove a vendorless/no-PN part cannot be received until PN + vendor entered.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3560,6 +4034,12 @@
           <t>S6-R1</t>
         </is>
       </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3607,6 +4087,12 @@
           <t>S6-R2</t>
         </is>
       </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -3654,6 +4140,16 @@
           <t>S6-R3</t>
         </is>
       </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks sync inspection (vendor-missing PO excluded from QB).</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -3701,6 +4197,16 @@
           <t>S6-R4</t>
         </is>
       </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>vendor-missing PO seedable by completing a WO with vendorless vendor parts; check vendor-select + PN-edit options.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -3748,6 +4254,16 @@
           <t>S6-R5</t>
         </is>
       </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>vendor-missing PO; confirm the flag clears once vendor + PN supplied.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -3795,6 +4311,16 @@
           <t>S6-R6</t>
         </is>
       </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>reports data (Vendor Missing POs flagged 'needs vendor').</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -3842,6 +4368,12 @@
           <t>Story 7 — PO multi-select (SV-7702) | S7-R1</t>
         </is>
       </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -3889,6 +4421,12 @@
           <t>Story 7 — PO multi-select (SV-7702) | S7-R2</t>
         </is>
       </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -3936,6 +4474,12 @@
           <t>Story 7 — PO multi-select (SV-7702) | S7-R3</t>
         </is>
       </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -3983,6 +4527,12 @@
           <t>Story 7 — PO multi-select (SV-7702) | S7-R4</t>
         </is>
       </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -4030,6 +4580,12 @@
           <t>Story 7 — PO multi-select (SV-7702) | S7-R5</t>
         </is>
       </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -4077,6 +4633,12 @@
           <t>Story 7 — PO multi-select (SV-7702) | S7 (select-all scope)</t>
         </is>
       </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -4124,6 +4686,12 @@
           <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R1</t>
         </is>
       </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -4171,6 +4739,12 @@
           <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R2 / S8-R3</t>
         </is>
       </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -4218,6 +4792,12 @@
           <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R4</t>
         </is>
       </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -4265,6 +4845,12 @@
           <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R5</t>
         </is>
       </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -4312,6 +4898,12 @@
           <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R6</t>
         </is>
       </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -4359,6 +4951,12 @@
           <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R7 / S10-R2</t>
         </is>
       </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -4406,6 +5004,12 @@
           <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R8</t>
         </is>
       </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -4453,6 +5057,12 @@
           <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R10</t>
         </is>
       </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -4500,6 +5110,12 @@
           <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R11</t>
         </is>
       </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -4547,6 +5163,12 @@
           <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-C1 / S8-C2</t>
         </is>
       </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -4594,6 +5216,12 @@
           <t>Story 9 — Apply invoice to selected POs (SV-7704) | S9-R1</t>
         </is>
       </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -4641,6 +5269,12 @@
           <t>Story 9 — Apply invoice to selected POs (SV-7704) | S9-R2</t>
         </is>
       </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -4688,6 +5322,12 @@
           <t>Story 9 — Apply invoice to selected POs (SV-7704) | S9-R3</t>
         </is>
       </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -4735,6 +5375,16 @@
           <t>S10-R1</t>
         </is>
       </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>no-PN PO line; inline Missing-part-number Edit -&gt; enter -&gt; save persists.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -4782,6 +5432,16 @@
           <t>S10 AC (new number)</t>
         </is>
       </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>receiving + inventory/catalog inspection (new PN creates inventory part + stock + Part History on receive).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -4829,6 +5489,16 @@
           <t>S10 AC (existing number)</t>
         </is>
       </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>receiving + inventory inspection (existing PN links to item, updates stock/cost/history).</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -4876,6 +5546,16 @@
           <t>S10-R2 / S8-R7</t>
         </is>
       </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>a WO in invoiced/paid state (sell-field locking).</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -4923,6 +5603,16 @@
           <t>S10 Negative</t>
         </is>
       </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>an invoiced/paid WO + a receive attempt (cannot receive without PN).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -4970,6 +5660,16 @@
           <t>S10 Technical guardrails</t>
         </is>
       </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>receiving + catalog/inventory back-end inspection (real creation/linking, not a stored string).</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -5017,6 +5717,16 @@
           <t>S11-R1</t>
         </is>
       </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>seed a WO-originated PO; confirm Receive action on PO list + detail.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -5064,6 +5774,16 @@
           <t>S11-R2</t>
         </is>
       </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>an ordered/deliverable PO so the Receive action opens Accept Delivery (optional-flow Receive Parts routed back to the WO in VIU).</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5111,6 +5831,12 @@
           <t>S11-R3</t>
         </is>
       </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -5158,6 +5884,12 @@
           <t>S12 (existing multi-vendor)</t>
         </is>
       </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -5205,6 +5937,12 @@
           <t>Q11 | S12-R1</t>
         </is>
       </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -5252,6 +5990,16 @@
           <t>S12-R2</t>
         </is>
       </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>a deliverable PO to exercise Accept Delivery receive gates (vendor set, missing PN entered, invoice # captured).</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -5299,6 +6047,12 @@
           <t>Q11 | S12-R3</t>
         </is>
       </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -5346,6 +6100,16 @@
           <t>S12-R4</t>
         </is>
       </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks inspection (per-vendor vendor bill + separate AP entry).</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -5393,6 +6157,16 @@
           <t>S12 (existing) received-more-than-ordered</t>
         </is>
       </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>a receive with received qty &gt; ordered qty (received-more-than-ordered warning).</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -5440,6 +6214,16 @@
           <t>S13-R1</t>
         </is>
       </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>vendor-missing PO; confirm vendor dropdown assigns a vendor at PO level and saves.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -5487,6 +6271,16 @@
           <t>S13-R2</t>
         </is>
       </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>a PO where the assigned vendor already exists on the PO (Add-to-vendor merge vs keep-separate prompt).</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -5534,6 +6328,16 @@
           <t>S13-R3</t>
         </is>
       </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>two POs for the same WO with the same vendor (merge-POs prompt).</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -5581,6 +6385,16 @@
           <t>S13-R4 / S13-R5</t>
         </is>
       </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>a vendor-missing PO + receive-enable + QB-flag-clear check after auto-assign.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -5628,6 +6442,16 @@
           <t>S13 Technical guardrails</t>
         </is>
       </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>invoiced/paid WO + multi-PO merge guardrail state (match-by-ID, merge scoped to same WO, receive blocked when invoiced/paid).</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -5675,6 +6499,12 @@
           <t>Story 14 — Waiting-on-Parts column (SV-7709) | S14-R1</t>
         </is>
       </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -5722,6 +6552,12 @@
           <t>Story 14 — Waiting-on-Parts column (SV-7709) | S14-R2</t>
         </is>
       </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -5769,6 +6605,12 @@
           <t>Story 14 — Waiting-on-Parts column (SV-7709) | S14-R3</t>
         </is>
       </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -5816,6 +6658,12 @@
           <t>R1</t>
         </is>
       </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -5863,6 +6711,12 @@
           <t>R2</t>
         </is>
       </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -5910,6 +6764,16 @@
           <t>R3</t>
         </is>
       </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>enable Require Review; Details step collects mileage + engine hours (VIN captured later by reviewer).</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -5957,6 +6821,16 @@
           <t>R4</t>
         </is>
       </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>a deliverable PO in the review flow (Receive Parts routes to the shared receive page).</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6004,6 +6878,12 @@
           <t>R5 / R6</t>
         </is>
       </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6051,6 +6931,12 @@
           <t>R7 / R10</t>
         </is>
       </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -6098,6 +6984,16 @@
           <t>R6</t>
         </is>
       </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>enable Require Review; Send to Review locks lines to Complete + auto-picks inventory.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -6145,6 +7041,12 @@
           <t>Q8, Q4 | R5 / R8 (distinct Reviewed state)</t>
         </is>
       </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
@@ -6192,6 +7094,12 @@
           <t>R7 (role-gating) | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
+      <c r="J121" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K121" s="6" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -6239,6 +7147,12 @@
           <t>Q7 | R7 / R10 (optional note)</t>
         </is>
       </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -6286,6 +7200,12 @@
           <t>Q8 | R8</t>
         </is>
       </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -6333,6 +7253,16 @@
           <t>R9</t>
         </is>
       </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>enable Require Review; confirm a 'Ready for Review' list filter/column.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -6380,6 +7310,16 @@
           <t>R11</t>
         </is>
       </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>enable Require Review; all lines must be approved to Send to Review (approve-line error).</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -6427,6 +7367,16 @@
           <t>R Core parts / invoicing block</t>
         </is>
       </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>cores + receiving in the review flow (cores resolved before sign-off; invoicing blocked until Reviewed + cores resolved).</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -6474,6 +7424,12 @@
           <t>Q1 | R Open (default)</t>
         </is>
       </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -6521,6 +7477,12 @@
           <t>S15-R1</t>
         </is>
       </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -6568,6 +7530,12 @@
           <t>S15-R2</t>
         </is>
       </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -6615,6 +7583,12 @@
           <t>S15-R3</t>
         </is>
       </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -6662,6 +7636,12 @@
           <t>Q10 | S15-R4</t>
         </is>
       </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -6709,6 +7689,12 @@
           <t>S1 AC / §8 Permissions</t>
         </is>
       </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
@@ -6756,6 +7742,12 @@
           <t>§8 Permissions | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
+      <c r="J133" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K133" s="6" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -6803,6 +7795,12 @@
           <t>Story 8 — PO Bulk Receive page (SV-7703) | §8 Permissions</t>
         </is>
       </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
@@ -6850,6 +7848,12 @@
           <t>R7 / §8 role-gating review | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K135" s="6" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -6897,6 +7901,12 @@
           <t>S11-R3</t>
         </is>
       </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
@@ -6944,6 +7954,12 @@
           <t>§8 BE enforcement | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -6991,6 +8007,12 @@
           <t>§8 role-gating review | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
@@ -7038,53 +8060,65 @@
           <t>R7 (reviewer != completer) | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
+      <c r="J139" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K139" s="6" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="4" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>SF-PERM-09</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G140" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: a role account WITHOUT 'See Financial Data' to prove the vendorless part-add gate (tech confirmed no seeFinancialData; sub-form not reached).</t>
-        </is>
-      </c>
-      <c r="I140" s="4" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>S5 / §9 (See Financial Data gate)</t>
         </is>
       </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -7132,6 +8166,16 @@
           <t>§9 per-role completion matrix</t>
         </is>
       </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>needs-account</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>role accounts Office / Service Manager / Foreman (ideally also Senior SA / Parts Manager / Sales Rep / Time Clock) to run the per-role completion matrix (only admin+ and Technician- available).</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -7179,6 +8223,12 @@
           <t>S2-R2 / S3-R3 / S4-R3</t>
         </is>
       </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -7226,53 +8276,69 @@
           <t>S15-R2 / S3-R3</t>
         </is>
       </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>an asset/vehicle with NO VIN so the non-review wizard prompts for VIN (VIN is currently prefilled from the asset, so the gate is not reachable with existing assets).</t>
+        </is>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-03</t>
         </is>
       </c>
-      <c r="B144" s="4" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C144" s="4" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G144" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I144" s="4" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>S3-R3 / S4-R3</t>
         </is>
       </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -7320,6 +8386,12 @@
           <t>TS-R4</t>
         </is>
       </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -7367,6 +8439,16 @@
           <t>S3-R3 / S4-R5 / §4</t>
         </is>
       </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>a required-invoice receive attempt without an invoice number (receivable PO).</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -7414,6 +8496,16 @@
           <t>S10 / S12-R2 / S13</t>
         </is>
       </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>a vendor-missing part receive attempt (deliverable state).</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -7461,6 +8553,16 @@
           <t>R7</t>
         </is>
       </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>review flow; Confirm Review disabled until VIN entered in Mark Reviewed dialog.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -7508,6 +8610,16 @@
           <t>S3-R9 (idempotency)</t>
         </is>
       </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>re-complete after cancelling; check no duplicate POs.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -7555,6 +8667,12 @@
           <t>Story 8 — Bulk Receive field locking (S8-R7, SV-7703) | S8-R7 / §4 field locking</t>
         </is>
       </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -7602,6 +8720,12 @@
           <t>Story 9 — Apply-invoice uniqueness (S9-R3, SV-7704) | S9-R3 / §4 (uniqueness relaxed)</t>
         </is>
       </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -7649,6 +8773,12 @@
           <t>Key Decision (line approval)</t>
         </is>
       </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -7696,6 +8826,12 @@
           <t>Q2 | §5 invariant 1</t>
         </is>
       </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
@@ -7743,6 +8879,12 @@
           <t>Q5 | §5 / §4 (Create POs OFF)</t>
         </is>
       </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -7790,6 +8932,16 @@
           <t>§5 invariant 2</t>
         </is>
       </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks / inventory back-end inspection (receive -&gt; Delivery -&gt; Vendor Bill -&gt; QBO) — likely needs dev/QB access.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -7837,6 +8989,16 @@
           <t>§5 (vendorless/no-PN)</t>
         </is>
       </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks / inventory inspection (vendorless/no-PN part = zero inventory interaction) — likely needs dev/QB access.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -7884,6 +9046,16 @@
           <t>§5 / S6-R3</t>
         </is>
       </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks inspection (Vendor-Missing POs excluded from QB until vendor + PN) — likely needs dev/QB access.</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -7931,6 +9103,16 @@
           <t>§8 (cost at completion)</t>
         </is>
       </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks inspection (cost-at-completion to avoid $0-cost margins) — likely needs dev/QB access.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -7978,6 +9160,16 @@
           <t>§5 (Journal Entry / Inventory → QBO)</t>
         </is>
       </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks inspection (Journal Entry / Inventory sync fires on invoice creation) — likely needs dev/QB access.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -8023,6 +9215,16 @@
       <c r="I160" s="4" t="inlineStr">
         <is>
           <t>§5 invariant 3</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>Inventory Part History inspection for any part that becomes inventory-tracked — likely needs dev/QB access.</t>
         </is>
       </c>
     </row>
@@ -8037,7 +9239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -8099,7 +9301,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -8129,7 +9331,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -8246,101 +9448,101 @@
       <c r="C18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>WHAT TO SEND ME NEXT (to unblock each batch)</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA) — by sub-bucket</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>• Milos's answers to the 11 Open Questions</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>unblocks 15 cases (all the MILOS-ANSWER rows). Send the filled-in OpenQuestions-for-Milos sheet.</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>admin+tech + normal data; just needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>• Dev deploys Story 8 — PO Bulk Receive page (SV-7703)</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>unblocks 12 case(s); then I re-run VIU and send an update file.</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>needs a data state not seedable via the app (see per-case detail).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>• Dev deploys Story 7 — PO multi-select (SV-7702)</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>unblocks 6 case(s); then I re-run VIU and send an update file.</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>needs-account</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>needs a role account we don't have (see per-case detail).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>• Dev deploys Story 9 — Apply invoice to selected POs (SV-7704)</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>unblocks 4 case(s); then I re-run VIU and send an update file.</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
+          <t>TOTAL VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="C23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>• Dev deploys Story 14 — Waiting-on-Parts column (SV-7709)</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>unblocks 3 case(s); then I re-run VIU and send an update file.</t>
-        </is>
-      </c>
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
       <c r="C24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>• Fresh QA cookies for sv7301 (admin + tech) + seeded test data</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>unblocks the bulk of the 71 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
-        </is>
-      </c>
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>WHAT TO SEND ME NEXT (to unblock each batch)</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>• A 2nd/3rd role account (Office, Service Manager, Foreman) — some WITHOUT 'See Financial Data'</t>
+          <t>• Milos's answers to the 11 Open Questions</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>unblocks SF-PERM-09 and SF-PERM-10 (per-role completion + vendorless-add gate).</t>
+          <t>unblocks 15 cases (all the MILOS-ANSWER rows). Send the filled-in OpenQuestions-for-Milos sheet.</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
@@ -8348,15 +9550,93 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
+          <t>• Dev deploys Story 8 — PO Bulk Receive page (SV-7703)</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>unblocks 12 case(s); then I re-run VIU and send an update file.</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>• Dev deploys Story 7 — PO multi-select (SV-7702)</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>unblocks 6 case(s); then I re-run VIU and send an update file.</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>• Dev deploys Story 9 — Apply invoice to selected POs (SV-7704)</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>unblocks 4 case(s); then I re-run VIU and send an update file.</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>• Dev deploys Story 14 — Waiting-on-Parts column (SV-7709)</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>unblocks 3 case(s); then I re-run VIU and send an update file.</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>• Fresh QA cookies for sv7301 (admin + tech) + seeded test data</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>unblocks the bulk of the 59 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>• A 2nd/3rd role account (Office, Service Manager, Foreman) — some WITHOUT 'See Financial Data'</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>unblocks SF-PERM-09 and SF-PERM-10 (per-role completion + vendorless-add gate).</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
           <t>• A dev/PO ruling on FE-only BE enforcement + the missing reviewer!=completer rule (resolve SV-8183 'BE enforces' vs SV-7864 atom-collapse)</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>finalizes the 6 BUG/RULING cases.</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -1043,61 +1043,57 @@
       <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SF-SET-10</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Work Order Settings</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Verify a settings change applies to future completions only and not to already-completed work orders</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: toggle the setting and confirm the downstream behaviour.</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>S1-R9 (future completions only, never retroactive)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2555,61 +2551,57 @@
       <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-23</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Completion — Idempotency</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>S3-R9 (no duplicate POs on re-Complete)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>re-run completion after a prior attempt; check no duplicate POs.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -5672,61 +5664,57 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>SF-RCV-01</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
         <is>
           <t>S11-R1</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K96" s="4" t="inlineStr">
-        <is>
-          <t>seed a WO-originated PO; confirm Receive action on PO list + detail.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -8121,61 +8109,57 @@
       <c r="K140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="4" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>SF-PERM-10</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G141" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H141" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: additional role accounts (Office / Service Manager / Foreman) to run the per-role completion matrix (only Technician-negative confirmed).</t>
-        </is>
-      </c>
-      <c r="I141" s="4" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>§9 per-role completion matrix</t>
         </is>
       </c>
-      <c r="J141" s="5" t="inlineStr">
-        <is>
-          <t>needs-account</t>
-        </is>
-      </c>
-      <c r="K141" s="4" t="inlineStr">
-        <is>
-          <t>role accounts Office / Service Manager / Foreman (ideally also Senior SA / Parts Manager / Sales Rep / Time Clock) to run the per-role completion matrix (only admin+ and Technician- available).</t>
-        </is>
-      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8565,61 +8549,57 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-08</t>
         </is>
       </c>
-      <c r="B149" s="4" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G149" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I149" s="4" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>S3-R9 (idempotency)</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K149" s="4" t="inlineStr">
-        <is>
-          <t>re-complete after cancelling; check no duplicate POs.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -9301,7 +9281,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9331,7 +9311,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9471,7 +9451,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
@@ -9501,7 +9481,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
@@ -9516,7 +9496,7 @@
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C23" s="8" t="inlineStr"/>
     </row>
@@ -9607,7 +9587,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 59 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 54 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -5717,61 +5717,57 @@
       <c r="K96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>SF-RCV-02</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
         <is>
           <t>S11-R2</t>
         </is>
       </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K97" s="4" t="inlineStr">
-        <is>
-          <t>an ordered/deliverable PO so the Receive action opens Accept Delivery (optional-flow Receive Parts routed back to the WO in VIU).</t>
-        </is>
-      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5978,14 +5974,14 @@
           <t>S12-R2</t>
         </is>
       </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>a deliverable PO to exercise Accept Delivery receive gates (vendor set, missing PN entered, invoice # captured).</t>
+          <t>BATCH 5: Accept Delivery happy path driven on PO 93fb82e9 (vendor set, invoice # captured -&gt; Receive 201). Only the NEGATIVE sub-gates remain (receive blocked with vendor unset / missing PN) — need a vendor-missing item on an Accept Delivery group (seedable by completing a WO with vendorless vendor parts).</t>
         </is>
       </c>
     </row>
@@ -6100,61 +6096,57 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>SF-RCV-09</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
-        </is>
-      </c>
-      <c r="I104" s="4" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>S12 (existing) received-more-than-ordered</t>
         </is>
       </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K104" s="4" t="inlineStr">
-        <is>
-          <t>a receive with received qty &gt; ordered qty (received-more-than-ordered warning).</t>
-        </is>
-      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -9281,7 +9273,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9311,7 +9303,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9451,7 +9443,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
@@ -9466,7 +9458,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
@@ -9496,7 +9488,7 @@
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" s="8" t="inlineStr"/>
     </row>
@@ -9587,7 +9579,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 54 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 52 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -1777,14 +1777,14 @@
           <t>S2-R2 / S2 AC (auto-pick off ⇒ pick in modal)</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>reachable-now</t>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>flip Auto-pick Inventory OFF and drive the completion modal pick step.</t>
+          <t>BATCH 6: with autoPickInventoryParts OFF, adding a catalog inventory part (P550848) still picks it via the bin-quantity input (status in_stock) so no Pick step appears. Needs an UNPICKED inventory part at completion (not seedable via the current add-part form).</t>
         </is>
       </c>
     </row>
@@ -1842,61 +1842,57 @@
       <c r="K25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-10</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Completion — No-PO / Skip (Story 2)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>S2 AC (individual-line Complete + per-part receive kept)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2057,7 +2053,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>a WO PO in an ORDERED/deliverable state (vendor-assigned part on a PO with pending delivery); optional-flow 'Receive Parts' routed back to the WO, not Accept Delivery.</t>
+          <t>BATCH 6: a deliverable ORDERED WO PO IS now achievable (Source=Vendor + real vendor + free-text PN). The shared Accept Delivery page opens for it via the PO Receive action, BUT the completion WIZARD Receive Parts still routes back to the WO lines (PO not placed until completion), and receiving the WO PO 500s (BUG-11).</t>
         </is>
       </c>
     </row>
@@ -2115,61 +2111,57 @@
       <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-15</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>S3-R7 / S3-R9 (Cancel idempotent)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>drive optional-flow Cancel and re-open; check no duplicate POs.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2383,66 +2375,62 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>a receivable PO + vendor invoice number to drive the required-invoice receive round-trip.</t>
+          <t>BATCH 6: deliverable WO PO achieved, but the receive round-trip is blocked by BUG-11 (POST /api/inventory/orders/accept returns 500 for a WO PO).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-20</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>S4-R6</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>required-invoice flow (requireVendorInvoiceNumber=ON) + part-bearing WO; Cancel = no change.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3757,61 +3745,57 @@
       <c r="K60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>SF-VPART-04</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed + drive the vendorless / no-PN part add flow.</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>S5-R3</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>edit an existing vendorless part inline (part_number/sell/qty row fields exist).</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3867,61 +3851,57 @@
       <c r="K62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>SF-VPART-06</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed + drive the vendorless / no-PN part add flow.</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>S5 AC (transitions out of vendorless)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>add a PN + vendor to a vendorless part and confirm it transitions out of vendorless.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -3976,7 +3956,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>a receivable/deliverable state to prove a vendorless/no-PN part cannot be received until PN + vendor entered.</t>
+          <t>BATCH 6: deliverable WO PO achievable, but receiving it is blocked by BUG-11 (500), so the cannot-receive-until-PN+vendor proof cannot complete.</t>
         </is>
       </c>
     </row>
@@ -4189,14 +4169,14 @@
           <t>S6-R4</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>reachable-now</t>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>vendor-missing PO seedable by completing a WO with vendorless vendor parts; check vendor-select + PN-edit options.</t>
+          <t>BATCH 6: vendor-missing WO PO seeded (S2-15774), but NO assign-vendor dropdown / PN-edit on any reachable surface (PO list = Receive only; single /accept-delivery = Vendor Missing badge + invoice/qty/Receive only; /parts/deliveries = received invoices). Appears to require the Bulk Receive page (Story 8, NOT built).</t>
         </is>
       </c>
     </row>
@@ -4246,14 +4226,14 @@
           <t>S6-R5</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>reachable-now</t>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>vendor-missing PO; confirm the flag clears once vendor + PN supplied.</t>
+          <t>BATCH 6: no assign-vendor UI on reachable PO/receive surfaces to clear the flag (see SF-VMIS-04); part-level vendor+PN add DOES clear vendorless via WO Parts editor (part/change-request, SF-VPART-06). PO-surface flag-clear appears tied to Bulk Receive (Story 8, NOT built).</t>
         </is>
       </c>
     </row>
@@ -5367,14 +5347,14 @@
           <t>S10-R1</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>reachable-now</t>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>no-PN PO line; inline Missing-part-number Edit -&gt; enter -&gt; save persists.</t>
+          <t>BATCH 6: no inline Missing-part-number Edit on the vendor-missing PO Accept Delivery (empty PN cell, no edit control). Inline PN-fix appears tied to the Bulk Receive page (Story 8, NOT built).</t>
         </is>
       </c>
     </row>
@@ -5974,14 +5954,14 @@
           <t>S12-R2</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>reachable-now</t>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>BATCH 5: Accept Delivery happy path driven on PO 93fb82e9 (vendor set, invoice # captured -&gt; Receive 201). Only the NEGATIVE sub-gates remain (receive blocked with vendor unset / missing PN) — need a vendor-missing item on an Accept Delivery group (seedable by completing a WO with vendorless vendor parts).</t>
+          <t>BATCH 6: on a deliverable WO PO the Accept Delivery gates are present (vendor set, invoice # field), but Receive 500s (BUG-11); on a vendor-missing WO PO there is no assign-vendor / PN-edit control. Happy path was proven on an INVENTORY PO in BATCH 5; the WO-PO negative sub-gates need BUG-11 fixed.</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6071,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>QuickBooks inspection (per-vendor vendor bill + separate AP entry).</t>
+          <t>QuickBooks inspection (per-vendor vendor bill + separate AP entry) — and WO-PO receive additionally blocked by BUG-11 (500).</t>
         </is>
       </c>
     </row>
@@ -6194,14 +6174,14 @@
           <t>S13-R1</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>reachable-now</t>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>vendor-missing PO; confirm vendor dropdown assigns a vendor at PO level and saves.</t>
+          <t>BATCH 6: vendor-missing WO PO seeded, but no PO-level vendor dropdown on any reachable surface (PO list/accept-delivery/deliveries). The vendor-missing-group vendor dropdown appears to live on the Bulk Receive page (Story 8/13 UI, NOT built).</t>
         </is>
       </c>
     </row>
@@ -6699,61 +6679,57 @@
       <c r="K114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>SF-REV-03</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
-        </is>
-      </c>
-      <c r="I115" s="4" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K115" s="4" t="inlineStr">
-        <is>
-          <t>enable Require Review; Details step collects mileage + engine hours (VIN captured later by reviewer).</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -6808,7 +6784,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>a deliverable PO in the review flow (Receive Parts routes to the shared receive page).</t>
+          <t>BATCH 6: deliverable WO PO achievable in the review flow, but receiving it is blocked by BUG-11 (500).</t>
         </is>
       </c>
     </row>
@@ -6919,61 +6895,57 @@
       <c r="K118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>SF-REV-07</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G119" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
-        </is>
-      </c>
-      <c r="I119" s="4" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K119" s="4" t="inlineStr">
-        <is>
-          <t>enable Require Review; Send to Review locks lines to Complete + auto-picks inventory.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -7245,61 +7217,57 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>SF-REV-13</t>
         </is>
       </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G125" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
-        </is>
-      </c>
-      <c r="I125" s="4" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K125" s="4" t="inlineStr">
-        <is>
-          <t>enable Require Review; all lines must be approved to Send to Review (approve-line error).</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -7354,7 +7322,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>cores + receiving in the review flow (cores resolved before sign-off; invoicing blocked until Reviewed + cores resolved).</t>
+          <t>cores + receiving in the review flow — blocked by BUG-10 (no wizard resolve step) + BUG-11 (WO-PO receive 500) + special-order cores not seedable.</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8227,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>an asset/vehicle with NO VIN so the non-review wizard prompts for VIN (VIN is currently prefilled from the asset, so the gate is not reachable with existing assets).</t>
+          <t>an asset/vehicle with NO VIN so the non-review wizard prompts for VIN. BATCH 6: VIN prefills from the asset; the asset-creation flow (VIN likely required) was not reliably drivable in-harness. Needs a VIN-less asset seeded.</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8390,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>a required-invoice receive attempt without an invoice number (receivable PO).</t>
+          <t>BATCH 6: blocked by BUG-11 (WO-PO receive 500) — cannot complete a required-invoice receive to test the no-invoice-number negative.</t>
         </is>
       </c>
     </row>
@@ -8479,66 +8447,62 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>a vendor-missing part receive attempt (deliverable state).</t>
+          <t>BATCH 6: blocked by BUG-11 (WO-PO receive 500) and no assign-vendor UI on the reachable receive surface.</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-07</t>
         </is>
       </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
-      <c r="D148" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G148" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I148" s="4" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K148" s="4" t="inlineStr">
-        <is>
-          <t>review flow; Confirm Review disabled until VIN entered in Mark Reviewed dialog.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9273,7 +9237,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9303,7 +9267,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9443,7 +9407,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
@@ -9458,7 +9422,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
@@ -9488,7 +9452,7 @@
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C23" s="8" t="inlineStr"/>
     </row>
@@ -9579,7 +9543,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 52 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 43 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K160"/>
+  <dimension ref="A1:K163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Open-Question</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Open-Question</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Open-Question</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1948,57 +1948,61 @@
       <c r="K27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>SF-COMP-12</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Verify the optional-invoice modal creates POs in the background and shows the count of parts to receive</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>S3-R1 / S3-R2 / S3-R9</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2592,61 +2596,57 @@
       <c r="K39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-01</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Verify inventory cores are gated in the completion modal after Pick with Ok/Not OK per core</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>S3-C1 / S4-C1 / Resolve Cores handoff</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>an inventory/catalog part flagged is_core (genuine core) + a received cored line; the manual sub-form only sets core_charge (is_core stays false) and resolve-cores needs receiving.</t>
-        </is>
-      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
+          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -3105,61 +3105,57 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-10</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Core parts — Resolve step UI</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>Resolve Cores handoff (live +$ total)</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>the Resolve-Cores step live '+$ to invoice' total (needs is_core part + receiving).</t>
-        </is>
-      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3586,110 +3582,118 @@
       <c r="K57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>SF-VPART-01</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>Verify a part can be requested with only description, quantity and sell price (part number, cost, vendor empty)</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: seed + drive the vendorless / no-PN part add flow.</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>S5-R1</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>SF-VPART-02</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>Verify adding a part is blocked when description, quantity or sell price is missing</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: drive the vendorless / no-PN add sub-form validation (not reached in the last session's budget).</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>S5-R1 / S5 AC (validation)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr"/>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4295,62 +4299,66 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>SF-POSEL-01</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>PO Multi-Select (Story 7)</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>SF-VMIS-07</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Vendor Missing on WO PO (Story 6)</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 7 — PO multi-select (SV-7702); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>Story 7 — PO multi-select (SV-7702) | S7-R1</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="5" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>S6-R7</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -4360,7 +4368,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -4390,7 +4398,7 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Story 7 — PO multi-select (SV-7702) | S7-R2</t>
+          <t>Story 7 — PO multi-select (SV-7702) | S7-R1</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
@@ -4403,7 +4411,7 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -4413,7 +4421,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -4443,7 +4451,7 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Story 7 — PO multi-select (SV-7702) | S7-R3</t>
+          <t>Story 7 — PO multi-select (SV-7702) | S7-R2</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
@@ -4456,7 +4464,7 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -4466,7 +4474,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -4496,7 +4504,7 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Story 7 — PO multi-select (SV-7702) | S7-R4</t>
+          <t>Story 7 — PO multi-select (SV-7702) | S7-R3</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
@@ -4509,7 +4517,7 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -4519,7 +4527,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -4549,7 +4557,7 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Story 7 — PO multi-select (SV-7702) | S7-R5</t>
+          <t>Story 7 — PO multi-select (SV-7702) | S7-R4</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
@@ -4562,7 +4570,7 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -4572,7 +4580,7 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -4602,7 +4610,7 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Story 7 — PO multi-select (SV-7702) | S7 (select-all scope)</t>
+          <t>Story 7 — PO multi-select (SV-7702) | S7-R5</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
@@ -4615,17 +4623,17 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -4650,12 +4658,12 @@
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
+          <t>Dev deploys Story 7 — PO multi-select (SV-7702); then QA re-runs VIU.</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R1</t>
+          <t>Story 7 — PO multi-select (SV-7702) | S7 (select-all scope)</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
@@ -4668,7 +4676,7 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -4678,7 +4686,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -4708,7 +4716,7 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R2 / S8-R3</t>
+          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R1</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
@@ -4721,7 +4729,7 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -4731,7 +4739,7 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -4761,7 +4769,7 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R4</t>
+          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R2 / S8-R3</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
@@ -4774,7 +4782,7 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -4784,7 +4792,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -4814,7 +4822,7 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R5</t>
+          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R4</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
@@ -4827,7 +4835,7 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -4837,7 +4845,7 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -4867,7 +4875,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R6</t>
+          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R5</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
@@ -4880,7 +4888,7 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -4890,7 +4898,7 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -4920,7 +4928,7 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R7 / S10-R2</t>
+          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R6</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
@@ -4933,7 +4941,7 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -4943,7 +4951,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -4973,7 +4981,7 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R8</t>
+          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R7 / S10-R2</t>
         </is>
       </c>
       <c r="J83" s="5" t="inlineStr">
@@ -4986,7 +4994,7 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -4996,7 +5004,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -5026,7 +5034,7 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R10</t>
+          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R8</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
@@ -5039,7 +5047,7 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -5049,7 +5057,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -5079,7 +5087,7 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R11</t>
+          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R10</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
@@ -5092,7 +5100,7 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -5102,7 +5110,7 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -5132,7 +5140,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-C1 / S8-C2</t>
+          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R11</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
@@ -5145,17 +5153,17 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -5180,12 +5188,12 @@
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>Dev deploys Story 9 — Apply invoice to selected POs (SV-7704); then QA re-runs VIU.</t>
+          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Story 9 — Apply invoice to selected POs (SV-7704) | S9-R1</t>
+          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-C1 / S8-C2</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
@@ -5198,7 +5206,7 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -5208,7 +5216,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -5238,7 +5246,7 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Story 9 — Apply invoice to selected POs (SV-7704) | S9-R2</t>
+          <t>Story 9 — Apply invoice to selected POs (SV-7704) | S9-R1</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
@@ -5251,117 +5259,113 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
+          <t>SF-INV-02</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>DEV NOT BUILT</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Dev team</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>Dev deploys Story 9 — Apply invoice to selected POs (SV-7704); then QA re-runs VIU.</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Story 9 — Apply invoice to selected POs (SV-7704) | S9-R2</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
           <t>SF-INV-03</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="F90" s="5" t="inlineStr">
         <is>
           <t>DEV NOT BUILT</t>
         </is>
       </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>Dev team</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H90" s="5" t="inlineStr">
         <is>
           <t>Dev deploys Story 9 — Apply invoice to selected POs (SV-7704); then QA re-runs VIU.</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I90" s="5" t="inlineStr">
         <is>
           <t>Story 9 — Apply invoice to selected POs (SV-7704) | S9-R3</t>
         </is>
       </c>
-      <c r="J89" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K89" s="5" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>SF-PNFIX-01</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
-        </is>
-      </c>
-      <c r="I90" s="4" t="inlineStr">
-        <is>
-          <t>S10-R1</t>
-        </is>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K90" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: no inline Missing-part-number Edit on the vendor-missing PO Accept Delivery (empty PN cell, no edit control). Inline PN-fix appears tied to the Bulk Receive page (Story 8, NOT built).</t>
-        </is>
-      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -5371,7 +5375,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -5401,7 +5405,7 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>S10 AC (new number)</t>
+          <t>S10-R1</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -5411,14 +5415,14 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>receiving + inventory/catalog inspection (new PN creates inventory part + stock + Part History on receive).</t>
+          <t>BATCH 6: no inline Missing-part-number Edit on the vendor-missing PO Accept Delivery (empty PN cell, no edit control). Inline PN-fix appears tied to the Bulk Receive page (Story 8, NOT built).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5428,7 +5432,7 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -5458,7 +5462,7 @@
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>S10 AC (existing number)</t>
+          <t>S10 AC (new number)</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
@@ -5468,14 +5472,14 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>receiving + inventory inspection (existing PN links to item, updates stock/cost/history).</t>
+          <t>receiving + inventory/catalog inspection (new PN creates inventory part + stock + Part History on receive).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -5485,7 +5489,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -5515,7 +5519,7 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>S10-R2 / S8-R7</t>
+          <t>S10 AC (existing number)</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -5525,14 +5529,14 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>a WO in invoiced/paid state (sell-field locking).</t>
+          <t>receiving + inventory inspection (existing PN links to item, updates stock/cost/history).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -5542,7 +5546,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -5572,7 +5576,7 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>S10 Negative</t>
+          <t>S10-R2 / S8-R7</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -5582,124 +5586,128 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>an invoiced/paid WO + a receive attempt (cannot receive without PN).</t>
+          <t>a WO in invoiced/paid state (sell-field locking).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
+          <t>SF-PNFIX-05</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Inline Part-Number Fix (Story 10)</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>S10 Negative</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>an invoiced/paid WO + a receive attempt (cannot receive without PN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
           <t>SF-PNFIX-06</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G95" s="4" t="inlineStr">
+      <c r="G96" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H95" s="4" t="inlineStr">
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr">
+      <c r="I96" s="4" t="inlineStr">
         <is>
           <t>S10 Technical guardrails</t>
         </is>
       </c>
-      <c r="J95" s="4" t="inlineStr">
+      <c r="J96" s="4" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="K95" s="4" t="inlineStr">
+      <c r="K96" s="4" t="inlineStr">
         <is>
           <t>receiving + catalog/inventory back-end inspection (real creation/linking, not a stored string).</t>
         </is>
       </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>SF-RCV-01</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Receive Button on WO POs (Story 11)</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>S11-R1</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-RCV-01</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5709,7 +5717,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5739,7 +5747,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>S11-R2</t>
+          <t>S11-R1</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -5752,7 +5760,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>SF-RCV-03</t>
+          <t>SF-RCV-02</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5762,7 +5770,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
+          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5792,7 +5800,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>S11-R3</t>
+          <t>S11-R2</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -5805,400 +5813,396 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>SF-RCV-03</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Receive Button on WO POs (Story 11)</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>S11-R3</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
           <t>SF-RCV-04</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>None — VIU-verified; uploadable now.</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>S12 (existing multi-vendor)</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>SF-RCV-05</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>MILOS ANSWER</t>
         </is>
       </c>
-      <c r="G100" s="3" t="inlineStr">
+      <c r="G101" s="3" t="inlineStr">
         <is>
           <t>Milos (Product Owner)</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
+      <c r="H101" s="3" t="inlineStr">
         <is>
           <t>Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
         </is>
       </c>
-      <c r="I100" s="3" t="inlineStr">
+      <c r="I101" s="3" t="inlineStr">
         <is>
           <t>Q11 | S12-R1</t>
         </is>
       </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>SF-RCV-06</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D102" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G101" s="4" t="inlineStr">
+      <c r="G102" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr">
+      <c r="H102" s="4" t="inlineStr">
         <is>
           <t>QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
         </is>
       </c>
-      <c r="I101" s="4" t="inlineStr">
+      <c r="I102" s="4" t="inlineStr">
         <is>
           <t>S12-R2</t>
         </is>
       </c>
-      <c r="J101" s="4" t="inlineStr">
+      <c r="J102" s="4" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="K101" s="4" t="inlineStr">
+      <c r="K102" s="4" t="inlineStr">
         <is>
           <t>BATCH 6: on a deliverable WO PO the Accept Delivery gates are present (vendor set, invoice # field), but Receive 500s (BUG-11); on a vendor-missing WO PO there is no assign-vendor / PN-edit control. Happy path was proven on an INVENTORY PO in BATCH 5; the WO-PO negative sub-gates need BUG-11 fixed.</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>SF-RCV-07</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>MILOS ANSWER</t>
         </is>
       </c>
-      <c r="G102" s="3" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t>Milos (Product Owner)</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t>Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t>Q11 | S12-R3</t>
         </is>
       </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>SF-RCV-08</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D104" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="E104" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="G104" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr">
+      <c r="H104" s="4" t="inlineStr">
         <is>
           <t>QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
         </is>
       </c>
-      <c r="I103" s="4" t="inlineStr">
+      <c r="I104" s="4" t="inlineStr">
         <is>
           <t>S12-R4</t>
         </is>
       </c>
-      <c r="J103" s="4" t="inlineStr">
+      <c r="J104" s="4" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="K103" s="4" t="inlineStr">
+      <c r="K104" s="4" t="inlineStr">
         <is>
           <t>QuickBooks inspection (per-vendor vendor bill + separate AP entry) — and WO-PO receive additionally blocked by BUG-11 (500).</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>SF-RCV-09</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>None — VIU-verified; uploadable now.</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr">
         <is>
           <t>S12 (existing) received-more-than-ordered</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>SF-VEND-01</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
-        </is>
-      </c>
-      <c r="I105" s="4" t="inlineStr">
-        <is>
-          <t>S13-R1</t>
-        </is>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K105" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: vendor-missing WO PO seeded, but no PO-level vendor dropdown on any reachable surface (PO list/accept-delivery/deliveries). The vendor-missing-group vendor dropdown appears to live on the Bulk Receive page (Story 8/13 UI, NOT built).</t>
-        </is>
-      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-RCV-10</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -6223,29 +6227,29 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+          <t>QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>S13-R2</t>
-        </is>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
+          <t>S12-R5</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>a PO where the assigned vendor already exists on the PO (Add-to-vendor merge vs keep-separate prompt).</t>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -6255,7 +6259,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -6285,7 +6289,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>S13-R3</t>
+          <t>S13-R1</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -6295,14 +6299,14 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>two POs for the same WO with the same vendor (merge-POs prompt).</t>
+          <t>BATCH 6: vendor-missing WO PO seeded, but no PO-level vendor dropdown on any reachable surface (PO list/accept-delivery/deliveries). The vendor-missing-group vendor dropdown appears to live on the Bulk Receive page (Story 8/13 UI, NOT built).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -6312,7 +6316,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -6342,7 +6346,7 @@
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>S13-R4 / S13-R5</t>
+          <t>S13-R2</t>
         </is>
       </c>
       <c r="J108" s="4" t="inlineStr">
@@ -6352,336 +6356,344 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>a vendor-missing PO + receive-enable + QB-flag-clear check after auto-assign.</t>
+          <t>a PO where the assigned vendor already exists on the PO (Add-to-vendor merge vs keep-separate prompt).</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
+          <t>SF-VEND-03</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Assign Vendor + Merge (Story 13)</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>S13-R3</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>two POs for the same WO with the same vendor (merge-POs prompt).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>SF-VEND-04</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Assign Vendor + Merge (Story 13)</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>S13-R4 / S13-R5</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>a vendor-missing PO + receive-enable + QB-flag-clear check after auto-assign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
           <t>SF-VEND-05</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr">
         <is>
           <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D111" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="E111" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr">
+      <c r="F111" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G109" s="4" t="inlineStr">
+      <c r="G111" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H109" s="4" t="inlineStr">
+      <c r="H111" s="4" t="inlineStr">
         <is>
           <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
-      <c r="I109" s="4" t="inlineStr">
+      <c r="I111" s="4" t="inlineStr">
         <is>
           <t>S13 Technical guardrails</t>
         </is>
       </c>
-      <c r="J109" s="4" t="inlineStr">
+      <c r="J111" s="4" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="K109" s="4" t="inlineStr">
+      <c r="K111" s="4" t="inlineStr">
         <is>
           <t>invoiced/paid WO + multi-PO merge guardrail state (match-by-ID, merge scoped to same WO, receive blocked when invoiced/paid).</t>
         </is>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>SF-WOP-01</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>Waiting on Parts Column (Story 14)</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H110" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 14 — Waiting-on-Parts column (SV-7709); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I110" s="5" t="inlineStr">
-        <is>
-          <t>Story 14 — Waiting-on-Parts column (SV-7709) | S14-R1</t>
-        </is>
-      </c>
-      <c r="J110" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K110" s="5" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>SF-WOP-02</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>Waiting on Parts Column (Story 14)</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 14 — Waiting-on-Parts column (SV-7709); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I111" s="5" t="inlineStr">
-        <is>
-          <t>Story 14 — Waiting-on-Parts column (SV-7709) | S14-R2</t>
-        </is>
-      </c>
-      <c r="J111" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
+          <t>SF-WOP-01</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Waiting on Parts Column (Story 14)</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>DEV NOT BUILT</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>Dev team</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>Dev deploys Story 14 — Waiting-on-Parts column (SV-7709); then QA re-runs VIU.</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Story 14 — Waiting-on-Parts column (SV-7709) | S14-R1</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>SF-WOP-02</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Waiting on Parts Column (Story 14)</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>DEV NOT BUILT</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Dev team</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>Dev deploys Story 14 — Waiting-on-Parts column (SV-7709); then QA re-runs VIU.</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>Story 14 — Waiting-on-Parts column (SV-7709) | S14-R2</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
           <t>SF-WOP-03</t>
         </is>
       </c>
-      <c r="B112" s="5" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
         <is>
           <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E112" s="5" t="inlineStr">
+      <c r="E114" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr">
+      <c r="F114" s="5" t="inlineStr">
         <is>
           <t>DEV NOT BUILT</t>
         </is>
       </c>
-      <c r="G112" s="5" t="inlineStr">
+      <c r="G114" s="5" t="inlineStr">
         <is>
           <t>Dev team</t>
         </is>
       </c>
-      <c r="H112" s="5" t="inlineStr">
+      <c r="H114" s="5" t="inlineStr">
         <is>
           <t>Dev deploys Story 14 — Waiting-on-Parts column (SV-7709); then QA re-runs VIU.</t>
         </is>
       </c>
-      <c r="I112" s="5" t="inlineStr">
+      <c r="I114" s="5" t="inlineStr">
         <is>
           <t>Story 14 — Waiting-on-Parts column (SV-7709) | S14-R3</t>
         </is>
       </c>
-      <c r="J112" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K112" s="5" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>SF-REV-01</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Require Review setting drives the review flow when turned on</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>SF-REV-02</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr"/>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-REV-01</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -6691,7 +6703,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -6721,7 +6733,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -6732,66 +6744,62 @@
       <c r="K115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>SF-REV-04</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>SF-REV-02</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
-        </is>
-      </c>
-      <c r="D116" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
-        </is>
-      </c>
-      <c r="I116" s="4" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K116" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: deliverable WO PO achievable in the review flow, but receiving it is blocked by BUG-11 (500).</t>
-        </is>
-      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>SF-REV-05</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -6801,7 +6809,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -6831,7 +6839,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>R5 / R6</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -6842,653 +6850,657 @@
       <c r="K117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>SF-REV-06</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>SF-REV-04</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>R7 / R10</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr"/>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>BATCH 6: deliverable WO PO achievable in the review flow, but receiving it is blocked by BUG-11 (500).</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>SF-REV-05</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>R5 / R6</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>SF-REV-06</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>R7 / R10</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
           <t>SF-REV-07</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>None — VIU-verified; uploadable now.</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>SF-REV-08</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>Verify Confirm Review moves the WO to a distinct Reviewed state requiring a separate final Complete Work Order</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>MILOS ANSWER</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>Milos (Product Owner)</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
-        </is>
-      </c>
-      <c r="I120" s="3" t="inlineStr">
-        <is>
-          <t>Q8, Q4 | R5 / R8 (distinct Reviewed state)</t>
-        </is>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K120" s="3" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>SF-REV-09</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F121" s="6" t="inlineStr">
-        <is>
-          <t>BUG/RULING</t>
-        </is>
-      </c>
-      <c r="G121" s="6" t="inlineStr">
-        <is>
-          <t>Dev / PO ruling</t>
-        </is>
-      </c>
-      <c r="H121" s="6" t="inlineStr">
-        <is>
-          <t>Review role-gating expected depends on reviewer!=completer (missing) and the FE-vs-BE ruling.</t>
-        </is>
-      </c>
-      <c r="I121" s="6" t="inlineStr">
-        <is>
-          <t>R7 (role-gating) | see viu-findings BUGS #5/#6/#7</t>
-        </is>
-      </c>
-      <c r="J121" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K121" s="6" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
+          <t>SF-REV-08</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>MILOS ANSWER</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>Milos (Product Owner)</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>Q8, Q4 | R5 / R8 (distinct Reviewed state)</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>SF-REV-09</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>BUG/RULING</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>Dev / PO ruling</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>Review role-gating expected depends on reviewer!=completer (missing) and the FE-vs-BE ruling.</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>R7 (role-gating) | see viu-findings BUGS #5/#6/#7</t>
+        </is>
+      </c>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K123" s="6" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
           <t>SF-REV-10</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>Verify the Mark Reviewed dialog includes an optional review note field (input_review_note)</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Verify the Mark Reviewed dialog includes VIN (required) and an optional review note field (input_review_note)</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
         <is>
           <t>MILOS ANSWER</t>
         </is>
       </c>
-      <c r="G122" s="3" t="inlineStr">
+      <c r="G124" s="3" t="inlineStr">
         <is>
           <t>Milos (Product Owner)</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H124" s="3" t="inlineStr">
         <is>
           <t>Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
         </is>
       </c>
-      <c r="I122" s="3" t="inlineStr">
+      <c r="I124" s="3" t="inlineStr">
         <is>
           <t>Q7 | R7 / R10 (optional note)</t>
         </is>
       </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K122" s="3" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>SF-REV-11</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E123" s="3" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t>MILOS ANSWER</t>
         </is>
       </c>
-      <c r="G123" s="3" t="inlineStr">
+      <c r="G125" s="3" t="inlineStr">
         <is>
           <t>Milos (Product Owner)</t>
         </is>
       </c>
-      <c r="H123" s="3" t="inlineStr">
+      <c r="H125" s="3" t="inlineStr">
         <is>
           <t>Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
         </is>
       </c>
-      <c r="I123" s="3" t="inlineStr">
+      <c r="I125" s="3" t="inlineStr">
         <is>
           <t>Q8 | R8</t>
         </is>
       </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K123" s="3" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>SF-REV-12</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
-        </is>
-      </c>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G124" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
-        </is>
-      </c>
-      <c r="I124" s="4" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K124" s="4" t="inlineStr">
-        <is>
-          <t>enable Require Review; confirm a 'Ready for Review' list filter/column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>SF-REV-13</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>R11</t>
-        </is>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K125" s="2" t="inlineStr"/>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
+          <t>SF-REV-12</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
+        </is>
+      </c>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>enable Require Review; confirm a 'Ready for Review' list filter/column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>SF-REV-13</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
           <t>SF-REV-14</t>
         </is>
       </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
+      <c r="C128" s="4" t="inlineStr">
         <is>
           <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="D128" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="E128" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F126" s="4" t="inlineStr">
+      <c r="F128" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G126" s="4" t="inlineStr">
+      <c r="G128" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H126" s="4" t="inlineStr">
+      <c r="H128" s="4" t="inlineStr">
         <is>
           <t>QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
         </is>
       </c>
-      <c r="I126" s="4" t="inlineStr">
+      <c r="I128" s="4" t="inlineStr">
         <is>
           <t>R Core parts / invoicing block</t>
         </is>
       </c>
-      <c r="J126" s="4" t="inlineStr">
+      <c r="J128" s="4" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="K126" s="4" t="inlineStr">
+      <c r="K128" s="4" t="inlineStr">
         <is>
           <t>cores + receiving in the review flow — blocked by BUG-10 (no wizard resolve step) + BUG-11 (WO-PO receive 500) + special-order cores not seedable.</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t>SF-REV-15</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>Verify the Require Review default for new vs existing orgs matches the agreed cohort rule</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>Open-Question</t>
         </is>
       </c>
-      <c r="E127" s="3" t="inlineStr">
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr">
         <is>
           <t>MILOS ANSWER</t>
         </is>
       </c>
-      <c r="G127" s="3" t="inlineStr">
+      <c r="G129" s="3" t="inlineStr">
         <is>
           <t>Milos (Product Owner)</t>
         </is>
       </c>
-      <c r="H127" s="3" t="inlineStr">
+      <c r="H129" s="3" t="inlineStr">
         <is>
           <t>Milos answers Open Question Q1 — Require-review default cohort rule + new-org preset.</t>
         </is>
       </c>
-      <c r="I127" s="3" t="inlineStr">
+      <c r="I129" s="3" t="inlineStr">
         <is>
           <t>Q1 | R Open (default)</t>
         </is>
       </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K127" s="3" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>SF-UX-01</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>UX Refinements (Story 15)</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Verify the work order primary button reads 'Create Work Order'</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>S15-R1</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>SF-UX-02</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>UX Refinements (Story 15)</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>S15-R2</t>
-        </is>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K129" s="2" t="inlineStr"/>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>SF-UX-03</t>
+          <t>SF-UX-01</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -7498,7 +7510,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
+          <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -7528,7 +7540,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>S15-R3</t>
+          <t>S15-R1</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -7539,221 +7551,221 @@
       <c r="K130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>SF-UX-04</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>SF-UX-02</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t>MILOS ANSWER</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="inlineStr">
-        <is>
-          <t>Milos (Product Owner)</t>
-        </is>
-      </c>
-      <c r="H131" s="3" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
-        </is>
-      </c>
-      <c r="I131" s="3" t="inlineStr">
-        <is>
-          <t>Q10 | S15-R4</t>
-        </is>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K131" s="3" t="inlineStr"/>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>S15-R2</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>SF-UX-03</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>UX Refinements (Story 15)</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>S15-R3</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>SF-UX-04</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>UX Refinements (Story 15)</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>MILOS ANSWER</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>Milos (Product Owner)</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>Q10 | S15-R4</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
           <t>SF-PERM-01</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>API — Permissions</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>None — VIU-verified; uploadable now.</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>S1 AC / §8 Permissions</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>SF-PERM-02</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>Verify which roles can complete a work order (Simple completion)</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F133" s="6" t="inlineStr">
-        <is>
-          <t>BUG/RULING</t>
-        </is>
-      </c>
-      <c r="G133" s="6" t="inlineStr">
-        <is>
-          <t>Dev / PO ruling</t>
-        </is>
-      </c>
-      <c r="H133" s="6" t="inlineStr">
-        <is>
-          <t>WO-completion role-gating is FE-only (button hidden for Tech, but BE allows it). Verdict depends on the same FE-vs-BE ruling as SF-PERM-06.</t>
-        </is>
-      </c>
-      <c r="I133" s="6" t="inlineStr">
-        <is>
-          <t>§8 Permissions | see viu-findings BUGS #5/#6/#7</t>
-        </is>
-      </c>
-      <c r="J133" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K133" s="6" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>SF-PERM-03</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>Verify which roles can perform Bulk Receive</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H134" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I134" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | §8 Permissions</t>
-        </is>
-      </c>
-      <c r="J134" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K134" s="5" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>SF-PERM-04</t>
+          <t>SF-PERM-02</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
@@ -7763,7 +7775,7 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Verify which roles can Mark Reviewed (sign off)</t>
+          <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -7788,12 +7800,12 @@
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
-          <t>Role-gating of Mark-Reviewed depends on reviewer!=completer (missing) and the FE-vs-BE ruling.</t>
+          <t>WO-completion role-gating is FE-only (button hidden for Tech, but BE allows it). Verdict depends on the same FE-vs-BE ruling as SF-PERM-06.</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>R7 / §8 role-gating review | see viu-findings BUGS #5/#6/#7</t>
+          <t>§8 Permissions | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
@@ -7804,72 +7816,72 @@
       <c r="K135" s="6" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>SF-PERM-05</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>SF-PERM-03</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Verify the PO Receive button is hidden for office/readonly users</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>S11-R3</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K136" s="2" t="inlineStr"/>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Verify which roles can perform Bulk Receive</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>DEV NOT BUILT</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>Dev team</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>Story 8 — PO Bulk Receive page (SV-7703) | §8 Permissions</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>SF-PERM-06</t>
+          <t>SF-PERM-04</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>API — Permissions</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Verify the backend enforces the Simple-Flow settings and permission atoms (not front-end only)</t>
+          <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
@@ -7894,12 +7906,12 @@
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
-          <t>WO completion permission is FE-only at the BE (Technician completed via simple-complete API = 201). Ruling: SV-8183 says 'BE enforces' but SV-7864 atom-collapse lets any WO C&amp;E role act. Which governs?</t>
+          <t>Role-gating of Mark-Reviewed depends on reviewer!=completer (missing) and the FE-vs-BE ruling.</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>§8 BE enforcement | see viu-findings BUGS #5/#6/#7</t>
+          <t>R7 / §8 role-gating review | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
@@ -7910,231 +7922,231 @@
       <c r="K137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>SF-PERM-07</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>SF-PERM-05</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Verify the PO Receive button is hidden for office/readonly users</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F138" s="6" t="inlineStr">
-        <is>
-          <t>BUG/RULING</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>Dev / PO ruling</t>
-        </is>
-      </c>
-      <c r="H138" s="6" t="inlineStr">
-        <is>
-          <t>Review sign-off permission (woReviewWorkOrders) is FE-only at the BE (Technician drove change-status = 201). Same FE-vs-BE ruling.</t>
-        </is>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>§8 role-gating review | see viu-findings BUGS #5/#6/#7</t>
-        </is>
-      </c>
-      <c r="J138" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K138" s="6" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>S11-R3</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
+          <t>SF-PERM-06</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>API — Permissions</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>Verify the backend enforces the Simple-Flow settings and permission atoms (not front-end only)</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>BUG/RULING</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>Dev / PO ruling</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>WO completion permission is FE-only at the BE (Technician completed via simple-complete API = 201). Ruling: SV-8183 says 'BE enforces' but SV-7864 atom-collapse lets any WO C&amp;E role act. Which governs?</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>§8 BE enforcement | see viu-findings BUGS #5/#6/#7</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K139" s="6" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>SF-PERM-07</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>BUG/RULING</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>Dev / PO ruling</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>Review sign-off permission (woReviewWorkOrders) is FE-only at the BE (Technician drove change-status = 201). Same FE-vs-BE ruling.</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>§8 role-gating review | see viu-findings BUGS #5/#6/#7</t>
+        </is>
+      </c>
+      <c r="J140" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K140" s="6" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
           <t>SF-PERM-08</t>
         </is>
       </c>
-      <c r="B139" s="6" t="inlineStr">
+      <c r="B141" s="6" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr">
+      <c r="C141" s="6" t="inlineStr">
         <is>
           <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
+      <c r="D141" s="6" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="E141" s="6" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F139" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <t>BUG/RULING</t>
         </is>
       </c>
-      <c r="G139" s="6" t="inlineStr">
+      <c r="G141" s="6" t="inlineStr">
         <is>
           <t>Dev / PO ruling</t>
         </is>
       </c>
-      <c r="H139" s="6" t="inlineStr">
+      <c r="H141" s="6" t="inlineStr">
         <is>
           <t>reviewer != completer rule NOT implemented (a user can sign off their own WO). Ruling: enforce the rule (currently FAIL) or descope?</t>
         </is>
       </c>
-      <c r="I139" s="6" t="inlineStr">
+      <c r="I141" s="6" t="inlineStr">
         <is>
           <t>R7 (reviewer != completer) | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
-      <c r="J139" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K139" s="6" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>SF-PERM-09</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>S5 / §9 (See Financial Data gate)</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>SF-PERM-10</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>§9 per-role completion matrix</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K141" s="2" t="inlineStr"/>
+      <c r="J141" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K141" s="6" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>SF-VAL-01</t>
+          <t>SF-PERM-09</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required mileage is missing</t>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -8164,7 +8176,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>S2-R2 / S3-R3 / S4-R3</t>
+          <t>S5 / §9 (See Financial Data gate)</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -8175,771 +8187,763 @@
       <c r="K142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>SF-VAL-02</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr">
-        <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G143" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I143" s="4" t="inlineStr">
-        <is>
-          <t>S15-R2 / S3-R3</t>
-        </is>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K143" s="4" t="inlineStr">
-        <is>
-          <t>an asset/vehicle with NO VIN so the non-review wizard prompts for VIN. BATCH 6: VIN prefills from the asset; the asset-creation flow (VIN likely required) was not reliably drivable in-harness. Needs a VIN-less asset seeded.</t>
-        </is>
-      </c>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>SF-PERM-10</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>§9 per-role completion matrix</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>SF-VAL-01</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Verify completion is blocked when required mileage is missing</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>S2-R2 / S3-R3 / S4-R3</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>SF-VAL-02</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>S15-R2 / S3-R3</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>an asset/vehicle with NO VIN so the non-review wizard prompts for VIN. BATCH 6: VIN prefills from the asset; the asset-creation flow (VIN likely required) was not reliably drivable in-harness. Needs a VIN-less asset seeded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
           <t>SF-VAL-03</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>None — VIU-verified; uploadable now.</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr">
         <is>
           <t>S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-04</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>None — VIU-verified; uploadable now.</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>TS-R4</t>
         </is>
       </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="4" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>SF-VAL-05</t>
         </is>
       </c>
-      <c r="B146" s="4" t="inlineStr">
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C146" s="4" t="inlineStr">
+      <c r="C148" s="4" t="inlineStr">
         <is>
           <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="D148" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
+      <c r="E148" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr">
+      <c r="F148" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G146" s="4" t="inlineStr">
+      <c r="G148" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H146" s="4" t="inlineStr">
+      <c r="H148" s="4" t="inlineStr">
         <is>
           <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
-      <c r="I146" s="4" t="inlineStr">
+      <c r="I148" s="4" t="inlineStr">
         <is>
           <t>S3-R3 / S4-R5 / §4</t>
         </is>
       </c>
-      <c r="J146" s="4" t="inlineStr">
+      <c r="J148" s="4" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="K146" s="4" t="inlineStr">
+      <c r="K148" s="4" t="inlineStr">
         <is>
           <t>BATCH 6: blocked by BUG-11 (WO-PO receive 500) — cannot complete a required-invoice receive to test the no-invoice-number negative.</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="4" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t>SF-VAL-06</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="B149" s="4" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C149" s="4" t="inlineStr">
         <is>
           <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="D149" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
+      <c r="E149" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr">
+      <c r="F149" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G147" s="4" t="inlineStr">
+      <c r="G149" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H147" s="4" t="inlineStr">
+      <c r="H149" s="4" t="inlineStr">
         <is>
           <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
-      <c r="I147" s="4" t="inlineStr">
+      <c r="I149" s="4" t="inlineStr">
         <is>
           <t>S10 / S12-R2 / S13</t>
         </is>
       </c>
-      <c r="J147" s="4" t="inlineStr">
+      <c r="J149" s="4" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="K147" s="4" t="inlineStr">
+      <c r="K149" s="4" t="inlineStr">
         <is>
           <t>BATCH 6: blocked by BUG-11 (WO-PO receive 500) and no assign-vendor UI on the reachable receive surface.</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-07</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>None — VIU-verified; uploadable now.</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-08</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>None — VIU-verified; uploadable now.</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>S3-R9 (idempotency)</t>
         </is>
       </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="5" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
         <is>
           <t>SF-VAL-09</t>
         </is>
       </c>
-      <c r="B150" s="5" t="inlineStr">
+      <c r="B152" s="5" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C150" s="5" t="inlineStr">
+      <c r="C152" s="5" t="inlineStr">
         <is>
           <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
-      <c r="D150" s="5" t="inlineStr">
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E150" s="5" t="inlineStr">
+      <c r="E152" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F150" s="5" t="inlineStr">
+      <c r="F152" s="5" t="inlineStr">
         <is>
           <t>DEV NOT BUILT</t>
         </is>
       </c>
-      <c r="G150" s="5" t="inlineStr">
+      <c r="G152" s="5" t="inlineStr">
         <is>
           <t>Dev team</t>
         </is>
       </c>
-      <c r="H150" s="5" t="inlineStr">
+      <c r="H152" s="5" t="inlineStr">
         <is>
           <t>Dev deploys Story 8 — Bulk Receive field locking (S8-R7, SV-7703); then QA re-runs VIU.</t>
         </is>
       </c>
-      <c r="I150" s="5" t="inlineStr">
+      <c r="I152" s="5" t="inlineStr">
         <is>
           <t>Story 8 — Bulk Receive field locking (S8-R7, SV-7703) | S8-R7 / §4 field locking</t>
         </is>
       </c>
-      <c r="J150" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K150" s="5" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="5" t="inlineStr">
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t>SF-VAL-10</t>
         </is>
       </c>
-      <c r="B151" s="5" t="inlineStr">
+      <c r="B153" s="5" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C151" s="5" t="inlineStr">
+      <c r="C153" s="5" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="D151" s="5" t="inlineStr">
+      <c r="D153" s="5" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E151" s="5" t="inlineStr">
+      <c r="E153" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F151" s="5" t="inlineStr">
+      <c r="F153" s="5" t="inlineStr">
         <is>
           <t>DEV NOT BUILT</t>
         </is>
       </c>
-      <c r="G151" s="5" t="inlineStr">
+      <c r="G153" s="5" t="inlineStr">
         <is>
           <t>Dev team</t>
         </is>
       </c>
-      <c r="H151" s="5" t="inlineStr">
+      <c r="H153" s="5" t="inlineStr">
         <is>
           <t>Dev deploys Story 9 — Apply-invoice uniqueness (S9-R3, SV-7704); then QA re-runs VIU.</t>
         </is>
       </c>
-      <c r="I151" s="5" t="inlineStr">
+      <c r="I153" s="5" t="inlineStr">
         <is>
           <t>Story 9 — Apply-invoice uniqueness (S9-R3, SV-7704) | S9-R3 / §4 (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="J151" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K151" s="5" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-11</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>Verify the approve-line error text appears when completing with an unapproved line</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>VIU-Verified</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>None — VIU-verified; uploadable now.</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
         <is>
           <t>Key Decision (line approval)</t>
         </is>
       </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
         <is>
           <t>SF-QB-01</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr">
+      <c r="B155" s="3" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>MILOS ANSWER</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>Milos (Product Owner)</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>Milos answers Open Question Q2 — Inventory decrement / Part History on skip-path completion.</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>Q2 | §5 invariant 1</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>SF-QB-02</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>Open-Question</t>
         </is>
       </c>
-      <c r="E153" s="3" t="inlineStr">
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F153" s="3" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr">
         <is>
           <t>MILOS ANSWER</t>
         </is>
       </c>
-      <c r="G153" s="3" t="inlineStr">
+      <c r="G156" s="3" t="inlineStr">
         <is>
           <t>Milos (Product Owner)</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q2 — Inventory decrement / Part History on skip-path completion.</t>
-        </is>
-      </c>
-      <c r="I153" s="3" t="inlineStr">
-        <is>
-          <t>Q2 | §5 invariant 1</t>
-        </is>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K153" s="3" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>SF-QB-02</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t>MILOS ANSWER</t>
-        </is>
-      </c>
-      <c r="G154" s="3" t="inlineStr">
-        <is>
-          <t>Milos (Product Owner)</t>
-        </is>
-      </c>
-      <c r="H154" s="3" t="inlineStr">
+      <c r="H156" s="3" t="inlineStr">
         <is>
           <t>Milos answers Open Question Q5 — QuickBooks integrity when Create-POs is OFF (toggle absent).</t>
         </is>
       </c>
-      <c r="I154" s="3" t="inlineStr">
+      <c r="I156" s="3" t="inlineStr">
         <is>
           <t>Q5 | §5 / §4 (Create POs OFF)</t>
         </is>
       </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K154" s="3" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>SF-QB-03</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I155" s="4" t="inlineStr">
-        <is>
-          <t>§5 invariant 2</t>
-        </is>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K155" s="4" t="inlineStr">
-        <is>
-          <t>QuickBooks / inventory back-end inspection (receive -&gt; Delivery -&gt; Vendor Bill -&gt; QBO) — likely needs dev/QB access.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="4" t="inlineStr">
-        <is>
-          <t>SF-QB-04</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I156" s="4" t="inlineStr">
-        <is>
-          <t>§5 (vendorless/no-PN)</t>
-        </is>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K156" s="4" t="inlineStr">
-        <is>
-          <t>QuickBooks / inventory inspection (vendorless/no-PN part = zero inventory interaction) — likely needs dev/QB access.</t>
-        </is>
-      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-05</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -8949,7 +8953,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -8979,7 +8983,7 @@
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>§5 / S6-R3</t>
+          <t>§5 invariant 2</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -8989,14 +8993,14 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>QuickBooks inspection (Vendor-Missing POs excluded from QB until vendor + PN) — likely needs dev/QB access.</t>
+          <t>QuickBooks / inventory back-end inspection (receive -&gt; Delivery -&gt; Vendor Bill -&gt; QBO) — likely needs dev/QB access.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-06</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -9006,7 +9010,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -9036,7 +9040,7 @@
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>§8 (cost at completion)</t>
+          <t>§5 (vendorless/no-PN)</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
@@ -9046,14 +9050,14 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>QuickBooks inspection (cost-at-completion to avoid $0-cost margins) — likely needs dev/QB access.</t>
+          <t>QuickBooks / inventory inspection (vendorless/no-PN part = zero inventory interaction) — likely needs dev/QB access.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-07</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -9063,7 +9067,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -9093,7 +9097,7 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>§5 (Journal Entry / Inventory → QBO)</t>
+          <t>§5 / S6-R3</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -9103,64 +9107,235 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>QuickBooks inspection (Journal Entry / Inventory sync fires on invoice creation) — likely needs dev/QB access.</t>
+          <t>QuickBooks inspection (Vendor-Missing POs excluded from QB until vendor + PN) — likely needs dev/QB access.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
+          <t>SF-QB-06</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>§8 (cost at completion)</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks inspection (cost-at-completion to avoid $0-cost margins) — likely needs dev/QB access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>SF-QB-07</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>§5 (Journal Entry / Inventory → QBO)</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks inspection (Journal Entry / Inventory sync fires on invoice creation) — likely needs dev/QB access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
           <t>SF-QB-08</t>
         </is>
       </c>
-      <c r="B160" s="4" t="inlineStr">
+      <c r="B162" s="4" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C160" s="4" t="inlineStr">
+      <c r="C162" s="4" t="inlineStr">
         <is>
           <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr">
+      <c r="D162" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E160" s="4" t="inlineStr">
+      <c r="E162" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F160" s="4" t="inlineStr">
+      <c r="F162" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G160" s="4" t="inlineStr">
+      <c r="G162" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H160" s="4" t="inlineStr">
+      <c r="H162" s="4" t="inlineStr">
         <is>
           <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
-      <c r="I160" s="4" t="inlineStr">
+      <c r="I162" s="4" t="inlineStr">
         <is>
           <t>§5 invariant 3</t>
         </is>
       </c>
-      <c r="J160" s="4" t="inlineStr">
+      <c r="J162" s="4" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="K160" s="4" t="inlineStr">
+      <c r="K162" s="4" t="inlineStr">
         <is>
           <t>Inventory Part History inspection for any part that becomes inventory-tracked — likely needs dev/QB access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>SF-QB-09</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>Investigate: Part Sales unaffected by the shared order/status logic (requested -&gt; orderable/waiting-to-receive)</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>Open-Question</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>§8 open question (Part Sales impact — BE investigation)</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
         </is>
       </c>
     </row>
@@ -9204,7 +9379,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C3" s="8" t="n"/>
     </row>
@@ -9237,7 +9412,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9267,7 +9442,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9312,7 +9487,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C11" s="8" t="inlineStr"/>
     </row>
@@ -9407,7 +9582,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
@@ -9422,7 +9597,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
@@ -9452,7 +9627,7 @@
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C23" s="8" t="inlineStr"/>
     </row>
@@ -9543,7 +9718,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 43 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 47 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Open-Question</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3582,118 +3582,110 @@
       <c r="K57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>SF-VPART-01</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Verify a part can be requested with only description, quantity and sell price (part number, cost, vendor empty)</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed + drive the vendorless / no-PN part add flow.</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>S5-R1</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>SF-VPART-02</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Verify adding a part is blocked when description, quantity or sell price is missing</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the vendorless / no-PN add sub-form validation (not reached in the last session's budget).</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>S5-R1 / S5 AC (validation)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -7184,12 +7176,12 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog includes VIN (required) and an optional review note field (input_review_note)</t>
+          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
@@ -7214,7 +7206,7 @@
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>Q7 | R7 / R10 (optional note)</t>
+          <t>Q7 | R7 (VIN required, no note)</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
@@ -7987,7 +7979,7 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Verify the backend enforces the Simple-Flow settings and permission atoms (not front-end only)</t>
+          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -9412,7 +9404,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9442,7 +9434,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9582,7 +9574,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
@@ -9627,7 +9619,7 @@
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C23" s="8" t="inlineStr"/>
     </row>
@@ -9718,7 +9710,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 47 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 45 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -71,12 +71,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,9 +109,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -119,6 +116,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4120,118 +4120,110 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>SF-VMIS-04</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>S6-R4</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: vendor-missing WO PO seeded (S2-15774), but NO assign-vendor dropdown / PN-edit on any reachable surface (PO list = Receive only; single /accept-delivery = Vendor Missing badge + invoice/qty/Receive only; /parts/deliveries = received invoices). Appears to require the Bulk Receive page (Story 8, NOT built).</t>
-        </is>
-      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>SF-VMIS-05</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>S6-R5</t>
         </is>
       </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: no assign-vendor UI on reachable PO/receive surfaces to clear the flag (see SF-VMIS-04); part-level vendor+PN add DOES clear vendorless via WO Parts editor (part/change-request, SF-VPART-06). PO-surface flag-clear appears tied to Bulk Receive (Story 8, NOT built).</t>
-        </is>
-      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -4348,1011 +4340,1015 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>SF-POSEL-01</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>S7-R1</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>SF-POSEL-02</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>PO Multi-Select (Story 7)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>S7-R2</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>SF-POSEL-03</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>PO Multi-Select (Story 7)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>S7-R3</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>SF-POSEL-04</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>PO Multi-Select (Story 7)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>S7-R4</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>SF-POSEL-05</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>PO Multi-Select (Story 7)</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>S7-R5</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>SF-POSEL-06</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>PO Multi-Select (Story 7)</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>S7 (select-all scope)</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>SF-BULK-01</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>PO Bulk Receive Page (Story 8)</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>S8-R1</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SF-BULK-02</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>PO Bulk Receive Page (Story 8)</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>S8-R2 / S8-R3</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>SF-BULK-03</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>PO Bulk Receive Page (Story 8)</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>S8-R4</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>SF-BULK-04</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>PO Bulk Receive Page (Story 8)</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>S8-R5</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>SF-BULK-05</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>PO Bulk Receive Page (Story 8)</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>S8-R6</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>SF-BULK-06</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>PO Bulk Receive Page (Story 8)</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>S8-R7 / S10-R2</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>SF-BULK-07</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>PO Bulk Receive Page (Story 8)</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>S8-R8</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>SF-BULK-08</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>PO Bulk Receive Page (Story 8)</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>S8-R10</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>SF-BULK-09</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>PO Bulk Receive Page (Story 8)</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>S8-R11</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>SF-BULK-10</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>PO Bulk Receive Page (Story 8)</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 7 — PO multi-select (SV-7702); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>Story 7 — PO multi-select (SV-7702) | S7-R1</t>
-        </is>
-      </c>
-      <c r="J72" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>SF-POSEL-02</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>PO Multi-Select (Story 7)</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 7 — PO multi-select (SV-7702); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>Story 7 — PO multi-select (SV-7702) | S7-R2</t>
-        </is>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="5" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>SF-POSEL-03</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>PO Multi-Select (Story 7)</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 7 — PO multi-select (SV-7702); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>Story 7 — PO multi-select (SV-7702) | S7-R3</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="5" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>SF-POSEL-04</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>PO Multi-Select (Story 7)</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 7 — PO multi-select (SV-7702); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>Story 7 — PO multi-select (SV-7702) | S7-R4</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>SF-POSEL-05</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>PO Multi-Select (Story 7)</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 7 — PO multi-select (SV-7702); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>Story 7 — PO multi-select (SV-7702) | S7-R5</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>SF-POSEL-06</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>PO Multi-Select (Story 7)</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 7 — PO multi-select (SV-7702); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>Story 7 — PO multi-select (SV-7702) | S7 (select-all scope)</t>
-        </is>
-      </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="5" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>SF-BULK-01</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R1</t>
-        </is>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="5" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>SF-BULK-02</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R2 / S8-R3</t>
-        </is>
-      </c>
-      <c r="J79" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="5" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>SF-BULK-03</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R4</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="5" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>SF-BULK-04</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R5</t>
-        </is>
-      </c>
-      <c r="J81" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="5" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>SF-BULK-05</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R6</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="5" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>SF-BULK-06</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R7 / S10-R2</t>
-        </is>
-      </c>
-      <c r="J83" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K83" s="5" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>SF-BULK-07</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R8</t>
-        </is>
-      </c>
-      <c r="J84" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K84" s="5" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>SF-BULK-08</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I85" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R10</t>
-        </is>
-      </c>
-      <c r="J85" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K85" s="5" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>SF-BULK-09</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-R11</t>
-        </is>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K86" s="5" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>SF-BULK-10</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I87" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | S8-C1 / S8-C2</t>
-        </is>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K87" s="5" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>S8-C1 / S8-C2</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>RE-VIU 2026-07-09: Bulk Receive page BUILT; this case needs a genuine cored part received on the bulk page to expose Ok/Not-OK resolution (is_core part not seedable via canned/sub-form).</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>SF-INV-01</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 9 — Apply invoice to selected POs (SV-7704); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>Story 9 — Apply invoice to selected POs (SV-7704) | S9-R1</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K88" s="5" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>S9-R1</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>SF-INV-02</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 9 — Apply invoice to selected POs (SV-7704); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>Story 9 — Apply invoice to selected POs (SV-7704) | S9-R2</t>
-        </is>
-      </c>
-      <c r="J89" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K89" s="5" t="inlineStr"/>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>S9-R2</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>SF-INV-03</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 9 — Apply invoice to selected POs (SV-7704); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>Story 9 — Apply invoice to selected POs (SV-7704) | S9-R3</t>
-        </is>
-      </c>
-      <c r="J90" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K90" s="5" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>S9-R3</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -6239,61 +6235,57 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>SF-VEND-01</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>S13-R1</t>
         </is>
       </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K107" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: vendor-missing WO PO seeded, but no PO-level vendor dropdown on any reachable surface (PO list/accept-delivery/deliveries). The vendor-missing-group vendor dropdown appears to live on the Bulk Receive page (Story 8/13 UI, NOT built).</t>
-        </is>
-      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -6524,163 +6516,167 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>SF-WOP-01</t>
         </is>
       </c>
-      <c r="B112" s="5" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>S14-R1</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>SF-WOP-02</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Waiting on Parts Column (Story 14)</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E112" s="5" t="inlineStr">
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H112" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 14 — Waiting-on-Parts column (SV-7709); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I112" s="5" t="inlineStr">
-        <is>
-          <t>Story 14 — Waiting-on-Parts column (SV-7709) | S14-R1</t>
-        </is>
-      </c>
-      <c r="J112" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K112" s="5" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>SF-WOP-02</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>S14-R2</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>RE-VIU 2026-07-09: 'Waiting On Parts' column + unreceived count BUILT &amp; verified (SF-WOP-01); only the click-count-&gt;Accept-Delivery navigation is undriven (harness column-persistence flakiness + no non-zero cell surfaced). Just needs a stable WO row with a non-zero count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>SF-WOP-03</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 14 — Waiting-on-Parts column (SV-7709); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I113" s="5" t="inlineStr">
-        <is>
-          <t>Story 14 — Waiting-on-Parts column (SV-7709) | S14-R2</t>
-        </is>
-      </c>
-      <c r="J113" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K113" s="5" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>SF-WOP-03</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>Waiting on Parts Column (Story 14)</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 14 — Waiting-on-Parts column (SV-7709); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>Story 14 — Waiting-on-Parts column (SV-7709) | S14-R3</t>
-        </is>
-      </c>
-      <c r="J114" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K114" s="5" t="inlineStr"/>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>S14-R3</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7111,57 +7107,57 @@
       <c r="K122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
+      <c r="A123" s="5" t="inlineStr">
         <is>
           <t>SF-REV-09</t>
         </is>
       </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="B123" s="5" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="C123" s="5" t="inlineStr">
         <is>
           <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr">
+      <c r="F123" s="5" t="inlineStr">
         <is>
           <t>BUG/RULING</t>
         </is>
       </c>
-      <c r="G123" s="6" t="inlineStr">
+      <c r="G123" s="5" t="inlineStr">
         <is>
           <t>Dev / PO ruling</t>
         </is>
       </c>
-      <c r="H123" s="6" t="inlineStr">
+      <c r="H123" s="5" t="inlineStr">
         <is>
           <t>Review role-gating expected depends on reviewer!=completer (missing) and the FE-vs-BE ruling.</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr">
+      <c r="I123" s="5" t="inlineStr">
         <is>
           <t>R7 (role-gating) | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
-      <c r="J123" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K123" s="6" t="inlineStr"/>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -7755,163 +7751,163 @@
       <c r="K134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="6" t="inlineStr">
+      <c r="A135" s="5" t="inlineStr">
         <is>
           <t>SF-PERM-02</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
         <is>
           <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr">
+      <c r="F135" s="5" t="inlineStr">
         <is>
           <t>BUG/RULING</t>
         </is>
       </c>
-      <c r="G135" s="6" t="inlineStr">
+      <c r="G135" s="5" t="inlineStr">
         <is>
           <t>Dev / PO ruling</t>
         </is>
       </c>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>WO-completion role-gating is FE-only (button hidden for Tech, but BE allows it). Verdict depends on the same FE-vs-BE ruling as SF-PERM-06.</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
+      <c r="I135" s="5" t="inlineStr">
         <is>
           <t>§8 Permissions | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
-      <c r="J135" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K135" s="6" t="inlineStr"/>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>SF-PERM-03</t>
         </is>
       </c>
-      <c r="B136" s="5" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>§8 Permissions</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>SF-PERM-04</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Verify which roles can Mark Reviewed (sign off)</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — PO Bulk Receive page (SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703) | §8 Permissions</t>
-        </is>
-      </c>
-      <c r="J136" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K136" s="5" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>SF-PERM-04</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr">
-        <is>
-          <t>Verify which roles can Mark Reviewed (sign off)</t>
-        </is>
-      </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F137" s="6" t="inlineStr">
+      <c r="F137" s="5" t="inlineStr">
         <is>
           <t>BUG/RULING</t>
         </is>
       </c>
-      <c r="G137" s="6" t="inlineStr">
+      <c r="G137" s="5" t="inlineStr">
         <is>
           <t>Dev / PO ruling</t>
         </is>
       </c>
-      <c r="H137" s="6" t="inlineStr">
+      <c r="H137" s="5" t="inlineStr">
         <is>
           <t>Role-gating of Mark-Reviewed depends on reviewer!=completer (missing) and the FE-vs-BE ruling.</t>
         </is>
       </c>
-      <c r="I137" s="6" t="inlineStr">
+      <c r="I137" s="5" t="inlineStr">
         <is>
           <t>R7 / §8 role-gating review | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
-      <c r="J137" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K137" s="6" t="inlineStr"/>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -7967,163 +7963,163 @@
       <c r="K138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="6" t="inlineStr">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>SF-PERM-06</t>
         </is>
       </c>
-      <c r="B139" s="6" t="inlineStr">
+      <c r="B139" s="5" t="inlineStr">
         <is>
           <t>API — Permissions</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr">
+      <c r="C139" s="5" t="inlineStr">
         <is>
           <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F139" s="6" t="inlineStr">
+      <c r="F139" s="5" t="inlineStr">
         <is>
           <t>BUG/RULING</t>
         </is>
       </c>
-      <c r="G139" s="6" t="inlineStr">
+      <c r="G139" s="5" t="inlineStr">
         <is>
           <t>Dev / PO ruling</t>
         </is>
       </c>
-      <c r="H139" s="6" t="inlineStr">
+      <c r="H139" s="5" t="inlineStr">
         <is>
           <t>WO completion permission is FE-only at the BE (Technician completed via simple-complete API = 201). Ruling: SV-8183 says 'BE enforces' but SV-7864 atom-collapse lets any WO C&amp;E role act. Which governs?</t>
         </is>
       </c>
-      <c r="I139" s="6" t="inlineStr">
+      <c r="I139" s="5" t="inlineStr">
         <is>
           <t>§8 BE enforcement | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
-      <c r="J139" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K139" s="6" t="inlineStr"/>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="6" t="inlineStr">
+      <c r="A140" s="5" t="inlineStr">
         <is>
           <t>SF-PERM-07</t>
         </is>
       </c>
-      <c r="B140" s="6" t="inlineStr">
+      <c r="B140" s="5" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
+      <c r="C140" s="5" t="inlineStr">
         <is>
           <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F140" s="6" t="inlineStr">
+      <c r="F140" s="5" t="inlineStr">
         <is>
           <t>BUG/RULING</t>
         </is>
       </c>
-      <c r="G140" s="6" t="inlineStr">
+      <c r="G140" s="5" t="inlineStr">
         <is>
           <t>Dev / PO ruling</t>
         </is>
       </c>
-      <c r="H140" s="6" t="inlineStr">
+      <c r="H140" s="5" t="inlineStr">
         <is>
           <t>Review sign-off permission (woReviewWorkOrders) is FE-only at the BE (Technician drove change-status = 201). Same FE-vs-BE ruling.</t>
         </is>
       </c>
-      <c r="I140" s="6" t="inlineStr">
+      <c r="I140" s="5" t="inlineStr">
         <is>
           <t>§8 role-gating review | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
-      <c r="J140" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K140" s="6" t="inlineStr"/>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="6" t="inlineStr">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>SF-PERM-08</t>
         </is>
       </c>
-      <c r="B141" s="6" t="inlineStr">
+      <c r="B141" s="5" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C141" s="6" t="inlineStr">
+      <c r="C141" s="5" t="inlineStr">
         <is>
           <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F141" s="6" t="inlineStr">
+      <c r="F141" s="5" t="inlineStr">
         <is>
           <t>BUG/RULING</t>
         </is>
       </c>
-      <c r="G141" s="6" t="inlineStr">
+      <c r="G141" s="5" t="inlineStr">
         <is>
           <t>Dev / PO ruling</t>
         </is>
       </c>
-      <c r="H141" s="6" t="inlineStr">
+      <c r="H141" s="5" t="inlineStr">
         <is>
           <t>reviewer != completer rule NOT implemented (a user can sign off their own WO). Ruling: enforce the rule (currently FAIL) or descope?</t>
         </is>
       </c>
-      <c r="I141" s="6" t="inlineStr">
+      <c r="I141" s="5" t="inlineStr">
         <is>
           <t>R7 (reviewer != completer) | see viu-findings BUGS #5/#6/#7</t>
         </is>
       </c>
-      <c r="J141" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K141" s="6" t="inlineStr"/>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8668,110 +8664,118 @@
       <c r="K151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="inlineStr">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t>SF-VAL-09</t>
         </is>
       </c>
-      <c r="B152" s="5" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="D152" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E152" s="5" t="inlineStr">
+      <c r="E152" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G152" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H152" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 8 — Bulk Receive field locking (S8-R7, SV-7703); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I152" s="5" t="inlineStr">
-        <is>
-          <t>Story 8 — Bulk Receive field locking (S8-R7, SV-7703) | S8-R7 / §4 field locking</t>
-        </is>
-      </c>
-      <c r="J152" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K152" s="5" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>S8-R7 / §4 field locking</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>RE-VIU 2026-07-09: Bulk Receive field-locking BUILT (qty/cost/sell editable verified); the sell-lock-after-invoiced/paid clause needs an invoiced/paid WO to drive.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="inlineStr">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t>SF-VAL-10</t>
         </is>
       </c>
-      <c r="B153" s="5" t="inlineStr">
+      <c r="B153" s="4" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C153" s="5" t="inlineStr">
+      <c r="C153" s="4" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="D153" s="5" t="inlineStr">
+      <c r="D153" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E153" s="5" t="inlineStr">
+      <c r="E153" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>DEV NOT BUILT</t>
-        </is>
-      </c>
-      <c r="G153" s="5" t="inlineStr">
-        <is>
-          <t>Dev team</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr">
-        <is>
-          <t>Dev deploys Story 9 — Apply-invoice uniqueness (S9-R3, SV-7704); then QA re-runs VIU.</t>
-        </is>
-      </c>
-      <c r="I153" s="5" t="inlineStr">
-        <is>
-          <t>Story 9 — Apply-invoice uniqueness (S9-R3, SV-7704) | S9-R3 / §4 (uniqueness relaxed)</t>
-        </is>
-      </c>
-      <c r="J153" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K153" s="5" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>S9-R3 / §4 (uniqueness relaxed)</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>RE-VIU 2026-07-09: Apply-invoice BUILT &amp; verified (SF-INV-01/02/03); the reused-invoice-number (uniqueness relaxed) clause just needs a targeted drive applying the same invoice # to multiple POs.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -9342,7 +9346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9351,47 +9355,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Simple Flow — Blockers Tracker · Summary</t>
         </is>
       </c>
-      <c r="B1" s="8" t="n"/>
-      <c r="C1" s="8" t="n"/>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Total authored cases</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="7" t="n">
         <v>162</v>
       </c>
-      <c r="C3" s="8" t="n"/>
+      <c r="C3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Blocker category</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
@@ -9404,7 +9408,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9413,15 +9417,15 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>BLOCKED — DEV NOT BUILT</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="B7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Dev team</t>
         </is>
@@ -9434,7 +9438,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9458,15 +9462,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — BUG/RULING</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Dev / PO ruling</t>
         </is>
@@ -9481,12 +9485,12 @@
       <c r="B11" s="10" t="n">
         <v>162</v>
       </c>
-      <c r="C11" s="8" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -9499,247 +9503,151 @@
           <t>Count</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n"/>
+      <c r="C13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Story 8 — PO Bulk Receive page (SV-7703)</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C14" s="8" t="n"/>
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Story 7 — PO multi-select (SV-7702)</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C15" s="8" t="n"/>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA) — by sub-bucket</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Story 9 — Apply invoice to selected POs (SV-7704)</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" s="8" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>admin+tech + normal data; just needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Story 14 — Waiting-on-Parts column (SV-7709)</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" s="8" t="n"/>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>needs a data state not seedable via the app (see per-case detail).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>needs-account</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>needs a role account we don't have (see per-case detail).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>VIU PENDING (QA) — by sub-bucket</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
+          <t>TOTAL VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>admin+tech + normal data; just needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>needs a data state not seedable via the app (see per-case detail).</t>
-        </is>
-      </c>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>WHAT TO SEND ME NEXT (to unblock each batch)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>needs-account</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>needs a role account we don't have (see per-case detail).</t>
-        </is>
-      </c>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>• Milos's answers to the 11 Open Questions</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>unblocks 15 cases (all the MILOS-ANSWER rows). Send the filled-in OpenQuestions-for-Milos sheet.</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>TOTAL VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="C23" s="8" t="inlineStr"/>
+          <t>• Fresh QA cookies for sv7301 (admin + tech) + seeded test data</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>unblocks the bulk of the 46 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>• A 2nd/3rd role account (Office, Service Manager, Foreman) — some WITHOUT 'See Financial Data'</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>unblocks SF-PERM-09 and SF-PERM-10 (per-role completion + vendorless-add gate).</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>WHAT TO SEND ME NEXT (to unblock each batch)</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>• Milos's answers to the 11 Open Questions</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>unblocks 15 cases (all the MILOS-ANSWER rows). Send the filled-in OpenQuestions-for-Milos sheet.</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>• Dev deploys Story 8 — PO Bulk Receive page (SV-7703)</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>unblocks 12 case(s); then I re-run VIU and send an update file.</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>• Dev deploys Story 7 — PO multi-select (SV-7702)</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>unblocks 6 case(s); then I re-run VIU and send an update file.</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>• Dev deploys Story 9 — Apply invoice to selected POs (SV-7704)</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>unblocks 4 case(s); then I re-run VIU and send an update file.</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>• Dev deploys Story 14 — Waiting-on-Parts column (SV-7709)</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>unblocks 3 case(s); then I re-run VIU and send an update file.</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>• Fresh QA cookies for sv7301 (admin + tech) + seeded test data</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>unblocks the bulk of the 45 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>• A 2nd/3rd role account (Office, Service Manager, Foreman) — some WITHOUT 'See Financial Data'</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>unblocks SF-PERM-09 and SF-PERM-10 (per-role completion + vendorless-add gate).</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>• A dev/PO ruling on FE-only BE enforcement + the missing reviewer!=completer rule (resolve SV-8183 'BE enforces' vs SV-7864 atom-collapse)</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>finalizes the 6 BUG/RULING cases.</t>
         </is>
       </c>
-      <c r="C33" s="8" t="n"/>
+      <c r="C25" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -1948,61 +1948,57 @@
       <c r="K27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-12</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Verify the optional-invoice modal creates POs in the background and shows the count of parts to receive</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>S3-R1 / S3-R2 / S3-R9</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -4283,61 +4279,57 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>SF-VMIS-07</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>S6-R7</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K71" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5958,61 +5950,57 @@
       <c r="K101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>SF-RCV-06</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
-        </is>
-      </c>
-      <c r="I102" s="4" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>S12-R2</t>
         </is>
       </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K102" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: on a deliverable WO PO the Accept Delivery gates are present (vendor set, invoice # field), but Receive 500s (BUG-11); on a vendor-missing WO PO there is no assign-vendor / PN-edit control. Happy path was proven on an INVENTORY PO in BATCH 5; the WO-PO negative sub-gates need BUG-11 fixed.</t>
-        </is>
-      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -6178,61 +6166,57 @@
       <c r="K105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>SF-RCV-10</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G106" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>S12-R5</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K106" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6402,61 +6386,57 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>SF-VEND-04</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G110" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
-        </is>
-      </c>
-      <c r="I110" s="4" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>S13-R4 / S13-R5</t>
         </is>
       </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K110" s="4" t="inlineStr">
-        <is>
-          <t>a vendor-missing PO + receive-enable + QB-flag-clear check after auto-assign.</t>
-        </is>
-      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -6569,61 +6549,57 @@
       <c r="K112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>SF-WOP-02</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
         <is>
           <t>S14-R2</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K113" s="4" t="inlineStr">
-        <is>
-          <t>RE-VIU 2026-07-09: 'Waiting On Parts' column + unreceived count BUILT &amp; verified (SF-WOP-01); only the click-count-&gt;Accept-Delivery navigation is undriven (harness column-persistence flakiness + no non-zero cell surfaced). Just needs a stable WO row with a non-zero count.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7266,61 +7242,57 @@
       <c r="K125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>SF-REV-12</t>
         </is>
       </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G126" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
-        </is>
-      </c>
-      <c r="I126" s="4" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K126" s="4" t="inlineStr">
-        <is>
-          <t>enable Require Review; confirm a 'Ready for Review' list filter/column.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -8721,61 +8693,57 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="4" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-10</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C153" s="4" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G153" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I153" s="4" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>S9-R3 / §4 (uniqueness relaxed)</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K153" s="4" t="inlineStr">
-        <is>
-          <t>RE-VIU 2026-07-09: Apply-invoice BUILT &amp; verified (SF-INV-01/02/03); the reused-invoice-number (uniqueness relaxed) clause just needs a targeted drive applying the same invoice # to multiple POs.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -9408,7 +9376,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9438,7 +9406,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9534,7 +9502,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -9549,7 +9517,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -9579,7 +9547,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C19" s="7" t="inlineStr"/>
     </row>
@@ -9618,7 +9586,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 46 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 38 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -7120,7 +7120,7 @@
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>Review role-gating expected depends on reviewer!=completer (missing) and the FE-vs-BE ruling.</t>
+          <t>Review role-gating: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
@@ -7723,57 +7723,57 @@
       <c r="K134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>SF-PERM-02</t>
         </is>
       </c>
-      <c r="B135" s="5" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>BUG/RULING</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>Dev / PO ruling</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr">
-        <is>
-          <t>WO-completion role-gating is FE-only (button hidden for Tech, but BE allows it). Verdict depends on the same FE-vs-BE ruling as SF-PERM-06.</t>
-        </is>
-      </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>§8 Permissions | see viu-findings BUGS #5/#6/#7</t>
-        </is>
-      </c>
-      <c r="J135" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K135" s="5" t="inlineStr"/>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>§8 Permissions</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>Role-gating of Mark-Reviewed depends on reviewer!=completer (missing) and the FE-vs-BE ruling.</t>
+          <t>Role-gating of Mark-Reviewed: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, which is missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
@@ -7935,57 +7935,57 @@
       <c r="K138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>SF-PERM-06</t>
         </is>
       </c>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>API — Permissions</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
-      <c r="D139" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>BUG/RULING</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>Dev / PO ruling</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>WO completion permission is FE-only at the BE (Technician completed via simple-complete API = 201). Ruling: SV-8183 says 'BE enforces' but SV-7864 atom-collapse lets any WO C&amp;E role act. Which governs?</t>
-        </is>
-      </c>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>§8 BE enforcement | see viu-findings BUGS #5/#6/#7</t>
-        </is>
-      </c>
-      <c r="J139" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K139" s="5" t="inlineStr"/>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>§8 BE enforcement</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>Review sign-off permission (woReviewWorkOrders) is FE-only at the BE (Technician drove change-status = 201). Same FE-vs-BE ruling.</t>
+          <t>Review sign-off permission FE-only at BE was resolved by the 2026-07-10 ruling (UI pass / API fail, T2), BUT this case's expected also requires reviewer != completer, which fails at the UI too (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>reviewer != completer rule NOT implemented (a user can sign off their own WO). Ruling: enforce the rule (currently FAIL) or descope?</t>
+          <t>reviewer != completer rule NOT implemented (a user can sign off their own WO via the UI). NOT covered by the 2026-07-10 FE-vs-API ruling (the UI does not block it) — held on BUG-5 (TICKET 1): enforce or descope?</t>
         </is>
       </c>
       <c r="I141" s="5" t="inlineStr">
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>finalizes the 6 BUG/RULING cases.</t>
+          <t>finalizes the 4 BUG/RULING cases.</t>
         </is>
       </c>
       <c r="C25" s="7" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -1679,57 +1679,57 @@
       <c r="K22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-07</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Completion — No-PO / Skip (Story 2)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Verify in-stock inventory parts decrement inventory and write Part History on simple completion</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>MILOS ANSWER</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Milos (Product Owner)</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q2 — Auto-receive of in-stock parts on simple completion — intended behaviour?</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>Q2 | S2-R6 / §5 invariant 1</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>S2-R6 / §5 invariant 1</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1777,14 +1777,14 @@
           <t>S2-R2 / S2 AC (auto-pick off ⇒ pick in modal)</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>BATCH 6: with autoPickInventoryParts OFF, adding a catalog inventory part (P550848) still picks it via the bin-quantity input (status in_stock) so no Pick step appears. Needs an UNPICKED inventory part at completion (not seedable via the current add-part form).</t>
+          <t>FRESH VIU 2026-07-10: with autoPickInventoryParts=OFF, an added inventory part stays 'in_stock' and simple-complete is BE-BLOCKED (400 'All inventory and found parts must be picked...'); after line-level Pick it completes (201) — expected #2/#3 PROVEN. Remaining: surface the completion-WIZARD Pick step UI ('Pick all from default bins'/'Review individually') for expected #1 (drive the completion modal, not line-level pick).</t>
         </is>
       </c>
     </row>
@@ -8799,57 +8799,61 @@
       <c r="K154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="inlineStr">
+      <c r="A155" s="4" t="inlineStr">
         <is>
           <t>SF-QB-01</t>
         </is>
       </c>
-      <c r="B155" s="3" t="inlineStr">
+      <c r="B155" s="4" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="C155" s="4" t="inlineStr">
         <is>
           <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
-      <c r="D155" s="3" t="inlineStr">
+      <c r="D155" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E155" s="3" t="inlineStr">
+      <c r="E155" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F155" s="3" t="inlineStr">
-        <is>
-          <t>MILOS ANSWER</t>
-        </is>
-      </c>
-      <c r="G155" s="3" t="inlineStr">
-        <is>
-          <t>Milos (Product Owner)</t>
-        </is>
-      </c>
-      <c r="H155" s="3" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q2 — Inventory decrement / Part History on skip-path completion.</t>
-        </is>
-      </c>
-      <c r="I155" s="3" t="inlineStr">
-        <is>
-          <t>Q2 | §5 invariant 1</t>
-        </is>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K155" s="3" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t>§5 invariant 1</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>FRESH VIU 2026-07-10: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted through simple-complete 201). Part-History LOG surface BLOCKED-ENV: GET /api/inventory/parts/history -&gt; 500; /parts/inventory/{id} detail page crashes ('page is totaled'); other history endpoints 404/405 (see bugs-log OBS-6). QuickBooks-integrity leg needs QB access.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -9376,7 +9380,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9406,7 +9410,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9421,7 +9425,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -9502,7 +9506,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -9547,7 +9551,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="7" t="inlineStr"/>
     </row>
@@ -9573,7 +9577,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>unblocks 15 cases (all the MILOS-ANSWER rows). Send the filled-in OpenQuestions-for-Milos sheet.</t>
+          <t>unblocks 13 cases (all the MILOS-ANSWER rows). Send the filled-in OpenQuestions-for-Milos sheet.</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -9586,7 +9590,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 38 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 39 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -2323,61 +2323,57 @@
       <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-19</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>S4-R5 / S4-R7</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: deliverable WO PO achieved, but the receive round-trip is blocked by BUG-11 (POST /api/inventory/orders/accept returns 500 for a WO PO).</t>
-        </is>
-      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3896,61 +3892,57 @@
       <c r="K63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>SF-VPART-07</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed + drive the vendorless / no-PN part add flow.</t>
-        </is>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>S5-R4 / S5 AC (receive gate)</t>
         </is>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K64" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: deliverable WO PO achievable, but receiving it is blocked by BUG-11 (500), so the cannot-receive-until-PN+vendor proof cannot complete.</t>
-        </is>
-      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5343,61 +5335,57 @@
       <c r="K90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>SF-PNFIX-01</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
         <is>
           <t>S10-R1</t>
         </is>
       </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: no inline Missing-part-number Edit on the vendor-missing PO Accept Delivery (empty PN cell, no edit control). Inline PN-fix appears tied to the Bulk Receive page (Story 8, NOT built).</t>
-        </is>
-      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -8416,118 +8404,110 @@
       <c r="K147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-05</t>
         </is>
       </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
-      <c r="D148" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G148" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I148" s="4" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>S3-R3 / S4-R5 / §4</t>
         </is>
       </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K148" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: blocked by BUG-11 (WO-PO receive 500) — cannot complete a required-invoice receive to test the no-invoice-number negative.</t>
-        </is>
-      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-06</t>
         </is>
       </c>
-      <c r="B149" s="4" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G149" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I149" s="4" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>S10 / S12-R2 / S13</t>
         </is>
       </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K149" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: blocked by BUG-11 (WO-PO receive 500) and no assign-vendor UI on the reachable receive surface.</t>
-        </is>
-      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -9380,7 +9360,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9390,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9521,7 +9501,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -9551,7 +9531,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C19" s="7" t="inlineStr"/>
     </row>
@@ -9590,7 +9570,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 39 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 34 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -2001,61 +2001,57 @@
       <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-13</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>S3-R5</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: a deliverable ORDERED WO PO IS now achievable (Source=Vendor + real vendor + free-text PN). The shared Accept Delivery page opens for it via the PO Receive action, BUT the completion WIZARD Receive Parts still routes back to the WO lines (PO not placed until completion), and receiving the WO PO 500s (BUG-11).</t>
-        </is>
-      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6802,61 +6798,57 @@
       <c r="K117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>SF-REV-04</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G118" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
-        </is>
-      </c>
-      <c r="I118" s="4" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K118" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: deliverable WO PO achievable in the review flow, but receiving it is blocked by BUG-11 (500).</t>
-        </is>
-      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -9360,7 +9352,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9390,7 +9382,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9501,7 +9493,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -9531,7 +9523,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C19" s="7" t="inlineStr"/>
     </row>
@@ -9570,7 +9562,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 34 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 32 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -1732,61 +1732,57 @@
       <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-08</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Completion — No-PO / Skip (Story 2)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>S2-R2 / S2 AC (auto-pick off ⇒ pick in modal)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>FRESH VIU 2026-07-10: with autoPickInventoryParts=OFF, an added inventory part stays 'in_stock' and simple-complete is BE-BLOCKED (400 'All inventory and found parts must be picked...'); after line-level Pick it completes (201) — expected #2/#3 PROVEN. Remaining: surface the completion-WIZARD Pick step UI ('Pick all from default bins'/'Review individually') for expected #1 (drive the completion modal, not line-level pick).</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -9352,7 +9348,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9382,7 +9378,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9478,7 +9474,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -9523,7 +9519,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="7" t="inlineStr"/>
     </row>
@@ -9562,7 +9558,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 32 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 31 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -71,12 +71,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,9 +106,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -116,6 +113,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7059,57 +7059,57 @@
       <c r="K122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>SF-REV-09</t>
         </is>
       </c>
-      <c r="B123" s="5" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>BUG/RULING</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>Dev / PO ruling</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="inlineStr">
-        <is>
-          <t>Review role-gating: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
-        </is>
-      </c>
-      <c r="I123" s="5" t="inlineStr">
-        <is>
-          <t>R7 (role-gating) | see viu-findings BUGS #5/#6/#7</t>
-        </is>
-      </c>
-      <c r="J123" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K123" s="5" t="inlineStr"/>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>R7 (role-gating)</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -7805,57 +7805,57 @@
       <c r="K136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>SF-PERM-04</t>
         </is>
       </c>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C137" s="5" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
-      <c r="D137" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>BUG/RULING</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>Dev / PO ruling</t>
-        </is>
-      </c>
-      <c r="H137" s="5" t="inlineStr">
-        <is>
-          <t>Role-gating of Mark-Reviewed: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, which is missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
-        </is>
-      </c>
-      <c r="I137" s="5" t="inlineStr">
-        <is>
-          <t>R7 / §8 role-gating review | see viu-findings BUGS #5/#6/#7</t>
-        </is>
-      </c>
-      <c r="J137" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K137" s="5" t="inlineStr"/>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>R7 / §8 role-gating review</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -7964,110 +7964,110 @@
       <c r="K139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>SF-PERM-07</t>
         </is>
       </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>BUG/RULING</t>
-        </is>
-      </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>Dev / PO ruling</t>
-        </is>
-      </c>
-      <c r="H140" s="5" t="inlineStr">
-        <is>
-          <t>Review sign-off permission FE-only at BE was resolved by the 2026-07-10 ruling (UI pass / API fail, T2), BUT this case's expected also requires reviewer != completer, which fails at the UI too (BUG-5). Held on BUG-5 (TICKET 1).</t>
-        </is>
-      </c>
-      <c r="I140" s="5" t="inlineStr">
-        <is>
-          <t>§8 role-gating review | see viu-findings BUGS #5/#6/#7</t>
-        </is>
-      </c>
-      <c r="J140" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K140" s="5" t="inlineStr"/>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>§8 role-gating review</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>SF-PERM-08</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E141" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>BUG/RULING</t>
-        </is>
-      </c>
-      <c r="G141" s="5" t="inlineStr">
-        <is>
-          <t>Dev / PO ruling</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="inlineStr">
-        <is>
-          <t>reviewer != completer rule NOT implemented (a user can sign off their own WO via the UI). NOT covered by the 2026-07-10 FE-vs-API ruling (the UI does not block it) — held on BUG-5 (TICKET 1): enforce or descope?</t>
-        </is>
-      </c>
-      <c r="I141" s="5" t="inlineStr">
-        <is>
-          <t>R7 (reviewer != completer) | see viu-findings BUGS #5/#6/#7</t>
-        </is>
-      </c>
-      <c r="J141" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K141" s="5" t="inlineStr"/>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>[OBSOLETE — descoped v1] The completer reviewing their own WO is EXPECTED in v1 (was: user who completed cannot Mark Reviewed)</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>R7 (review sign-off) — reviewer != completer DESCOPED v1</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -9295,47 +9295,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Simple Flow — Blockers Tracker · Summary</t>
         </is>
       </c>
-      <c r="B1" s="7" t="n"/>
-      <c r="C1" s="7" t="n"/>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="n"/>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Total authored cases</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="6" t="n">
         <v>162</v>
       </c>
-      <c r="C3" s="7" t="n"/>
+      <c r="C3" s="6" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="n"/>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Blocker category</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9357,15 +9357,15 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>BLOCKED — DEV NOT BUILT</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Dev team</t>
         </is>
@@ -9402,15 +9402,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>BLOCKED — BUG/RULING</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="B10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Dev / PO ruling</t>
         </is>
@@ -9425,12 +9425,12 @@
       <c r="B11" s="10" t="n">
         <v>162</v>
       </c>
-      <c r="C11" s="7" t="inlineStr"/>
+      <c r="C11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -9443,12 +9443,12 @@
           <t>Count</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n"/>
+      <c r="C13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -9476,7 +9476,7 @@
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>admin+tech + normal data; just needs another VIU pass (no new inputs).</t>
         </is>
@@ -9491,22 +9491,22 @@
       <c r="B17" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>needs a data state not seedable via the app (see per-case detail).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>needs-account</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>needs a role account we don't have (see per-case detail).</t>
         </is>
@@ -9521,12 +9521,12 @@
       <c r="B19" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="C19" s="7" t="inlineStr"/>
+      <c r="C19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -9534,8 +9534,8 @@
           <t>WHAT TO SEND ME NEXT (to unblock each batch)</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -9543,12 +9543,12 @@
           <t>• Milos's answers to the 11 Open Questions</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>unblocks 13 cases (all the MILOS-ANSWER rows). Send the filled-in OpenQuestions-for-Milos sheet.</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
+      <c r="C22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -9556,12 +9556,12 @@
           <t>• Fresh QA cookies for sv7301 (admin + tech) + seeded test data</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>unblocks the bulk of the 31 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
+      <c r="C23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -9569,12 +9569,12 @@
           <t>• A 2nd/3rd role account (Office, Service Manager, Foreman) — some WITHOUT 'See Financial Data'</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>unblocks SF-PERM-09 and SF-PERM-10 (per-role completion + vendorless-add gate).</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n"/>
+      <c r="C24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -9582,12 +9582,12 @@
           <t>• A dev/PO ruling on FE-only BE enforcement + the missing reviewer!=completer rule (resolve SV-8183 'BE enforces' vs SV-7864 atom-collapse)</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>finalizes the 4 BUG/RULING cases.</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="n"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>finalizes the 0 BUG/RULING cases.</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -8029,7 +8029,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>[OBSOLETE — descoped v1] The completer reviewing their own WO is EXPECTED in v1 (was: user who completed cannot Mark Reviewed)</t>
+          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>R7 (review sign-off) — reviewer != completer DESCOPED v1</t>
+          <t>R7 (review sign-off) — self-review permission-gated (identity rule NOT in v1)</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K163"/>
+  <dimension ref="A1:K164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2156,57 +2156,61 @@
       <c r="K31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>SF-COMP-16</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Verify the optional-invoice completion modal collects the required vehicle fields (mileage and engine hours; VIN only when Require Review is off) when missing</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>S3-R3</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2421,110 +2425,118 @@
       <c r="K36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>SF-COMP-21</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Completion — Line approval gate</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Key Decision (all lines approved) / S3-R9 / S4-R8</t>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Verify on a required-invoice work order an unapproved line disables the Complete Work Order button with a tooltip</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>S4-R8 / Key Decision (all lines approved) / S3-R9</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>SF-COMP-22</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Completion — Line approval gate</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Key Decision (holds regardless of Auto-approve)</t>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Verify a manually unapproved line disables the required-invoice Complete Work Order button with a tooltip even when Auto-approve is ON</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>S4-R8 / Key Decision (holds regardless of Auto-approve)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -5563,12 +5575,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify a part cannot be received without a part number, a vendor (for vendor-missing) and a cost / sell price, even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -5593,7 +5605,7 @@
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>S10 Negative</t>
+          <t>S10 Negative / S13-R6 / S13-R7</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -5930,57 +5942,61 @@
       <c r="K101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>SF-RCV-06</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>S12-R2</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr"/>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Verify Accept Delivery receive gates: vendor set, part number entered, cost / sell price entered, vendor invoice # captured</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>S12-R2 / S13-R6 / S13-R7</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>BATCH 6: on a deliverable WO PO the Accept Delivery gates are present (vendor set, invoice # field), but Receive 500s (BUG-11); on a vendor-missing WO PO there is no assign-vendor / PN-edit control. Happy path was proven on an INVENTORY PO in BATCH 5; the WO-PO negative sub-gates need BUG-11 fixed.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -6366,57 +6382,61 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>SF-VEND-04</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>S13-R4 / S13-R5</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr"/>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Verify assigning a different vendor with no collision auto-assigns and clears the QB flag, and Receive enables only once the part number and cost / sell price are also present</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>S13-R4 / S13-R5 / S13-R6 / S13-R7</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>a vendor-missing PO + receive-enable + QB-flag-clear check after auto-assign.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -6476,62 +6496,66 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>SF-WOP-01</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Waiting on Parts Column (Story 14)</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>S14-R1</t>
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>SF-VEND-06</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Assign Vendor + Merge (Story 13)</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Verify a part cannot be received until a missing cost / sell price is entered</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Pending / Retest — new case for V2.4 Δ3 (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>S13-R7</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr"/>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -6541,7 +6565,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -6571,7 +6595,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>S14-R2</t>
+          <t>S14-R1</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -6584,7 +6608,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -6594,7 +6618,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6624,7 +6648,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>S14-R3</t>
+          <t>S14-R2</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -6637,17 +6661,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>SF-REV-01</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Verify the Require Review setting drives the review flow when turned on</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -6677,7 +6701,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>S14-R3</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -6690,7 +6714,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>SF-REV-02</t>
+          <t>SF-REV-01</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -6700,7 +6724,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
+          <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -6730,7 +6754,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -6743,7 +6767,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-REV-02</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -6753,7 +6777,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -6783,7 +6807,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -6796,7 +6820,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -6806,7 +6830,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -6836,7 +6860,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -6849,7 +6873,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>SF-REV-05</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6859,7 +6883,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -6889,7 +6913,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>R5 / R6</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -6902,7 +6926,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>SF-REV-06</t>
+          <t>SF-REV-05</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6912,7 +6936,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
+          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -6942,7 +6966,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>R7 / R10</t>
+          <t>R5 / R6</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -6955,541 +6979,541 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>SF-REV-06</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>R7 / R10</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
           <t>SF-REV-07</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>SF-REV-08</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>MILOS ANSWER</t>
         </is>
       </c>
-      <c r="G122" s="3" t="inlineStr">
+      <c r="G123" s="3" t="inlineStr">
         <is>
           <t>Milos (Product Owner)</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H123" s="3" t="inlineStr">
         <is>
           <t>Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
         </is>
       </c>
-      <c r="I122" s="3" t="inlineStr">
+      <c r="I123" s="3" t="inlineStr">
         <is>
           <t>Q8, Q4 | R5 / R8 (distinct Reviewed state)</t>
         </is>
       </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K122" s="3" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>SF-REV-09</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
         <is>
           <t>R7 (role-gating)</t>
         </is>
       </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>SF-REV-10</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>MILOS ANSWER</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>Milos (Product Owner)</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
-        </is>
-      </c>
-      <c r="I124" s="3" t="inlineStr">
-        <is>
-          <t>Q7 | R7 (VIN required, no note)</t>
-        </is>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K124" s="3" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
+          <t>SF-REV-10</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>MILOS ANSWER</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>Milos (Product Owner)</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>Q7 | R7 (VIN required, no note)</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
           <t>SF-REV-11</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C125" s="3" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E125" s="3" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F125" s="3" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr">
         <is>
           <t>MILOS ANSWER</t>
         </is>
       </c>
-      <c r="G125" s="3" t="inlineStr">
+      <c r="G126" s="3" t="inlineStr">
         <is>
           <t>Milos (Product Owner)</t>
         </is>
       </c>
-      <c r="H125" s="3" t="inlineStr">
+      <c r="H126" s="3" t="inlineStr">
         <is>
           <t>Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
         </is>
       </c>
-      <c r="I125" s="3" t="inlineStr">
+      <c r="I126" s="3" t="inlineStr">
         <is>
           <t>Q8 | R8</t>
         </is>
       </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K125" s="3" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>SF-REV-12</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr"/>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>SF-REV-12</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
           <t>SF-REV-13</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
         <is>
           <t>SF-REV-14</t>
         </is>
       </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="B129" s="4" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
+      <c r="C129" s="4" t="inlineStr">
         <is>
           <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D129" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
+      <c r="E129" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F128" s="4" t="inlineStr">
+      <c r="F129" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G128" s="4" t="inlineStr">
+      <c r="G129" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H128" s="4" t="inlineStr">
+      <c r="H129" s="4" t="inlineStr">
         <is>
           <t>QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
         </is>
       </c>
-      <c r="I128" s="4" t="inlineStr">
+      <c r="I129" s="4" t="inlineStr">
         <is>
           <t>R Core parts / invoicing block</t>
         </is>
       </c>
-      <c r="J128" s="4" t="inlineStr">
+      <c r="J129" s="4" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="K128" s="4" t="inlineStr">
+      <c r="K129" s="4" t="inlineStr">
         <is>
           <t>cores + receiving in the review flow — blocked by BUG-10 (no wizard resolve step) + BUG-11 (WO-PO receive 500) + special-order cores not seedable.</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t>SF-REV-15</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B130" s="3" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C130" s="3" t="inlineStr">
         <is>
           <t>Verify the Require Review default for new vs existing orgs matches the agreed cohort rule</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>Open-Question</t>
         </is>
       </c>
-      <c r="E129" s="3" t="inlineStr">
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr">
         <is>
           <t>MILOS ANSWER</t>
         </is>
       </c>
-      <c r="G129" s="3" t="inlineStr">
+      <c r="G130" s="3" t="inlineStr">
         <is>
           <t>Milos (Product Owner)</t>
         </is>
       </c>
-      <c r="H129" s="3" t="inlineStr">
+      <c r="H130" s="3" t="inlineStr">
         <is>
           <t>Milos answers Open Question Q1 — Require-review default cohort rule + new-org preset.</t>
         </is>
       </c>
-      <c r="I129" s="3" t="inlineStr">
+      <c r="I130" s="3" t="inlineStr">
         <is>
           <t>Q1 | R Open (default)</t>
         </is>
       </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K129" s="3" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>SF-UX-01</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>UX Refinements (Story 15)</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Verify the work order primary button reads 'Create Work Order'</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>S15-R1</t>
-        </is>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K130" s="2" t="inlineStr"/>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>SF-UX-02</t>
+          <t>SF-UX-01</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -7499,7 +7523,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
+          <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -7529,7 +7553,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>S15-R2</t>
+          <t>S15-R1</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -7542,176 +7566,176 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>SF-UX-02</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>UX Refinements (Story 15)</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>S15-R2</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
           <t>SF-UX-03</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
         <is>
           <t>S15-R3</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t>SF-UX-04</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E133" s="3" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>MILOS ANSWER</t>
         </is>
       </c>
-      <c r="G133" s="3" t="inlineStr">
+      <c r="G134" s="3" t="inlineStr">
         <is>
           <t>Milos (Product Owner)</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
+      <c r="H134" s="3" t="inlineStr">
         <is>
           <t>Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
         </is>
       </c>
-      <c r="I133" s="3" t="inlineStr">
+      <c r="I134" s="3" t="inlineStr">
         <is>
           <t>Q10 | S15-R4</t>
         </is>
       </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K133" s="3" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>SF-PERM-01</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>API — Permissions</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>S1 AC / §8 Permissions</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K134" s="2" t="inlineStr"/>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>SF-PERM-02</t>
+          <t>SF-PERM-01</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>API — Permissions</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Verify which roles can complete a work order (Simple completion)</t>
+          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -7741,7 +7765,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>§8 Permissions</t>
+          <t>S1 AC / §8 Permissions</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -7754,7 +7778,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-PERM-02</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -7764,7 +7788,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -7807,7 +7831,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>SF-PERM-04</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -7817,7 +7841,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Verify which roles can Mark Reviewed (sign off)</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -7847,7 +7871,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>R7 / §8 role-gating review</t>
+          <t>§8 Permissions</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -7860,7 +7884,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>SF-PERM-05</t>
+          <t>SF-PERM-04</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -7870,7 +7894,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Verify the PO Receive button is hidden for office/readonly users</t>
+          <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -7900,7 +7924,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>S11-R3</t>
+          <t>R7 / §8 role-gating review</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -7913,17 +7937,17 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>SF-PERM-06</t>
+          <t>SF-PERM-05</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>API — Permissions</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
+          <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -7953,7 +7977,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>§8 BE enforcement</t>
+          <t>S11-R3</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -7966,17 +7990,17 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>SF-PERM-07</t>
+          <t>SF-PERM-06</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>API — Permissions</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
+          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -8006,7 +8030,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>§8 role-gating review</t>
+          <t>§8 BE enforcement</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -8019,7 +8043,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>SF-PERM-08</t>
+          <t>SF-PERM-07</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -8029,7 +8053,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
+          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -8059,7 +8083,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>R7 (review sign-off) — self-review permission-gated (identity rule NOT in v1)</t>
+          <t>§8 role-gating review</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
@@ -8072,7 +8096,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>SF-PERM-09</t>
+          <t>SF-PERM-08</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -8082,7 +8106,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -8112,7 +8136,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>S5 / §9 (See Financial Data gate)</t>
+          <t>R7 (review sign-off) — self-review permission-gated (identity rule NOT in v1)</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -8125,7 +8149,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>SF-PERM-10</t>
+          <t>SF-PERM-09</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -8135,7 +8159,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -8165,7 +8189,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>§9 per-role completion matrix</t>
+          <t>S5 / §9 (See Financial Data gate)</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -8178,170 +8202,170 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>SF-PERM-10</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>§9 per-role completion matrix</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
           <t>SF-VAL-01</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
         <is>
           <t>S2-R2 / S3-R3 / S4-R3</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="4" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>SF-VAL-02</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C145" s="4" t="inlineStr">
-        <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E145" s="4" t="inlineStr">
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr">
+      <c r="F146" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G145" s="4" t="inlineStr">
+      <c r="G146" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H145" s="4" t="inlineStr">
+      <c r="H146" s="4" t="inlineStr">
         <is>
           <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
-      <c r="I145" s="4" t="inlineStr">
-        <is>
-          <t>S15-R2 / S3-R3</t>
-        </is>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>S15-R2 / S3-R3 / S4-R3</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="K145" s="4" t="inlineStr">
+      <c r="K146" s="4" t="inlineStr">
         <is>
           <t>an asset/vehicle with NO VIN so the non-review wizard prompts for VIN. BATCH 6: VIN prefills from the asset; the asset-creation flow (VIN likely required) was not reliably drivable in-harness. Needs a VIN-less asset seeded.</t>
         </is>
       </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>SF-VAL-03</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>S3-R3 / S4-R3</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>SF-VAL-04</t>
+          <t>SF-VAL-03</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -8351,7 +8375,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
+          <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -8381,7 +8405,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>TS-R4</t>
+          <t>S3-R3 / S4-R3</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -8394,7 +8418,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-VAL-04</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -8404,7 +8428,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -8434,7 +8458,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>S3-R3 / S4-R5 / §4</t>
+          <t>TS-R4</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -8447,276 +8471,280 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>SF-VAL-05</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>S3-R3 / S4-R5 / §4</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
           <t>SF-VAL-06</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B150" s="4" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>S10 / S12-R2 / S13</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>SF-VAL-07</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>R7</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K150" s="2" t="inlineStr"/>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>S10 / S12-R2 / S13-R6 / S13-R7</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>BATCH 6: blocked by BUG-11 (WO-PO receive 500) and no assign-vendor UI on the reachable receive surface.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>SF-VAL-07</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
           <t>SF-VAL-08</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
         <is>
           <t>S3-R9 (idempotency)</t>
         </is>
       </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="4" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t>SF-VAL-09</t>
         </is>
       </c>
-      <c r="B152" s="4" t="inlineStr">
+      <c r="B153" s="4" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C152" s="4" t="inlineStr">
+      <c r="C153" s="4" t="inlineStr">
         <is>
           <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
-      <c r="D152" s="4" t="inlineStr">
+      <c r="D153" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
+      <c r="E153" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F152" s="4" t="inlineStr">
+      <c r="F153" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G152" s="4" t="inlineStr">
+      <c r="G153" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H152" s="4" t="inlineStr">
+      <c r="H153" s="4" t="inlineStr">
         <is>
           <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
-      <c r="I152" s="4" t="inlineStr">
+      <c r="I153" s="4" t="inlineStr">
         <is>
           <t>S8-R7 / §4 field locking</t>
         </is>
       </c>
-      <c r="J152" s="4" t="inlineStr">
+      <c r="J153" s="4" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="K152" s="4" t="inlineStr">
+      <c r="K153" s="4" t="inlineStr">
         <is>
           <t>RE-VIU 2026-07-09: Bulk Receive field-locking BUILT (qty/cost/sell editable verified); the sell-lock-after-invoiced/paid clause needs an invoiced/paid WO to drive.</t>
         </is>
       </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>SF-VAL-10</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>S9-R3 / §4 (uniqueness relaxed)</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>SF-VAL-11</t>
+          <t>SF-VAL-10</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -8726,7 +8754,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Verify the approve-line error text appears when completing with an unapproved line</t>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -8756,7 +8784,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Key Decision (line approval)</t>
+          <t>S9-R3 / §4 (uniqueness relaxed)</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -8769,174 +8797,174 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
+          <t>SF-VAL-11</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>Verify an unapproved line blocks completion — required-invoice shows a disabled Complete button with a tooltip; other flows show the approve-line error</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t>S4-R8 / S3-R9 / Key Decision (line approval)</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
           <t>SF-QB-01</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="B156" s="4" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C155" s="4" t="inlineStr">
+      <c r="C156" s="4" t="inlineStr">
         <is>
           <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
-      <c r="D155" s="4" t="inlineStr">
+      <c r="D156" s="4" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
+      <c r="E156" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F155" s="4" t="inlineStr">
+      <c r="F156" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G155" s="4" t="inlineStr">
+      <c r="G156" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H155" s="4" t="inlineStr">
+      <c r="H156" s="4" t="inlineStr">
         <is>
           <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
-      <c r="I155" s="4" t="inlineStr">
+      <c r="I156" s="4" t="inlineStr">
         <is>
           <t>§5 invariant 1</t>
         </is>
       </c>
-      <c r="J155" s="4" t="inlineStr">
+      <c r="J156" s="4" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="K155" s="4" t="inlineStr">
+      <c r="K156" s="4" t="inlineStr">
         <is>
           <t>FRESH VIU 2026-07-10: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted through simple-complete 201). Part-History LOG surface BLOCKED-ENV: GET /api/inventory/parts/history -&gt; 500; /parts/inventory/{id} detail page crashes ('page is totaled'); other history endpoints 404/405 (see bugs-log OBS-6). QuickBooks-integrity leg needs QB access.</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="3" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
         <is>
           <t>SF-QB-02</t>
         </is>
       </c>
-      <c r="B156" s="3" t="inlineStr">
+      <c r="B157" s="3" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
+      <c r="C157" s="3" t="inlineStr">
         <is>
           <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
         </is>
       </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>Open-Question</t>
         </is>
       </c>
-      <c r="E156" s="3" t="inlineStr">
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F156" s="3" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr">
         <is>
           <t>MILOS ANSWER</t>
         </is>
       </c>
-      <c r="G156" s="3" t="inlineStr">
+      <c r="G157" s="3" t="inlineStr">
         <is>
           <t>Milos (Product Owner)</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
+      <c r="H157" s="3" t="inlineStr">
         <is>
           <t>Milos answers Open Question Q5 — QuickBooks integrity when Create-POs is OFF (toggle absent).</t>
         </is>
       </c>
-      <c r="I156" s="3" t="inlineStr">
+      <c r="I157" s="3" t="inlineStr">
         <is>
           <t>Q5 | §5 / §4 (Create POs OFF)</t>
         </is>
       </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K156" s="3" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>SF-QB-03</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="inlineStr">
-        <is>
-          <t>§5 invariant 2</t>
-        </is>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>QuickBooks / inventory back-end inspection (receive -&gt; Delivery -&gt; Vendor Bill -&gt; QBO) — likely needs dev/QB access.</t>
-        </is>
-      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-04</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -8946,7 +8974,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -8976,7 +9004,7 @@
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>§5 (vendorless/no-PN)</t>
+          <t>§5 invariant 2</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
@@ -8986,14 +9014,14 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>QuickBooks / inventory inspection (vendorless/no-PN part = zero inventory interaction) — likely needs dev/QB access.</t>
+          <t>QuickBooks / inventory back-end inspection (receive -&gt; Delivery -&gt; Vendor Bill -&gt; QBO) — likely needs dev/QB access.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-05</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -9003,7 +9031,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -9033,7 +9061,7 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>§5 / S6-R3</t>
+          <t>§5 (vendorless/no-PN)</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -9043,14 +9071,14 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>QuickBooks inspection (Vendor-Missing POs excluded from QB until vendor + PN) — likely needs dev/QB access.</t>
+          <t>QuickBooks / inventory inspection (vendorless/no-PN part = zero inventory interaction) — likely needs dev/QB access.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-06</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -9060,7 +9088,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -9090,7 +9118,7 @@
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>§8 (cost at completion)</t>
+          <t>§5 / S6-R3</t>
         </is>
       </c>
       <c r="J160" s="4" t="inlineStr">
@@ -9100,14 +9128,14 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>QuickBooks inspection (cost-at-completion to avoid $0-cost margins) — likely needs dev/QB access.</t>
+          <t>QuickBooks inspection (Vendor-Missing POs excluded from QB until vendor + PN) — likely needs dev/QB access.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-07</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -9117,7 +9145,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -9147,7 +9175,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>§5 (Journal Entry / Inventory → QBO)</t>
+          <t>§8 (cost at completion)</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -9157,14 +9185,14 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>QuickBooks inspection (Journal Entry / Inventory sync fires on invoice creation) — likely needs dev/QB access.</t>
+          <t>QuickBooks inspection (cost-at-completion to avoid $0-cost margins) — likely needs dev/QB access.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-08</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -9174,7 +9202,7 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -9204,7 +9232,7 @@
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>§5 invariant 3</t>
+          <t>§5 (Journal Entry / Inventory → QBO)</t>
         </is>
       </c>
       <c r="J162" s="4" t="inlineStr">
@@ -9214,62 +9242,119 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>Inventory Part History inspection for any part that becomes inventory-tracked — likely needs dev/QB access.</t>
+          <t>QuickBooks inspection (Journal Entry / Inventory sync fires on invoice creation) — likely needs dev/QB access.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
+          <t>SF-QB-08</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>§5 invariant 3</t>
+        </is>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>Inventory Part History inspection for any part that becomes inventory-tracked — likely needs dev/QB access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
           <t>SF-QB-09</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B164" s="4" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C163" s="4" t="inlineStr">
+      <c r="C164" s="4" t="inlineStr">
         <is>
           <t>Investigate: Part Sales unaffected by the shared order/status logic (requested -&gt; orderable/waiting-to-receive)</t>
         </is>
       </c>
-      <c r="D163" s="4" t="inlineStr">
+      <c r="D164" s="4" t="inlineStr">
         <is>
           <t>Open-Question</t>
         </is>
       </c>
-      <c r="E163" s="4" t="inlineStr">
+      <c r="E164" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F163" s="4" t="inlineStr">
+      <c r="F164" s="4" t="inlineStr">
         <is>
           <t>VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="G163" s="4" t="inlineStr">
+      <c r="G164" s="4" t="inlineStr">
         <is>
           <t>QA (needs cookies+seed data)</t>
         </is>
       </c>
-      <c r="H163" s="4" t="inlineStr">
+      <c r="H164" s="4" t="inlineStr">
         <is>
           <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
-      <c r="I163" s="4" t="inlineStr">
+      <c r="I164" s="4" t="inlineStr">
         <is>
           <t>§8 open question (Part Sales impact — BE investigation)</t>
         </is>
       </c>
-      <c r="J163" s="2" t="inlineStr">
+      <c r="J164" s="2" t="inlineStr">
         <is>
           <t>reachable-now</t>
         </is>
       </c>
-      <c r="K163" s="4" t="inlineStr">
+      <c r="K164" s="4" t="inlineStr">
         <is>
           <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
         </is>
@@ -9315,7 +9400,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C3" s="6" t="n"/>
     </row>
@@ -9348,7 +9433,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9378,7 +9463,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9423,7 +9508,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C11" s="6" t="inlineStr"/>
     </row>
@@ -9474,7 +9559,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -9489,7 +9574,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -9519,7 +9604,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C19" s="6" t="inlineStr"/>
     </row>
@@ -9558,7 +9643,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 31 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 39 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="6" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Verify the Work Order settings page shows all Simple-Flow toggles in order with new vs existing visually distinct</t>
+          <t>Verify the Work Orders settings tab lists all Work Order setting toggles in order</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Verify a 'Create Purchase Orders' toggle exists and, when off, hides the Vendor Invoice sub-setting</t>
+          <t>Verify a 'Create Purchase Orders' toggle exists on the Work Orders tab and controls the Vendor Invoice setting</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Open-Question</t>
+          <t>Deviation</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1043,57 +1043,61 @@
       <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SF-SET-10</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Work Order Settings</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Verify a settings change applies to future completions only and not to already-completed work orders</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: toggle the setting and confirm the downstream behaviour.</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>S1-R9 (future completions only, never retroactive)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1219,7 +1223,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1643,7 +1647,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Open-Question</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2156,61 +2160,57 @@
       <c r="K31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-16</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Verify the optional-invoice completion modal collects the required vehicle fields (mileage and engine hours; VIN only when Require Review is off) when missing</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Verify the completion modal collects the missing required vehicle fields (Mileage and Engine Hours; no VIN field in the modal)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>S3-R3</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -2645,61 +2645,57 @@
       <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-02</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Core parts — Completion modal</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>S3-C1 (skipped if none)</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>a genuine core part to prove the Resolve-Cores step appears, plus a no-core WO to prove it is skipped (is_core not seedable via canned/sub-form).</t>
-        </is>
-      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -3484,7 +3480,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
+          <t>Verify the tech-story modal has a text box for typing the story</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4072,7 +4068,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -4658,7 +4654,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify the Bulk Receive page has a 'Back To Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -5029,7 +5025,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify Receive All receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5192,7 +5188,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify each vendor group has an 'Apply to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5580,7 +5576,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -5959,7 +5955,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -6069,7 +6065,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -6399,7 +6395,7 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -6513,7 +6509,7 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Pending / Retest — new case for V2.4 Δ3 (2026-07-13), needs live re-VIU</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -7475,7 +7471,7 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Open-Question</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -8323,7 +8319,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -8539,7 +8535,7 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -8812,7 +8808,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -8926,7 +8922,7 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Open-Question</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
@@ -8979,7 +8975,7 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -9093,7 +9089,7 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
@@ -9150,7 +9146,7 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -9207,7 +9203,7 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
@@ -9433,7 +9429,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -9463,7 +9459,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -9574,7 +9570,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -9604,7 +9600,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="6" t="inlineStr"/>
     </row>
@@ -9643,7 +9639,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 39 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 38 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="6" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K164"/>
+  <dimension ref="A1:M164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -506,6 +506,8 @@
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="65" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -564,6 +566,16 @@
           <t>VIU sub-bucket detail (QA-pending only)</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TestRail ID</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TestRail Link</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -617,6 +629,16 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>C29275</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29275</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -670,6 +692,16 @@
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>C29276</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29276</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -723,6 +755,16 @@
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>C29277</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29277</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -776,6 +818,16 @@
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>C29278</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29278</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -829,6 +881,16 @@
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>C29279</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29279</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -882,6 +944,16 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>C29280</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29280</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -935,6 +1007,16 @@
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>C29281</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29281</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -988,6 +1070,16 @@
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>C29282</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29282</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1041,6 +1133,16 @@
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>C29283</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29283</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1098,6 +1200,16 @@
           <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
         </is>
       </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>C29284</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29284</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1151,6 +1263,16 @@
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>C29285</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29285</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1204,6 +1326,16 @@
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>C29286</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29286</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1257,6 +1389,16 @@
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>C29287</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29287</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1310,6 +1452,16 @@
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>C29288</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29288</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1363,6 +1515,16 @@
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>C29289</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29289</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1416,6 +1578,16 @@
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>C29290</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29290</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1469,6 +1641,16 @@
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>C29291</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29291</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1522,6 +1704,16 @@
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>C29292</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29292</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1575,6 +1767,16 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>C29293</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29293</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1628,6 +1830,16 @@
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>C29294</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29294</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1681,6 +1893,16 @@
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>C29295</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29295</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1734,6 +1956,16 @@
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>C29296</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29296</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1787,6 +2019,16 @@
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>C29297</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29297</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1840,6 +2082,16 @@
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>C29298</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29298</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1893,6 +2145,16 @@
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>C29299</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29299</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1946,6 +2208,16 @@
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>C29300</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29300</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1999,6 +2271,16 @@
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>C29301</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29301</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2052,6 +2334,16 @@
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>C29302</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29302</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2105,6 +2397,16 @@
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>C29303</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29303</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2158,6 +2460,16 @@
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>C29304</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29304</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2211,6 +2523,16 @@
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>C29305</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29305</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2264,6 +2586,16 @@
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>C29306</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29306</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2317,6 +2649,16 @@
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>C29307</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29307</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2370,6 +2712,16 @@
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>C29308</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2423,6 +2775,16 @@
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>C29309</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -2480,6 +2842,16 @@
           <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
         </is>
       </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>C29310</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -2537,6 +2909,16 @@
           <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
         </is>
       </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>C29311</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2590,6 +2972,16 @@
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>C29312</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2643,6 +3035,16 @@
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>C29313</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2696,6 +3098,16 @@
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>C29314</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -2753,6 +3165,16 @@
           <t>a special-order core part + optional-invoice completion (needs is_core part).</t>
         </is>
       </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>C29315</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -2810,6 +3232,16 @@
           <t>an unresolved special-order core at the invoice gate ('Cores pending' flag) — needs is_core part + receiving.</t>
         </is>
       </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>C29316</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2867,6 +3299,16 @@
           <t>resolve cores at the Create-Invoice gate -&gt; receive the cored line (needs is_core part + receiving).</t>
         </is>
       </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>C29317</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29317</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2924,6 +3366,16 @@
           <t>cancel the invoice-gate core resolution (needs is_core part + invoice gate).</t>
         </is>
       </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>C29318</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29318</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -2981,6 +3433,16 @@
           <t>special-order cores in the required-invoice receive round-trip (needs is_core part + receiving).</t>
         </is>
       </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>C29319</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3038,6 +3500,16 @@
           <t>an unresolved special-order core that exists only as a PartRequest (needs is_core part).</t>
         </is>
       </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>C29320</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -3095,6 +3567,16 @@
           <t>a part-sale WO vs service WO with cores (needs is_core part + receiving).</t>
         </is>
       </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>C29321</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29321</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3148,6 +3630,16 @@
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>C29322</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3201,6 +3693,16 @@
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>C29323</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3254,6 +3756,16 @@
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>C29324</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3307,6 +3819,16 @@
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>C29325</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3360,6 +3882,16 @@
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>C29326</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3413,6 +3945,16 @@
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>C29327</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3466,6 +4008,16 @@
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>C29328</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3519,6 +4071,16 @@
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>C29329</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -3572,6 +4134,16 @@
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>C29330</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3625,6 +4197,16 @@
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>C29331</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3678,6 +4260,16 @@
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>C29332</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3731,6 +4323,16 @@
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>C29333</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3784,6 +4386,16 @@
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>C29334</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3837,6 +4449,16 @@
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>C29335</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3890,6 +4512,16 @@
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>C29336</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3943,6 +4575,16 @@
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>C29337</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3996,6 +4638,16 @@
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>C29338</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4049,6 +4701,16 @@
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>C29339</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -4106,6 +4768,16 @@
           <t>QuickBooks sync inspection (vendor-missing PO excluded from QB).</t>
         </is>
       </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>C29340</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29340</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4159,6 +4831,16 @@
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>C29341</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4212,6 +4894,16 @@
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>C29342</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -4269,6 +4961,16 @@
           <t>reports data (Vendor Missing POs flagged 'needs vendor').</t>
         </is>
       </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>C29343</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4322,6 +5024,16 @@
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>C29439</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4375,6 +5087,16 @@
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>C29344</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4428,6 +5150,16 @@
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>C29345</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4481,6 +5213,16 @@
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>C29346</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4534,6 +5276,16 @@
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>C29347</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4587,6 +5339,16 @@
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>C29348</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4640,6 +5402,16 @@
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>C29349</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4693,6 +5465,16 @@
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>C29350</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4746,6 +5528,16 @@
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>C29351</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4799,6 +5591,16 @@
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>C29352</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4852,6 +5654,16 @@
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>C29353</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4905,6 +5717,16 @@
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>C29354</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4958,6 +5780,16 @@
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>C29355</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5011,6 +5843,16 @@
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>C29356</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5064,6 +5906,16 @@
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>C29357</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5117,6 +5969,16 @@
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>C29358</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -5174,6 +6036,16 @@
           <t>RE-VIU 2026-07-09: Bulk Receive page BUILT; this case needs a genuine cored part received on the bulk page to expose Ok/Not-OK resolution (is_core part not seedable via canned/sub-form).</t>
         </is>
       </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>C29359</t>
+        </is>
+      </c>
+      <c r="M87" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5227,6 +6099,16 @@
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>C29360</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5280,6 +6162,16 @@
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>C29361</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5333,6 +6225,16 @@
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>C29362</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5386,6 +6288,16 @@
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>C29363</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -5443,6 +6355,16 @@
           <t>receiving + inventory/catalog inspection (new PN creates inventory part + stock + Part History on receive).</t>
         </is>
       </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>C29364</t>
+        </is>
+      </c>
+      <c r="M92" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -5500,6 +6422,16 @@
           <t>receiving + inventory inspection (existing PN links to item, updates stock/cost/history).</t>
         </is>
       </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>C29365</t>
+        </is>
+      </c>
+      <c r="M93" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -5557,6 +6489,16 @@
           <t>a WO in invoiced/paid state (sell-field locking).</t>
         </is>
       </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>C29366</t>
+        </is>
+      </c>
+      <c r="M94" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -5614,6 +6556,16 @@
           <t>an invoiced/paid WO + a receive attempt (cannot receive without PN).</t>
         </is>
       </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>C29367</t>
+        </is>
+      </c>
+      <c r="M95" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -5671,6 +6623,16 @@
           <t>receiving + catalog/inventory back-end inspection (real creation/linking, not a stored string).</t>
         </is>
       </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>C29368</t>
+        </is>
+      </c>
+      <c r="M96" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5724,6 +6686,16 @@
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>C29369</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5777,6 +6749,16 @@
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>C29370</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -5830,6 +6812,16 @@
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>C29371</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5883,6 +6875,16 @@
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>C29372</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -5936,6 +6938,16 @@
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr"/>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>C29373</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -5993,6 +7005,16 @@
           <t>BATCH 6: on a deliverable WO PO the Accept Delivery gates are present (vendor set, invoice # field), but Receive 500s (BUG-11); on a vendor-missing WO PO there is no assign-vendor / PN-edit control. Happy path was proven on an INVENTORY PO in BATCH 5; the WO-PO negative sub-gates need BUG-11 fixed.</t>
         </is>
       </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>C29374</t>
+        </is>
+      </c>
+      <c r="M102" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -6046,6 +7068,16 @@
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr"/>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>C29375</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -6103,6 +7135,16 @@
           <t>QuickBooks inspection (per-vendor vendor bill + separate AP entry) — and WO-PO receive additionally blocked by BUG-11 (500).</t>
         </is>
       </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>C29376</t>
+        </is>
+      </c>
+      <c r="M104" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6156,6 +7198,16 @@
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>C29377</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6209,6 +7261,16 @@
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>C29440</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6262,6 +7324,16 @@
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>C29378</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -6319,6 +7391,16 @@
           <t>a PO where the assigned vendor already exists on the PO (Add-to-vendor merge vs keep-separate prompt).</t>
         </is>
       </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>C29379</t>
+        </is>
+      </c>
+      <c r="M108" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -6376,6 +7458,16 @@
           <t>two POs for the same WO with the same vendor (merge-POs prompt).</t>
         </is>
       </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>C29380</t>
+        </is>
+      </c>
+      <c r="M109" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -6433,6 +7525,16 @@
           <t>a vendor-missing PO + receive-enable + QB-flag-clear check after auto-assign.</t>
         </is>
       </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>C29381</t>
+        </is>
+      </c>
+      <c r="M110" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -6490,6 +7592,16 @@
           <t>invoiced/paid WO + multi-PO merge guardrail state (match-by-ID, merge scoped to same WO, receive blocked when invoiced/paid).</t>
         </is>
       </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>C29382</t>
+        </is>
+      </c>
+      <c r="M111" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -6547,6 +7659,16 @@
           <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
         </is>
       </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>C29442</t>
+        </is>
+      </c>
+      <c r="M112" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29442</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6600,6 +7722,16 @@
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>C29383</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6653,6 +7785,16 @@
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>C29384</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6706,6 +7848,16 @@
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>C29385</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6759,6 +7911,16 @@
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>C29386</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6812,6 +7974,16 @@
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>C29387</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6865,6 +8037,16 @@
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>C29388</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6918,6 +8100,16 @@
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>C29389</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -6971,6 +8163,16 @@
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>C29390</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7024,6 +8226,16 @@
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>C29391</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7077,6 +8289,16 @@
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>C29392</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -7130,6 +8352,16 @@
         </is>
       </c>
       <c r="K123" s="3" t="inlineStr"/>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>C29393</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7183,6 +8415,16 @@
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>C29394</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -7236,6 +8478,16 @@
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr"/>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>C29395</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -7289,6 +8541,16 @@
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>C29396</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7342,6 +8604,16 @@
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>C29397</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -7395,6 +8667,16 @@
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>C29398</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -7452,6 +8734,16 @@
           <t>cores + receiving in the review flow — blocked by BUG-10 (no wizard resolve step) + BUG-11 (WO-PO receive 500) + special-order cores not seedable.</t>
         </is>
       </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>C29399</t>
+        </is>
+      </c>
+      <c r="M129" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -7505,6 +8797,16 @@
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr"/>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>C29400</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29400</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -7558,6 +8860,16 @@
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>C29401</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -7611,6 +8923,16 @@
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>C29402</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7664,6 +8986,16 @@
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>C29403</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -7717,6 +9049,16 @@
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr"/>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>C29404</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -7770,6 +9112,16 @@
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>C29405</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -7823,6 +9175,16 @@
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>C29406</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -7876,6 +9238,16 @@
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>C29407</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -7929,6 +9301,16 @@
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>C29408</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -7982,6 +9364,16 @@
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>C29409</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8035,6 +9427,16 @@
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>C29410</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8088,6 +9490,16 @@
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>C29411</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8141,6 +9553,16 @@
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>C29412</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -8194,6 +9616,16 @@
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>C29413</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -8247,6 +9679,16 @@
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>C29414</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -8300,6 +9742,16 @@
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>C29415</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -8357,6 +9809,16 @@
           <t>an asset/vehicle with NO VIN so the non-review wizard prompts for VIN. BATCH 6: VIN prefills from the asset; the asset-creation flow (VIN likely required) was not reliably drivable in-harness. Needs a VIN-less asset seeded.</t>
         </is>
       </c>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>C29416</t>
+        </is>
+      </c>
+      <c r="M146" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -8410,6 +9872,16 @@
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>C29417</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -8463,6 +9935,16 @@
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>C29418</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -8516,6 +9998,16 @@
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>C29419</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -8573,6 +10065,16 @@
           <t>BATCH 6: blocked by BUG-11 (WO-PO receive 500) and no assign-vendor UI on the reachable receive surface.</t>
         </is>
       </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>C29420</t>
+        </is>
+      </c>
+      <c r="M150" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -8626,6 +10128,16 @@
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>C29421</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -8679,6 +10191,16 @@
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>C29422</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -8736,6 +10258,16 @@
           <t>RE-VIU 2026-07-09: Bulk Receive field-locking BUILT (qty/cost/sell editable verified); the sell-lock-after-invoiced/paid clause needs an invoiced/paid WO to drive.</t>
         </is>
       </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>C29423</t>
+        </is>
+      </c>
+      <c r="M153" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -8789,6 +10321,16 @@
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>C29424</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -8846,6 +10388,16 @@
           <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
         </is>
       </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>C29425</t>
+        </is>
+      </c>
+      <c r="M155" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -8903,6 +10455,16 @@
           <t>FRESH VIU 2026-07-10: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted through simple-complete 201). Part-History LOG surface BLOCKED-ENV: GET /api/inventory/parts/history -&gt; 500; /parts/inventory/{id} detail page crashes ('page is totaled'); other history endpoints 404/405 (see bugs-log OBS-6). QuickBooks-integrity leg needs QB access.</t>
         </is>
       </c>
+      <c r="L156" s="4" t="inlineStr">
+        <is>
+          <t>C29426</t>
+        </is>
+      </c>
+      <c r="M156" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -8956,6 +10518,16 @@
         </is>
       </c>
       <c r="K157" s="3" t="inlineStr"/>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>C29427</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29427</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -9013,6 +10585,16 @@
           <t>QuickBooks / inventory back-end inspection (receive -&gt; Delivery -&gt; Vendor Bill -&gt; QBO) — likely needs dev/QB access.</t>
         </is>
       </c>
+      <c r="L158" s="4" t="inlineStr">
+        <is>
+          <t>C29428</t>
+        </is>
+      </c>
+      <c r="M158" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -9070,6 +10652,16 @@
           <t>QuickBooks / inventory inspection (vendorless/no-PN part = zero inventory interaction) — likely needs dev/QB access.</t>
         </is>
       </c>
+      <c r="L159" s="4" t="inlineStr">
+        <is>
+          <t>C29429</t>
+        </is>
+      </c>
+      <c r="M159" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -9127,6 +10719,16 @@
           <t>QuickBooks inspection (Vendor-Missing POs excluded from QB until vendor + PN) — likely needs dev/QB access.</t>
         </is>
       </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>C29430</t>
+        </is>
+      </c>
+      <c r="M160" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -9184,6 +10786,16 @@
           <t>QuickBooks inspection (cost-at-completion to avoid $0-cost margins) — likely needs dev/QB access.</t>
         </is>
       </c>
+      <c r="L161" s="4" t="inlineStr">
+        <is>
+          <t>C29431</t>
+        </is>
+      </c>
+      <c r="M161" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -9241,6 +10853,16 @@
           <t>QuickBooks inspection (Journal Entry / Inventory sync fires on invoice creation) — likely needs dev/QB access.</t>
         </is>
       </c>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>C29432</t>
+        </is>
+      </c>
+      <c r="M162" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -9298,6 +10920,16 @@
           <t>Inventory Part History inspection for any part that becomes inventory-tracked — likely needs dev/QB access.</t>
         </is>
       </c>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>C29433</t>
+        </is>
+      </c>
+      <c r="M163" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -9355,6 +10987,8 @@
           <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
         </is>
       </c>
+      <c r="L164" s="4" t="inlineStr"/>
+      <c r="M164" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -7935,7 +7935,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
+          <t>Verify the completion action reads 'Send To Review' when Require Review is on</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>Q8, Q4 | R5 / R8 (distinct Reviewed state)</t>
+          <t>Q8, Q4 | R5 / R8 (direct sign-off, no separate Complete)</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
+          <t>Milos answers Open Question Q7 — Optional review-note field absent — descope or bug?</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify all lines must be approved before Send To Review (the 'Send To Review' action is disabled until every line is approved)</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -2787,134 +2787,126 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-21</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Completion — Line approval gate</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Verify on a required-invoice work order an unapproved line disables the Complete Work Order button with a tooltip</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>S4-R8 / Key Decision (all lines approved) / S3-R9</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>C29310</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>SF-COMP-22</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Completion — Line approval gate</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Verify a manually unapproved line disables the required-invoice Complete Work Order button with a tooltip even when Auto-approve is ON</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>S4-R8 / Key Decision (holds regardless of Auto-approve)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>C29311</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
         </is>
@@ -11063,7 +11055,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -11093,7 +11085,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -11189,7 +11181,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -11234,7 +11226,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C19" s="6" t="inlineStr"/>
     </row>
@@ -11273,7 +11265,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 38 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 36 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="6" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Blocked-Env</t>
+          <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1145,67 +1145,63 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SF-SET-10</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Work Order Settings</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Verify a settings change applies to future completions only and not to already-completed work orders</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: toggle the setting and confirm the downstream behaviour.</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>S1-R9 (future completions only, never retroactive)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>C29284</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29284</t>
         </is>
@@ -1859,7 +1855,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Blocked-Env</t>
+          <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3119,7 +3115,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -3186,7 +3182,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -3253,7 +3249,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -3320,7 +3316,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -3387,7 +3383,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -3454,7 +3450,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -3521,7 +3517,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -4915,7 +4911,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Deviation</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -5990,7 +5986,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -6309,7 +6305,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -6376,7 +6372,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -6443,7 +6439,7 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -6493,67 +6489,63 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>SF-PNFIX-05</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Verify a part cannot be received without a part number, a vendor (for vendor-missing) and a cost / sell price, even on an invoiced/paid WO</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
         <is>
           <t>S10 Negative / S13-R6 / S13-R7</t>
         </is>
       </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K95" s="4" t="inlineStr">
-        <is>
-          <t>an invoiced/paid WO + a receive attempt (cannot receive without PN).</t>
-        </is>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
         <is>
           <t>C29367</t>
         </is>
       </c>
-      <c r="M95" s="4" t="inlineStr">
+      <c r="M95" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
         </is>
@@ -6577,7 +6569,7 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -6896,7 +6888,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -6942,67 +6934,63 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>SF-RCV-06</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Verify Accept Delivery receive gates: vendor set, part number entered, cost / sell price entered, vendor invoice # captured</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
-        </is>
-      </c>
-      <c r="I102" s="4" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>S12-R2 / S13-R6 / S13-R7</t>
         </is>
       </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K102" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: on a deliverable WO PO the Accept Delivery gates are present (vendor set, invoice # field), but Receive 500s (BUG-11); on a vendor-missing WO PO there is no assign-vendor / PN-edit control. Happy path was proven on an INVENTORY PO in BATCH 5; the WO-PO negative sub-gates need BUG-11 fixed.</t>
-        </is>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
         <is>
           <t>C29374</t>
         </is>
       </c>
-      <c r="M102" s="4" t="inlineStr">
+      <c r="M102" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
         </is>
@@ -7026,7 +7014,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
@@ -7345,7 +7333,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -7412,7 +7400,7 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -7462,67 +7450,63 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>SF-VEND-04</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a different vendor with no collision auto-assigns and clears the QB flag, and Receive enables only once the part number and cost / sell price are also present</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G110" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
-        </is>
-      </c>
-      <c r="I110" s="4" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>S13-R4 / S13-R5 / S13-R6 / S13-R7</t>
         </is>
       </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K110" s="4" t="inlineStr">
-        <is>
-          <t>a vendor-missing PO + receive-enable + QB-flag-clear check after auto-assign.</t>
-        </is>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
         <is>
           <t>C29381</t>
         </is>
       </c>
-      <c r="M110" s="4" t="inlineStr">
+      <c r="M110" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
         </is>
@@ -7546,7 +7530,7 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -7596,67 +7580,63 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>SF-VEND-06</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Verify a part cannot be received until a missing cost / sell price is entered</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G112" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
-        </is>
-      </c>
-      <c r="I112" s="4" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>S13-R7</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K112" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr">
         <is>
           <t>C29442</t>
         </is>
       </c>
-      <c r="M112" s="4" t="inlineStr">
+      <c r="M112" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29442</t>
         </is>
@@ -8499,7 +8479,7 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -8688,7 +8668,7 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -8755,7 +8735,7 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Blocked-Env</t>
+          <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -9007,7 +8987,7 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -9763,7 +9743,7 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -10002,67 +9982,63 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="4" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-06</t>
         </is>
       </c>
-      <c r="B150" s="4" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C150" s="4" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
         </is>
       </c>
-      <c r="D150" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G150" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I150" s="4" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>S10 / S12-R2 / S13-R6 / S13-R7</t>
         </is>
       </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K150" s="4" t="inlineStr">
-        <is>
-          <t>BATCH 6: blocked by BUG-11 (WO-PO receive 500) and no assign-vendor UI on the reachable receive surface.</t>
-        </is>
-      </c>
-      <c r="L150" s="4" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
         <is>
           <t>C29420</t>
         </is>
       </c>
-      <c r="M150" s="4" t="inlineStr">
+      <c r="M150" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
         </is>
@@ -10212,7 +10188,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -10325,67 +10301,63 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="4" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-11</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>Verify an unapproved line blocks completion — required-invoice shows a disabled Complete button with a tooltip; other flows show the approve-line error</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I155" s="4" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Verify an unapproved line disables the Complete Work Order button with a tooltip (regardless of the Require Vendor Invoice Number setting)</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
         <is>
           <t>S4-R8 / S3-R9 / Key Decision (line approval)</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K155" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
-      <c r="L155" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
         <is>
           <t>C29425</t>
         </is>
       </c>
-      <c r="M155" s="4" t="inlineStr">
+      <c r="M155" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
         </is>
@@ -10409,7 +10381,7 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -10476,7 +10448,7 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Blocked-Env</t>
+          <t>VIU-observed-awaiting-Milos</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
@@ -10606,7 +10578,7 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -10874,7 +10846,7 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
@@ -11055,7 +11027,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -11085,7 +11057,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -11181,7 +11153,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -11196,7 +11168,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -11226,7 +11198,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C19" s="6" t="inlineStr"/>
     </row>
@@ -11265,7 +11237,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 36 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 29 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="6" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M164"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Verify a settings change applies to future completions only and not to already-completed work orders</t>
+          <t>Verify a settings change applies to future completions and to a completed work order when it is reopened, but not retroactively to work orders left completed</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>S1-R9 (future completions only, never retroactive)</t>
+          <t>S1-R9 (future completions + apply on reopen; never retroactive to WOs left completed)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>S2-R6 / S2 AC (re-open returns to Approved)</t>
+          <t>S2-R6 / S2 AC (re-open returns to Approved); S16-R12 (auto-complete on re-resolve)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify a waiting special-order core disables Complete Without Receiving (with a tooltip) and offers Receive Parts</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>S3-C2</t>
+          <t>S3-C2 (updated per design #4 core-block)</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -6288,134 +6288,126 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>SF-PNFIX-02</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>S10 AC (new number)</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K92" s="4" t="inlineStr">
-        <is>
-          <t>receiving + inventory/catalog inspection (new PN creates inventory part + stock + Part History on receive).</t>
-        </is>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Verify a NEW part number can be entered and saved so the part can be received</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>S10-R1 (PN mandatory to receive); S10-R2 struck (first-class part not required in v1)</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
         <is>
           <t>C29364</t>
         </is>
       </c>
-      <c r="M92" s="4" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>SF-PNFIX-03</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t>S10 AC (existing number)</t>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t>receiving + inventory inspection (existing PN links to item, updates stock/cost/history).</t>
-        </is>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Verify an EXISTING part number can be entered so the part can be received, without overwriting the item's description or category</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>S10-R1 (PN mandatory to receive); S10-R2 struck (linking to first-class item not required in v1)</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
         <is>
           <t>C29365</t>
         </is>
       </c>
-      <c r="M93" s="4" t="inlineStr">
+      <c r="M93" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
         </is>
@@ -6552,67 +6544,63 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>SF-PNFIX-06</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr">
-        <is>
-          <t>S10 Technical guardrails</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K96" s="4" t="inlineStr">
-        <is>
-          <t>receiving + catalog/inventory back-end inspection (real creation/linking, not a stored string).</t>
-        </is>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Verify the inline part-number save persists and enables receiving</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>S10-R1 + S10 technical guardrails; S10-R2 struck (catalog/inventory creation not required in v1)</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
         <is>
           <t>C29368</t>
         </is>
       </c>
-      <c r="M96" s="4" t="inlineStr">
+      <c r="M96" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
         </is>
@@ -7874,7 +7862,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R1 + S16-R12</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -8126,7 +8114,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>R5 / R6</t>
+          <t>R5 / R6 + S16-R12</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -8315,7 +8303,7 @@
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>Q8, Q4 | R5 / R8 (direct sign-off, no separate Complete)</t>
+          <t>Q8, Q4 | R5 / R8 (direct sign-off, no separate Complete) + S16-R12</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr">
@@ -8504,7 +8492,7 @@
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>Q8 | R8</t>
+          <t>Q8 | R8 + S16-R12</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr">
@@ -10829,67 +10817,63 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="4" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>SF-QB-08</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F163" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G163" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H163" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I163" s="4" t="inlineStr">
-        <is>
-          <t>§5 invariant 3</t>
-        </is>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K163" s="4" t="inlineStr">
-        <is>
-          <t>Inventory Part History inspection for any part that becomes inventory-tracked — likely needs dev/QB access.</t>
-        </is>
-      </c>
-      <c r="L163" s="4" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Verify Part History is preserved for a part that is genuinely inventory-tracked</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>§5 invariant 3 (rescoped after S10-R2 strike)</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
         <is>
           <t>C29433</t>
         </is>
       </c>
-      <c r="M163" s="4" t="inlineStr">
+      <c r="M163" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
         </is>
@@ -10953,6 +10937,455 @@
       </c>
       <c r="L164" s="4" t="inlineStr"/>
       <c r="M164" s="4" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>SF-AUTO-01</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Verify resolving the last open line by completing a single line auto-completes the work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>S16-R12 (a) single line</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>C29461</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29461</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>SF-AUTO-02</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Verify resolving the last open lines in bulk (several at once) auto-completes the work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>S16-R12 (b) bulk</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>C29462</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29462</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>SF-AUTO-03</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Verify a split that leaves a work order fully resolved auto-completes that work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>S16-R12 (c) split</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>C29463</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29463</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>SF-AUTO-04</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>Verify deleting a line so the remaining lines are all resolved auto-completes the work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
+          <t>S16-R12 (d) delete line</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
+      <c r="L168" s="4" t="inlineStr">
+        <is>
+          <t>C29464</t>
+        </is>
+      </c>
+      <c r="M168" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29464</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>SF-AUTO-05</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Verify that with Require Review on, resolving the last open line routes the work order to Ready for Review instead of auto-completing</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>S16-R12 review ON</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>C29465</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29465</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>SF-AUTO-06</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>Verify a clock-out that finishes the last line routes the work order to Ready for Review even when Require Review is off</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>S16-R13 clock-out exception</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>C29466</t>
+        </is>
+      </c>
+      <c r="M170" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29466</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>SF-AUTO-07</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>API — Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Verify the work order status transitions on the backend when the last open line is resolved (auto-Complete when review off, Ready for Review when review on)</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>S16-R12 backend status transition</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>C29467</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29467</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10994,7 +11427,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C3" s="6" t="n"/>
     </row>
@@ -11027,7 +11460,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -11057,7 +11490,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -11102,7 +11535,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C11" s="6" t="inlineStr"/>
     </row>
@@ -11153,7 +11586,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -11168,7 +11601,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -11198,7 +11631,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C19" s="6" t="inlineStr"/>
     </row>
@@ -11237,7 +11670,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 29 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 27 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="6" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -71,12 +71,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,6 +106,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -113,9 +116,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6859,63 +6859,63 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>SF-RCV-05</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>VIU-observed-awaiting-Milos</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Verify vendorless / no-part-number Work Order parts appear and can be received on the Receive (Accept Delivery) screen, and the Vendor Missing group sits per the agreed rule (top on Bulk Receive, bottom on the Receive screen)</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Deviation</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>MILOS ANSWER</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>Milos (Product Owner)</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>Q11 | S12-R1</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr"/>
-      <c r="L101" s="3" t="inlineStr">
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>BUG/RULING</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Dev / PO ruling</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>Dev fix: on the Receive (Accept Delivery) screen the Vendor Missing group must move to the BOTTOM (Milos Round-3 2026-07-16). Live VIU 2026-07-16: it currently leads at the TOP (Bulk Receive top = correct).</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>S12-R1 (+ Milos Round-3 2026-07-16)</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr"/>
+      <c r="L101" s="5" t="inlineStr">
         <is>
           <t>C29373</t>
         </is>
       </c>
-      <c r="M101" s="3" t="inlineStr">
+      <c r="M101" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
         </is>
@@ -6985,63 +6985,63 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>SF-RCV-07</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>VIU-observed-awaiting-Milos</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Verify the multi-vendor '+N' indicator and the Vendor Missing group position on the receiving screens</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Deviation</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>MILOS ANSWER</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>Milos (Product Owner)</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>Q11 | S12-R3</t>
-        </is>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr"/>
-      <c r="L103" s="3" t="inlineStr">
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>BUG/RULING</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Dev / PO ruling</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>Dev fix: same Vendor-Missing-group placement deviation as SF-RCV-05 — the Receive (Accept Delivery) screen shows the group at the TOP, should be BOTTOM (Milos Round-3 2026-07-16). '+N' indicator verified on the PO list.</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>S12-R3 (+ Milos Round-3 2026-07-16)</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr"/>
+      <c r="L103" s="5" t="inlineStr">
         <is>
           <t>C29375</t>
         </is>
       </c>
-      <c r="M103" s="3" t="inlineStr">
+      <c r="M103" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
         </is>
@@ -8706,63 +8706,67 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>SF-REV-15</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>Verify the Require Review default for new vs existing orgs matches the agreed cohort rule</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>VIU-observed-awaiting-Milos</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Verify Require Review Before Completion starts ON for a brand-new organization, and existing organizations keep today's behavior</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>MILOS ANSWER</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="inlineStr">
-        <is>
-          <t>Milos (Product Owner)</t>
-        </is>
-      </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q1 — Require-review default cohort rule + new-org preset.</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="inlineStr">
-        <is>
-          <t>Q1 | R Open (default)</t>
-        </is>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K130" s="3" t="inlineStr"/>
-      <c r="L130" s="3" t="inlineStr">
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>Env/provisioning: a freshly-provisioned organization (from backend/admin onboarding) to observe the new-org Require Review Before Completion ON default (Milos Round-3 2026-07-16). Not self-serviceable in shared QA — org-creation endpoints return 405/404; shared org's toggle reflects prior test toggling.</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t>R Open (default) - Milos Round-3 2026-07-16: ON for new orgs</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>Milos Round-3 2026-07-16: Require Review Before Completion starts ON for new orgs. Characterized env blocker (Rule 14 self-serve attempted): a brand-new org cannot be provisioned in shared QA (POST /api/organizations 405, /organizations/create 404, /register 405); shared org's requireReview reflects prior toggling. Needs a freshly-provisioned org from backend/admin onboarding to observe the ON default.</t>
+        </is>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
         <is>
           <t>C29400</t>
         </is>
       </c>
-      <c r="M130" s="3" t="inlineStr">
+      <c r="M130" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29400</t>
         </is>
@@ -11407,47 +11411,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Simple Flow — Blockers Tracker · Summary</t>
         </is>
       </c>
-      <c r="B1" s="6" t="n"/>
-      <c r="C1" s="6" t="n"/>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n"/>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Total authored cases</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="7" t="n">
         <v>170</v>
       </c>
-      <c r="C3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Blocker category</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
@@ -11469,15 +11473,15 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>BLOCKED — DEV NOT BUILT</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Dev team</t>
         </is>
@@ -11490,7 +11494,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -11505,7 +11509,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -11514,15 +11518,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>BLOCKED — BUG/RULING</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="B10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Dev / PO ruling</t>
         </is>
@@ -11537,12 +11541,12 @@
       <c r="B11" s="10" t="n">
         <v>170</v>
       </c>
-      <c r="C11" s="6" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -11555,12 +11559,12 @@
           <t>Count</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
+      <c r="C13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -11588,7 +11592,7 @@
       <c r="B16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>admin+tech + normal data; just needs another VIU pass (no new inputs).</t>
         </is>
@@ -11601,24 +11605,24 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>needs a data state not seedable via the app (see per-case detail).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>needs-account</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>needs a role account we don't have (see per-case detail).</t>
         </is>
@@ -11631,14 +11635,14 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="C19" s="6" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -11646,8 +11650,8 @@
           <t>WHAT TO SEND ME NEXT (to unblock each batch)</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -11655,12 +11659,12 @@
           <t>• Milos's answers to the 11 Open Questions</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>unblocks 13 cases (all the MILOS-ANSWER rows). Send the filled-in OpenQuestions-for-Milos sheet.</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>unblocks 10 cases (all the MILOS-ANSWER rows). Send the filled-in OpenQuestions-for-Milos sheet.</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -11668,12 +11672,12 @@
           <t>• Fresh QA cookies for sv7301 (admin + tech) + seeded test data</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>unblocks the bulk of the 27 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>unblocks the bulk of the 28 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -11681,12 +11685,12 @@
           <t>• A 2nd/3rd role account (Office, Service Manager, Foreman) — some WITHOUT 'See Financial Data'</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>unblocks SF-PERM-09 and SF-PERM-10 (per-role completion + vendorless-add gate).</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
+      <c r="C24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -11694,12 +11698,12 @@
           <t>• A dev/PO ruling on FE-only BE enforcement + the missing reviewer!=completer rule (resolve SV-8183 'BE enforces' vs SV-7864 atom-collapse)</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>finalizes the 0 BUG/RULING cases.</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n"/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>finalizes the 2 BUG/RULING cases.</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -3098,134 +3098,126 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-03</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Core parts — Completion modal</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Verify a Resolve cores screen appears before the Receive parts / Complete without receiving choice and only an undecided core blocks completing</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>S18 C-R1/C-R4</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>spec `_4` Story 18 C-R1/C-R4 (resolve screen + gate-on-undecided) — needs the SV-8353 build + a dev-seeded special-order core.</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>C29315</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-04</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Core parts — Invoice gate</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Verify the 'Cores pending' indication reflects only undecided special-order cores (a decided core clears it)</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>S18 C-R4</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>spec `_4` Story 18 C-R4 ('Cores pending' = undecided-only) — needs the SV-8353 build + a dev-seeded core.</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>C29316</t>
         </is>
       </c>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
         </is>
@@ -3429,67 +3421,63 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-11</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Core parts — Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Verify the Resolve cores screen lists every un-received vendor core with part info, core charge and OK / Not OK, plus an invoice-accuracy message</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>S18 C-R1</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>Story 18 C-R1 resolve screen — needs the SV-8353 build + a dev-seeded special-order core.</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>C29892</t>
         </is>
       </c>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29892</t>
         </is>
@@ -3898,67 +3886,63 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-18</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>API — Core Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>API: Verify POST /api/work-orders/{id}/pre-resolve-cores persists the core decision on the part request with no side-effect records</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>S18 C-R2 / technical plan</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>API POST /api/work-orders/{id}/pre-resolve-cores — endpoint from the SV-8353 tech plan; probe for existence first.</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>C29899</t>
         </is>
       </c>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29899</t>
         </is>
@@ -12426,7 +12410,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -12456,7 +12440,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -12567,7 +12551,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -12597,7 +12581,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C19" s="7" t="inlineStr"/>
     </row>
@@ -12636,7 +12620,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 46 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 42 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -3224,134 +3224,126 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-07</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Core parts — Required invoice (Story 4)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Verify the required-invoice flow asks to resolve special-order cores FIRST and then to receive them</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>S18 C-R6</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>spec `_4` Story 18 C-R6 (required flow: resolve FIRST then receive) — needs the SV-8353 build + a dev-seeded core.</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>C29319</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-08</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Core parts — Guardrail</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Verify the completion and invoice gates detect an undecided special-order core that exists only as a requested part</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>S18 C-R2/C-R4 (guardrail)</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>spec `_4` Story 18 C-R2/C-R4 (gate detects an undecided request-only core) — needs the SV-8353 build + a dev-seeded core.</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>C29320</t>
         </is>
       </c>
-      <c r="M45" s="4" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
         </is>
@@ -3484,201 +3476,189 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-12</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Core parts — Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Verify marking a core Not OK immediately adds the core charge to the work order total and customer invoice, while OK adds no charge</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>S18 C-R3</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>Story 18 C-R3 charge-follows-decision — needs the SV-8353 build + a dev-seeded special-order core.</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>C29893</t>
         </is>
       </c>
-      <c r="M48" s="4" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29893</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-13</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Core parts — Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Verify completion and invoice creation are blocked only while a core is undecided — a decided core does not block</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>S18 C-R4</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>Story 18 C-R4 gate-on-undecided — needs the SV-8353 build + a dev-seeded special-order core.</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>C29894</t>
         </is>
       </c>
-      <c r="M49" s="4" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29894</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-14</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Core parts — Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Verify receiving a pre-resolved core auto-applies the saved decision: OK creates exactly one vendor return, Not OK creates none, the invoice never changes, retries create no duplicates</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>S18 C-R5</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>Story 18 C-R5 auto-apply/idempotency — needs the SV-8353 build + a dev-seeded core + receive.</t>
-        </is>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>C29895</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29895</t>
         </is>
@@ -3752,67 +3732,63 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>SF-CORE-16</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Core parts — Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Verify the Lines tab shows the core decision state before and after receive: 'Core decision pending', 'Core OK — return to vendor, no charge', 'Core Not OK — customer charged'</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>S18 C-R9</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>Story 18 C-R9 Lines-tab states — needs the SV-8353 build + a dev-seeded core.</t>
-        </is>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>C29897</t>
         </is>
       </c>
-      <c r="M52" s="4" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29897</t>
         </is>
@@ -6170,67 +6146,63 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>SF-BULK-06</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Verify Bulk Receive field editability: quantity editable (partial receive), cost editable ONLY when it is $0, sell locks after the WO is invoiced/paid</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
-        </is>
-      </c>
-      <c r="I90" s="4" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
         <is>
           <t>S8-R7 / S10-R3</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K90" s="4" t="inlineStr">
-        <is>
-          <t>Δ14 re-VIU: can a NON-ZERO cost be edited on Bulk Receive? ($0-only rule; if editable → deviation until dev ships).</t>
-        </is>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
         <is>
           <t>C29355</t>
         </is>
       </c>
-      <c r="M90" s="4" t="inlineStr">
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
         </is>
@@ -6426,67 +6398,63 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>SF-BULK-10</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Verify a pre-resolved core's decision is applied automatically at receive with no re-prompt, and core-only partial receive is supported</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
         <is>
           <t>S18 C-R5</t>
         </is>
       </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t>spec `_4` Story 18 C-R5 (pre-resolved decision auto-applies at receive, no re-prompt) — needs the SV-8353 build + a dev-seeded core received on the bulk page.</t>
-        </is>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
         <is>
           <t>C29359</t>
         </is>
       </c>
-      <c r="M94" s="4" t="inlineStr">
+      <c r="M94" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
         </is>
@@ -6560,201 +6528,189 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>SF-INV-01</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Verify each vendor group has an invoice number field under the vendor name, available only when at least one PO of that vendor is selected (no Apply button)</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
         <is>
           <t>S9-R1</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K96" s="4" t="inlineStr">
-        <is>
-          <t>Δ13 re-VIU: is the 'Apply to selected POs' button still present? (2026-07-13 it WAS — likely build deviation until dev removes it).</t>
-        </is>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
         <is>
           <t>C29360</t>
         </is>
       </c>
-      <c r="M96" s="4" t="inlineStr">
+      <c r="M96" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>SF-INV-02</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Verify a typed invoice number fills only the selected POs of that vendor with no Apply click, still editable per PO</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
         <is>
           <t>S9-R2</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K97" s="4" t="inlineStr">
-        <is>
-          <t>Δ13 re-VIU: typed invoice # fills selected POs with no Apply click (old Apply-button behavior was live 2026-07-13).</t>
-        </is>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
         <is>
           <t>C29361</t>
         </is>
       </c>
-      <c r="M97" s="4" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>SF-INV-03</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Verify the vendor invoice number field is scoped per vendor, absent for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>S9-R3</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K98" s="4" t="inlineStr">
-        <is>
-          <t>Δ13 re-VIU: per-vendor scoping + vendorless group shows NO invoice-number field.</t>
-        </is>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
         <is>
           <t>C29362</t>
         </is>
       </c>
-      <c r="M98" s="4" t="inlineStr">
+      <c r="M98" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
         </is>
@@ -7911,67 +7867,63 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>SF-RCV-13</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless part can be assigned a vendor / merged into the single-part receive on the spot, reusing the same invoice number</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>S12-R6</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K117" s="4" t="inlineStr">
-        <is>
-          <t>S12-R6 assign/merge vendorless into the receive reusing the invoice # — seedable; may not be built yet.</t>
-        </is>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
         <is>
           <t>C29903</t>
         </is>
       </c>
-      <c r="M117" s="4" t="inlineStr">
+      <c r="M117" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29903</t>
         </is>
@@ -8435,67 +8387,63 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>SF-VEND-08</t>
         </is>
       </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>Verify the part number stays editable via the edit icon after entry until the part is received or the work order is invoiced/paid</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G125" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
-        </is>
-      </c>
-      <c r="I125" s="4" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
         <is>
           <t>S13-R8 (SV-8343)</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K125" s="4" t="inlineStr">
-        <is>
-          <t>S13-R8 part-number re-editable (edit icon) until received/invoiced-paid — seedable.</t>
-        </is>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr">
         <is>
           <t>C29905</t>
         </is>
       </c>
-      <c r="M125" s="4" t="inlineStr">
+      <c r="M125" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29905</t>
         </is>
@@ -9577,67 +9525,63 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="4" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>SF-REV-14</t>
         </is>
       </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>Verify cores are decided before receiving ahead of Send to Review, and invoicing stays blocked until Reviewed and every core is decided</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G143" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
-        </is>
-      </c>
-      <c r="I143" s="4" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
         <is>
           <t>S18 / Story 16 core paragraph</t>
         </is>
       </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K143" s="4" t="inlineStr">
-        <is>
-          <t>spec `_4` Story 18 (cores pre-resolved before receiving before Send To Review) — needs the SV-8353 build + a dev-seeded core.</t>
-        </is>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
         <is>
           <t>C29399</t>
         </is>
       </c>
-      <c r="M143" s="4" t="inlineStr">
+      <c r="M143" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
         </is>
@@ -12410,7 +12354,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -12440,7 +12384,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -12536,7 +12480,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -12551,7 +12495,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -12581,7 +12525,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C19" s="7" t="inlineStr"/>
     </row>
@@ -12620,7 +12564,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 42 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 28 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -3682,7 +3682,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -5764,67 +5764,63 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>SF-POSEL-07</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Verify part-sale-originated POs appear in the PO list and are selectable like work-order POs</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>S7 AC (part-sale POs) + §8 Part Sales — confirmed</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K84" s="4" t="inlineStr">
-        <is>
-          <t>Δ15 part-sale PO on the PO list + multi-select — seed a Part Sale with a vendor part (Rule 14).</t>
-        </is>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
         <is>
           <t>C29906</t>
         </is>
       </c>
-      <c r="M84" s="4" t="inlineStr">
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29906</t>
         </is>
@@ -6461,67 +6457,63 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>SF-BULK-11</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Verify a part-sale-originated PO can be received on the Bulk Receive page like a work-order PO</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
         <is>
           <t>S8 AC (part-sale POs) + §8 Part Sales — confirmed</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K95" s="4" t="inlineStr">
-        <is>
-          <t>Δ15 part-sale PO receivable on Bulk Receive — seed a Part Sale with a vendor part.</t>
-        </is>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
         <is>
           <t>C29907</t>
         </is>
       </c>
-      <c r="M95" s="4" t="inlineStr">
+      <c r="M95" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29907</t>
         </is>
@@ -8320,67 +8312,63 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>SF-VEND-07</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>Verify an assigned vendor stays changeable via the same dropdown until the part is received or the work order is invoiced/paid</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G124" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
-        </is>
-      </c>
-      <c r="I124" s="4" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
         <is>
           <t>S13-R8 (SV-8343)</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K124" s="4" t="inlineStr">
-        <is>
-          <t>S13-R8 vendor re-changeable until received/invoiced-paid — seedable (invoiced/paid leg may stay env-blocked).</t>
-        </is>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
         <is>
           <t>C29904</t>
         </is>
       </c>
-      <c r="M124" s="4" t="inlineStr">
+      <c r="M124" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29904</t>
         </is>
@@ -11783,7 +11771,7 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
@@ -12354,7 +12342,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -12384,7 +12372,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -12480,7 +12468,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -12525,7 +12513,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C19" s="7" t="inlineStr"/>
     </row>
@@ -12564,7 +12552,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>unblocks the bulk of the 28 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
+          <t>unblocks the bulk of the 25 VIU-PENDING (QA) cases (cores, receiving, vendor, validation round-trips).</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10525,139 +10525,119 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>SF-VAL-01</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Verify completion is blocked when required mileage is missing</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>S2-R2 / S3-R3 / S4-R3</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K159" s="2" t="inlineStr"/>
-      <c r="L159" s="2" t="inlineStr">
-        <is>
-          <t>C29415</t>
-        </is>
-      </c>
-      <c r="M159" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
-        </is>
-      </c>
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>SF-PERM-11</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>Verify a Vendor &amp; Order Management View-only user cannot receive purchase orders by any path on the Bulk Receive screen</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>VIU-Deviation</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>BUG/RULING</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>Dev / PO ruling</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>Dev fix (SV-8515, Ready-to-Fix): a Vendor &amp; Order Mgmt View-only (Office) user has the per-PO Receive button correctly hidden, but the multi-select 'Receive Selected' route currently EXPOSES the editable /bulk-receive screen (FE-exposure defect). Backend blocks the actual receive (accept -&gt; 403), so no data bypass. FE route guard should require Vendor &amp; Order Mgmt: Create &amp; Edit to reach Bulk Receive.</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>§9.1 Bulk Receive gate / §9.2 Office footnote-4</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr"/>
+      <c r="L159" s="5" t="inlineStr"/>
+      <c r="M159" s="5" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="4" t="inlineStr">
-        <is>
-          <t>SF-VAL-02</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I160" s="4" t="inlineStr">
-        <is>
-          <t>S15-R2 / S3-R3 / S4-R3</t>
-        </is>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K160" s="4" t="inlineStr">
-        <is>
-          <t>an asset/vehicle with NO VIN so the non-review wizard prompts for VIN. BATCH 6: VIN prefills from the asset; the asset-creation flow (VIN likely required) was not reliably drivable in-harness. Needs a VIN-less asset seeded.</t>
-        </is>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>C29416</t>
-        </is>
-      </c>
-      <c r="M160" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
-        </is>
-      </c>
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>SF-PERM-12</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Verify a no-access role (Time Clock) cannot edit, cancel or change the vendor of a work order part from the part menu</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>§9.2 Time Clock part-actions</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>SF-VAL-03</t>
+          <t>SF-VAL-01</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -10667,7 +10647,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
+          <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -10697,7 +10677,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>S3-R3 / S4-R3</t>
+          <t>S2-R2 / S3-R3 / S4-R3</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
@@ -10708,82 +10688,86 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>C29417</t>
+          <t>C29415</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>SF-VAL-04</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>SF-VAL-02</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t>TS-R4</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="inlineStr">
-        <is>
-          <t>C29418</t>
-        </is>
-      </c>
-      <c r="M162" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>S15-R2 / S3-R3 / S4-R3</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>an asset/vehicle with NO VIN so the non-review wizard prompts for VIN. BATCH 6: VIN prefills from the asset; the asset-creation flow (VIN likely required) was not reliably drivable in-harness. Needs a VIN-less asset seeded.</t>
+        </is>
+      </c>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>C29416</t>
+        </is>
+      </c>
+      <c r="M162" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-VAL-03</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -10793,7 +10777,7 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -10823,7 +10807,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>S3-R3 / S4-R5 / §4</t>
+          <t>S3-R3 / S4-R3</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
@@ -10834,19 +10818,19 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>C29419</t>
+          <t>C29417</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>SF-VAL-06</t>
+          <t>SF-VAL-04</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -10856,7 +10840,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
+          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -10886,7 +10870,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>S10 / S12-R2 / S13-R6 / S13-R7</t>
+          <t>TS-R4</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -10897,19 +10881,19 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>C29420</t>
+          <t>C29418</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>SF-VAL-07</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -10919,7 +10903,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -10949,7 +10933,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>S3-R3 / S4-R5 / §4</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -10960,19 +10944,19 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>C29421</t>
+          <t>C29419</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>SF-VAL-08</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -10982,7 +10966,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+          <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -11012,7 +10996,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>S3-R9 (idempotency)</t>
+          <t>S10 / S12-R2 / S13-R6 / S13-R7</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -11023,86 +11007,82 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>C29422</t>
+          <t>C29420</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>SF-VAL-09</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>SF-VAL-07</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I167" s="4" t="inlineStr">
-        <is>
-          <t>S8-R7 / §4 field locking</t>
-        </is>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K167" s="4" t="inlineStr">
-        <is>
-          <t>RE-VIU 2026-07-09: Bulk Receive field-locking BUILT (qty/cost/sell editable verified); the sell-lock-after-invoiced/paid clause needs an invoiced/paid WO to drive.</t>
-        </is>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>C29423</t>
-        </is>
-      </c>
-      <c r="M167" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>C29421</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>SF-VAL-10</t>
+          <t>SF-VAL-08</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -11112,7 +11092,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+          <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -11142,7 +11122,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>S9-R3 / §4 (uniqueness relaxed)</t>
+          <t>S3-R9 (idempotency)</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -11153,212 +11133,212 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
+          <t>C29422</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>SF-VAL-09</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>S8-R7 / §4 field locking</t>
+        </is>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>RE-VIU 2026-07-09: Bulk Receive field-locking BUILT (qty/cost/sell editable verified); the sell-lock-after-invoiced/paid clause needs an invoiced/paid WO to drive.</t>
+        </is>
+      </c>
+      <c r="L169" s="4" t="inlineStr">
+        <is>
+          <t>C29423</t>
+        </is>
+      </c>
+      <c r="M169" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>SF-VAL-10</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>S9-R3 / §4 (uniqueness relaxed)</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
           <t>C29424</t>
         </is>
       </c>
-      <c r="M168" s="2" t="inlineStr">
+      <c r="M170" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>SF-VAL-11</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
         <is>
           <t>Verify an unapproved line disables the Complete Work Order button with a tooltip (regardless of the Require Vendor Invoice Number setting)</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>S4-R8 / S3-R9 / Key Decision (line approval)</t>
         </is>
       </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr"/>
-      <c r="L169" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
         <is>
           <t>C29425</t>
         </is>
       </c>
-      <c r="M169" s="2" t="inlineStr">
+      <c r="M171" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>SF-QB-01</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F170" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G170" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I170" s="4" t="inlineStr">
-        <is>
-          <t>§5 invariant 1</t>
-        </is>
-      </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K170" s="4" t="inlineStr">
-        <is>
-          <t>FRESH VIU 2026-07-10: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted through simple-complete 201). Part-History LOG surface BLOCKED-ENV: GET /api/inventory/parts/history -&gt; 500; /parts/inventory/{id} detail page crashes ('page is totaled'); other history endpoints 404/405 (see bugs-log OBS-6). QuickBooks-integrity leg needs QB access.</t>
-        </is>
-      </c>
-      <c r="L170" s="4" t="inlineStr">
-        <is>
-          <t>C29426</t>
-        </is>
-      </c>
-      <c r="M170" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>SF-QB-02</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>VIU-observed-awaiting-Milos</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t>MILOS ANSWER</t>
-        </is>
-      </c>
-      <c r="G171" s="3" t="inlineStr">
-        <is>
-          <t>Milos (Product Owner)</t>
-        </is>
-      </c>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q5 — QuickBooks integrity when Create-POs is OFF (toggle absent).</t>
-        </is>
-      </c>
-      <c r="I171" s="3" t="inlineStr">
-        <is>
-          <t>Q5 | §5 / §4 (Create POs OFF)</t>
-        </is>
-      </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K171" s="3" t="inlineStr"/>
-      <c r="L171" s="3" t="inlineStr">
-        <is>
-          <t>C29427</t>
-        </is>
-      </c>
-      <c r="M171" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29427</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-03</t>
+          <t>SF-QB-01</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -11368,7 +11348,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
+          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -11398,7 +11378,7 @@
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>§5 invariant 2</t>
+          <t>§5 invariant 1</t>
         </is>
       </c>
       <c r="J172" s="4" t="inlineStr">
@@ -11408,91 +11388,87 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>QuickBooks / inventory back-end inspection (receive -&gt; Delivery -&gt; Vendor Bill -&gt; QBO) — likely needs dev/QB access.</t>
+          <t>FRESH VIU 2026-07-10: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted through simple-complete 201). Part-History LOG surface BLOCKED-ENV: GET /api/inventory/parts/history -&gt; 500; /parts/inventory/{id} detail page crashes ('page is totaled'); other history endpoints 404/405 (see bugs-log OBS-6). QuickBooks-integrity leg needs QB access.</t>
         </is>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>C29428</t>
+          <t>C29426</t>
         </is>
       </c>
       <c r="M172" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>SF-QB-04</t>
-        </is>
-      </c>
-      <c r="B173" s="4" t="inlineStr">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>SF-QB-02</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C173" s="4" t="inlineStr">
-        <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="inlineStr">
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>VIU-observed-awaiting-Milos</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
       </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G173" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H173" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I173" s="4" t="inlineStr">
-        <is>
-          <t>§5 (vendorless/no-PN)</t>
-        </is>
-      </c>
-      <c r="J173" s="4" t="inlineStr">
-        <is>
-          <t>needs-data</t>
-        </is>
-      </c>
-      <c r="K173" s="4" t="inlineStr">
-        <is>
-          <t>QuickBooks / inventory inspection (vendorless/no-PN part = zero inventory interaction) — likely needs dev/QB access.</t>
-        </is>
-      </c>
-      <c r="L173" s="4" t="inlineStr">
-        <is>
-          <t>C29429</t>
-        </is>
-      </c>
-      <c r="M173" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>MILOS ANSWER</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>Milos (Product Owner)</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>Milos answers Open Question Q5 — QuickBooks integrity when Create-POs is OFF (toggle absent).</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>Q5 | §5 / §4 (Create POs OFF)</t>
+        </is>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr"/>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>C29427</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29427</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-05</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -11502,7 +11478,7 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -11532,7 +11508,7 @@
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>§5 / S6-R3</t>
+          <t>§5 invariant 2</t>
         </is>
       </c>
       <c r="J174" s="4" t="inlineStr">
@@ -11542,24 +11518,24 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>QuickBooks inspection (Vendor-Missing POs excluded from QB until vendor + PN) — likely needs dev/QB access.</t>
+          <t>QuickBooks / inventory back-end inspection (receive -&gt; Delivery -&gt; Vendor Bill -&gt; QBO) — likely needs dev/QB access.</t>
         </is>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>C29430</t>
+          <t>C29428</t>
         </is>
       </c>
       <c r="M174" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-06</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -11569,7 +11545,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -11599,7 +11575,7 @@
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>§8 (cost at completion)</t>
+          <t>§5 (vendorless/no-PN)</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
@@ -11609,24 +11585,24 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>QuickBooks inspection (cost-at-completion to avoid $0-cost margins) — likely needs dev/QB access.</t>
+          <t>QuickBooks / inventory inspection (vendorless/no-PN part = zero inventory interaction) — likely needs dev/QB access.</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t>C29431</t>
+          <t>C29429</t>
         </is>
       </c>
       <c r="M175" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-07</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -11636,7 +11612,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -11666,7 +11642,7 @@
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>§5 (Journal Entry / Inventory → QBO)</t>
+          <t>§5 / S6-R3</t>
         </is>
       </c>
       <c r="J176" s="4" t="inlineStr">
@@ -11676,87 +11652,91 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>QuickBooks inspection (Journal Entry / Inventory sync fires on invoice creation) — likely needs dev/QB access.</t>
+          <t>QuickBooks inspection (Vendor-Missing POs excluded from QB until vendor + PN) — likely needs dev/QB access.</t>
         </is>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>C29432</t>
+          <t>C29430</t>
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>SF-QB-06</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>Verify Part History is preserved for a part that is genuinely inventory-tracked</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I177" s="2" t="inlineStr">
-        <is>
-          <t>§5 invariant 3 (rescoped after S10-R2 strike)</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="2" t="inlineStr">
-        <is>
-          <t>C29433</t>
-        </is>
-      </c>
-      <c r="M177" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>§8 (cost at completion)</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
+        </is>
+      </c>
+      <c r="K177" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks inspection (cost-at-completion to avoid $0-cost margins) — likely needs dev/QB access.</t>
+        </is>
+      </c>
+      <c r="L177" s="4" t="inlineStr">
+        <is>
+          <t>C29431</t>
+        </is>
+      </c>
+      <c r="M177" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>SF-QB-09</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -11766,7 +11746,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Verify part-sale order status transitions are not regressed by the shared order/status logic (requested to waiting-to-receive to received)</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -11796,44 +11776,44 @@
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>§8 Part Sales — confirmed (Jul 14) + S7/S8 part-sale AC</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="inlineStr">
-        <is>
-          <t>reachable-now</t>
+          <t>§5 (Journal Entry / Inventory → QBO)</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>needs-data</t>
         </is>
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>Δ15 residual check: part-sale status transitions not regressed — seed a Part Sale with a vendor part (now C29909).</t>
+          <t>QuickBooks inspection (Journal Entry / Inventory sync fires on invoice creation) — likely needs dev/QB access.</t>
         </is>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>C29909</t>
+          <t>C29432</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29909</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>SF-AUTO-01</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Verify resolving the last open line by completing a single line auto-completes the work order when Require Review is off</t>
+          <t>Verify Part History is preserved for a part that is genuinely inventory-tracked</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -11863,7 +11843,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>S16-R12 (a) single line</t>
+          <t>§5 invariant 3 (rescoped after S10-R2 strike)</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
@@ -11874,82 +11854,86 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>C29461</t>
+          <t>C29433</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>SF-AUTO-02</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Verify resolving the last open lines in bulk (several at once) auto-completes the work order when Require Review is off</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>READY</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>None — VIU-verified; uploadable now.</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr">
-        <is>
-          <t>S16-R12 (b) bulk</t>
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>SF-QB-09</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>Verify part-sale order status transitions are not regressed by the shared order/status logic (requested to waiting-to-receive to received)</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>§8 Part Sales — confirmed (Jul 14) + S7/S8 part-sale AC</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="2" t="inlineStr">
-        <is>
-          <t>C29462</t>
-        </is>
-      </c>
-      <c r="M180" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29462</t>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t>Δ15 residual check: part-sale status transitions not regressed — seed a Part Sale with a vendor part (now C29909).</t>
+        </is>
+      </c>
+      <c r="L180" s="4" t="inlineStr">
+        <is>
+          <t>C29909</t>
+        </is>
+      </c>
+      <c r="M180" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29909</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>SF-AUTO-03</t>
+          <t>SF-AUTO-01</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -11959,7 +11943,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Verify a split that leaves a work order fully resolved auto-completes that work order when Require Review is off</t>
+          <t>Verify resolving the last open line by completing a single line auto-completes the work order when Require Review is off</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -11989,7 +11973,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>S16-R12 (c) split</t>
+          <t>S16-R12 (a) single line</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
@@ -12000,86 +11984,82 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>C29463</t>
+          <t>C29461</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29461</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="4" t="inlineStr">
-        <is>
-          <t>SF-AUTO-04</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>SF-AUTO-02</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>Verify deleting a line so the remaining lines are all resolved auto-completes the work order when Require Review is off</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="inlineStr">
-        <is>
-          <t>Blocked-Env</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="F182" s="4" t="inlineStr">
-        <is>
-          <t>VIU PENDING (QA)</t>
-        </is>
-      </c>
-      <c r="G182" s="4" t="inlineStr">
-        <is>
-          <t>QA (needs cookies+seed data)</t>
-        </is>
-      </c>
-      <c r="H182" s="4" t="inlineStr">
-        <is>
-          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
-        </is>
-      </c>
-      <c r="I182" s="4" t="inlineStr">
-        <is>
-          <t>S16-R12 (d) delete line</t>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Verify resolving the last open lines in bulk (several at once) auto-completes the work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>S16-R12 (b) bulk</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>reachable-now</t>
-        </is>
-      </c>
-      <c r="K182" s="4" t="inlineStr">
-        <is>
-          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
-        </is>
-      </c>
-      <c r="L182" s="4" t="inlineStr">
-        <is>
-          <t>C29464</t>
-        </is>
-      </c>
-      <c r="M182" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29464</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>C29462</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29462</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>SF-AUTO-05</t>
+          <t>SF-AUTO-03</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -12089,7 +12069,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Verify that with Require Review on, resolving the last open line routes the work order to Ready for Review instead of auto-completing</t>
+          <t>Verify a split that leaves a work order fully resolved auto-completes that work order when Require Review is off</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -12119,7 +12099,7 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>S16-R12 review ON</t>
+          <t>S16-R12 (c) split</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
@@ -12130,19 +12110,19 @@
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>C29465</t>
+          <t>C29463</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29465</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29463</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>SF-AUTO-06</t>
+          <t>SF-AUTO-04</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -12152,7 +12132,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Verify a clock-out that finishes the last line routes the work order to Ready for Review even when Require Review is off</t>
+          <t>Verify deleting a line so the remaining lines are all resolved auto-completes the work order when Require Review is off</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -12182,7 +12162,7 @@
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>S16-R13 clock-out exception</t>
+          <t>S16-R12 (d) delete line</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -12197,29 +12177,29 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>C29466</t>
+          <t>C29464</t>
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29466</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29464</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>SF-AUTO-07</t>
+          <t>SF-AUTO-05</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>API — Auto-Complete Trigger (Story 16 R12/R13)</t>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Verify the work order status transitions on the backend when the last open line is resolved (auto-Complete when review off, Ready for Review when review on)</t>
+          <t>Verify that with Require Review on, resolving the last open line routes the work order to Ready for Review instead of auto-completing</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -12249,7 +12229,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>S16-R12 backend status transition</t>
+          <t>S16-R12 review ON</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -12260,10 +12240,140 @@
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr">
         <is>
+          <t>C29465</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29465</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>SF-AUTO-06</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>Verify a clock-out that finishes the last line routes the work order to Ready for Review even when Require Review is off</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>VIU PENDING (QA)</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>QA (needs cookies+seed data)</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
+        <is>
+          <t>QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
+          <t>S16-R13 clock-out exception</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>reachable-now</t>
+        </is>
+      </c>
+      <c r="K186" s="4" t="inlineStr">
+        <is>
+          <t>admin+tech + normal WO data; needs another VIU pass (no new inputs).</t>
+        </is>
+      </c>
+      <c r="L186" s="4" t="inlineStr">
+        <is>
+          <t>C29466</t>
+        </is>
+      </c>
+      <c r="M186" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29466</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>SF-AUTO-07</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>API — Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Verify the work order status transitions on the backend when the last open line is resolved (auto-Complete when review off, Ready for Review when review on)</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>None — VIU-verified; uploadable now.</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>S16-R12 backend status transition</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
           <t>C29467</t>
         </is>
       </c>
-      <c r="M185" s="2" t="inlineStr">
+      <c r="M187" s="2" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29467</t>
         </is>
@@ -12309,7 +12419,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C3" s="7" t="n"/>
     </row>
@@ -12342,7 +12452,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -12402,7 +12512,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -12417,7 +12527,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C11" s="7" t="inlineStr"/>
     </row>
@@ -12578,7 +12688,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>finalizes the 2 BUG/RULING cases.</t>
+          <t>finalizes the 3 BUG/RULING cases.</t>
         </is>
       </c>
       <c r="C25" s="7" t="n"/>

--- a/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
+++ b/build/simple-flow/SimpleFlow_Blockers_Tracker.xlsx
@@ -10576,8 +10576,16 @@
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr"/>
-      <c r="L159" s="5" t="inlineStr"/>
-      <c r="M159" s="5" t="inlineStr"/>
+      <c r="L159" s="5" t="inlineStr">
+        <is>
+          <t>C30646</t>
+        </is>
+      </c>
+      <c r="M159" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30646</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -10631,8 +10639,16 @@
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="2" t="inlineStr"/>
-      <c r="M160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>C30647</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30647</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
